--- a/public/downloads/Copilot-ROI-Rechner.xlsx
+++ b/public/downloads/Copilot-ROI-Rechner.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1. Eingaben" sheetId="1" r:id="Rd84be0bcc63241eb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2. Executive Summary" sheetId="2" r:id="R4593543433cf4a45"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3. 3-Jahres-Verlauf" sheetId="3" r:id="Rd8c5b334acb944fc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4. Szenarien" sheetId="4" r:id="R5f37cb86ab7046e2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5. Berechnung" sheetId="5" r:id="Ra9b51621f0ed460b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6. Quellen &amp; Methodik" sheetId="6" r:id="Ra6877d3fc6e04b9c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1. Eingaben" sheetId="1" r:id="R8c28451306a74ce9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2. Executive Summary" sheetId="2" r:id="Rce472285576e40cd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3. 3-Jahres-Verlauf" sheetId="3" r:id="R866dfb0b542e44ff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4. Szenarien" sheetId="4" r:id="Rd69ef74213fc40e2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5. Berechnung" sheetId="5" r:id="Rfe901cda8f7543c7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6. Quellen &amp; Methodik" sheetId="6" r:id="Rd050b37d1d9249a1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -88,6 +88,12 @@
       <x:name val="Carlito"/>
     </x:font>
     <x:font>
+      <x:i/>
+      <x:sz val="11"/>
+      <x:color rgb="FFED7D31"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
       <x:b/>
       <x:sz val="11"/>
       <x:color rgb="FF666666"/>
@@ -109,12 +115,6 @@
       <x:i/>
       <x:sz val="11"/>
       <x:color rgb="FF375623"/>
-      <x:name val="Carlito"/>
-    </x:font>
-    <x:font>
-      <x:i/>
-      <x:sz val="11"/>
-      <x:color rgb="FFED7D31"/>
       <x:name val="Carlito"/>
     </x:font>
     <x:font>
@@ -281,7 +281,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="133">
+  <x:cellXfs count="123">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -366,6 +366,9 @@
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
@@ -417,13 +420,45 @@
     <x:xf numFmtId="205" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="10" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="10" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="7" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
     <x:xf numFmtId="201" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
     <x:xf numFmtId="203" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="203" fontId="10" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="11" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
     <x:xf numFmtId="206" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -435,7 +470,7 @@
     <x:xf numFmtId="201" fontId="0" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="203" fontId="10" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="11" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
     <x:xf numFmtId="206" fontId="0" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -453,8 +488,8 @@
     <x:xf numFmtId="200" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="11" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="12" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="8" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
@@ -471,35 +506,11 @@
       <x:alignment vertical="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="12" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="12" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="13" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="13" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="6" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="6" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="13" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="13" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -514,9 +525,6 @@
     <x:xf numFmtId="0" fontId="13" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="13" fillId="6" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
@@ -529,36 +537,31 @@
     <x:xf numFmtId="0" fontId="13" fillId="6" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="14" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="14" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="14" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="14" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="14" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="14" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="14" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="14" fillId="6" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="14" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="14" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="7" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="14" fillId="6" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="15" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -593,37 +596,6 @@
     </x:xf>
     <x:xf numFmtId="202" fontId="0" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="7" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="207" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -929,7 +901,7 @@
           <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:r>
               <a:rPr sz="900"/>
-              <a:t>Die monatliche Zeitersparnis nähert sich dem Zielwert</a:t>
+              <a:t>Entwicklung von Nutzen, Kosten und Netto-Nutzen über 36 Monate (€)</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -951,7 +923,7 @@
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
-            <c:v>Brutto-Zeitersparnis je Nutzer</c:v>
+            <c:v>Kumulierter realisierter Nutzen</c:v>
           </c:tx>
           <c:marker>
             <c:symbol val="none"/>
@@ -968,7 +940,61 @@
             <c:numRef>
               <c:f>'3. 3-Jahres-Verlauf'!$K$2:$K$37</c:f>
               <c:numCache>
-                <c:formatCode>0.0" Std."</c:formatCode>
+                <c:formatCode>#,##0" €"</c:formatCode>
+                <c:ptCount val="0"/>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>Kumulierte Kosten</c:v>
+          </c:tx>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'3. 3-Jahres-Verlauf'!$J$2:$J$37</c:f>
+              <c:strCache>
+                <c:ptCount val="0"/>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'3. 3-Jahres-Verlauf'!$L$2:$L$37</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0" €"</c:formatCode>
+                <c:ptCount val="0"/>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:v>Kumulierter Netto-Nutzen</c:v>
+          </c:tx>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'3. 3-Jahres-Verlauf'!$J$2:$J$37</c:f>
+              <c:strCache>
+                <c:ptCount val="0"/>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'3. 3-Jahres-Verlauf'!$M$2:$M$37</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0" €"</c:formatCode>
                 <c:ptCount val="0"/>
               </c:numCache>
             </c:numRef>
@@ -1016,8 +1042,6 @@
         <c:axId val="48672768"/>
         <c:scaling>
           <c:orientation val="minMax"/>
-          <c:max val="9"/>
-          <c:min val="0"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
@@ -1031,13 +1055,17 @@
             </a:ln>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="0.0&quot; Std.&quot;"/>
+        <c:numFmt formatCode="#,##0&quot; €&quot;"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:crossAx val="48650112"/>
         <c:crossBetween val="between"/>
       </c:valAx>
     </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+    </c:legend>
     <c:plotVisOnly val="1"/>
   </c:chart>
   <c:spPr>
@@ -1064,7 +1092,7 @@
           <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:r>
               <a:rPr sz="900"/>
-              <a:t>Realisierter Nutzen wächst nach dem Kompetenzaufbau</a:t>
+              <a:t>Realisierter Nutzen übersteigt die jährlichen Kosten (€)</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -1091,7 +1119,7 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>'3. 3-Jahres-Verlauf'!$M$2:$M$4</c:f>
+              <c:f>'3. 3-Jahres-Verlauf'!$O$2:$O$4</c:f>
               <c:strCache>
                 <c:ptCount val="0"/>
               </c:strCache>
@@ -1099,7 +1127,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'3. 3-Jahres-Verlauf'!$N$2:$N$4</c:f>
+              <c:f>'3. 3-Jahres-Verlauf'!$P$2:$P$4</c:f>
               <c:numCache>
                 <c:formatCode>#,##0" €"</c:formatCode>
                 <c:ptCount val="0"/>
@@ -1115,7 +1143,7 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>'3. 3-Jahres-Verlauf'!$M$2:$M$4</c:f>
+              <c:f>'3. 3-Jahres-Verlauf'!$O$2:$O$4</c:f>
               <c:strCache>
                 <c:ptCount val="0"/>
               </c:strCache>
@@ -1123,7 +1151,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'3. 3-Jahres-Verlauf'!$O$2:$O$4</c:f>
+              <c:f>'3. 3-Jahres-Verlauf'!$Q$2:$Q$4</c:f>
               <c:numCache>
                 <c:formatCode>#,##0" €"</c:formatCode>
                 <c:ptCount val="0"/>
@@ -1210,172 +1238,6 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/drawings/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:r>
-              <a:rPr sz="900"/>
-              <a:t>Zeitersparnis: schneller Start, danach Sättigung</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" anchorCtr="1"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:pPr>
-            <a:defRPr sz="900"/>
-          </a:pPr>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:plotArea>
-      <c:lineChart>
-        <c:grouping val="standard"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:v>Realistisch</c:v>
-          </c:tx>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:cat>
-            <c:strRef>
-              <c:f>'4. Szenarien'!$A$22:$A$27</c:f>
-              <c:strCache>
-                <c:ptCount val="0"/>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'4. Szenarien'!$B$22:$B$27</c:f>
-              <c:numCache>
-                <c:formatCode>0.0" Std."</c:formatCode>
-                <c:ptCount val="0"/>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:v>Studiennah</c:v>
-          </c:tx>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:cat>
-            <c:strRef>
-              <c:f>'4. Szenarien'!$A$22:$A$27</c:f>
-              <c:strCache>
-                <c:ptCount val="0"/>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'4. Szenarien'!$C$22:$C$27</c:f>
-              <c:numCache>
-                <c:formatCode>0.0" Std."</c:formatCode>
-                <c:ptCount val="0"/>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-        </c:ser>
-        <c:axId val="48650112"/>
-        <c:axId val="48672768"/>
-      </c:lineChart>
-      <c:catAx>
-        <c:axId val="48650112"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
-              <a:solidFill>
-                <a:srgbClr val="CCCCCC"/>
-              </a:solidFill>
-              <a:prstDash val="dash"/>
-            </a:ln>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="General"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr sz="675"/>
-            </a:pPr>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="48672768"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="48672768"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-          <c:max val="10"/>
-          <c:min val="0"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
-              <a:solidFill>
-                <a:srgbClr val="CCCCCC"/>
-              </a:solidFill>
-              <a:prstDash val="dash"/>
-            </a:ln>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="0.0&quot; Std.&quot;"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:crossAx val="48650112"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-    </c:plotArea>
-    <c:legend>
-      <c:legendPos val="b"/>
-      <c:overlay val="0"/>
-    </c:legend>
-    <c:plotVisOnly val="1"/>
-  </c:chart>
-  <c:spPr>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
-      <a:solidFill>
-        <a:srgbClr val="D9D9D9"/>
-      </a:solidFill>
-      <a:prstDash val="solid"/>
-    </a:ln>
-  </c:spPr>
-</c:chartSpace>
-</file>
-
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <xdr:twoCellAnchor>
@@ -1402,7 +1264,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rc2cff140735245af"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R2dc09a6ff1454b9c"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1437,7 +1299,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rc9b3ecef3a764891"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Red19a76345dd45e3"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1467,42 +1329,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Re90dec74d359468d"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="1" name="Chart"/>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" x="0" y="0"/>
-        <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R2d131f55cd624159"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rd0451f76780f4716"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1942,14 +1769,14 @@
       <x:c r="A6" s="20" t="str">
         <x:v>Geplante Copilot-Nutzer</x:v>
       </x:c>
-      <x:c r="B6" s="45" t="n">
+      <x:c r="B6" s="46" t="n">
         <x:f>'1. Eingaben'!B8</x:f>
         <x:v>300</x:v>
       </x:c>
       <x:c r="D6" s="20" t="str">
         <x:v>Ziel-Zeitersparnis pro Monat</x:v>
       </x:c>
-      <x:c r="E6" s="71" t="n">
+      <x:c r="E6" s="84" t="n">
         <x:f>'5. Berechnung'!B4</x:f>
         <x:v>8</x:v>
       </x:c>
@@ -1958,14 +1785,14 @@
       <x:c r="A7" s="20" t="str">
         <x:v>Gesamtkosten Jahr 1</x:v>
       </x:c>
-      <x:c r="B7" s="69" t="n">
+      <x:c r="B7" s="82" t="n">
         <x:f>'5. Berechnung'!G19</x:f>
         <x:v>275072</x:v>
       </x:c>
       <x:c r="D7" s="20" t="str">
         <x:v>Ø Brutto-Zeitersparnis Jahr 1</x:v>
       </x:c>
-      <x:c r="E7" s="71" t="n">
+      <x:c r="E7" s="84" t="n">
         <x:f>'5. Berechnung'!B5</x:f>
         <x:v>7.103768939877063</x:v>
       </x:c>
@@ -1974,14 +1801,14 @@
       <x:c r="A8" s="20" t="str">
         <x:v>Realisierter Nutzen Jahr 1</x:v>
       </x:c>
-      <x:c r="B8" s="69" t="n">
+      <x:c r="B8" s="82" t="n">
         <x:f>'5. Berechnung'!B19</x:f>
         <x:v>639339.2045889356</x:v>
       </x:c>
       <x:c r="D8" s="20" t="str">
         <x:v>Kapazitätswert pro Nutzer Jahr 1</x:v>
       </x:c>
-      <x:c r="E8" s="69" t="n">
+      <x:c r="E8" s="82" t="n">
         <x:f>'5. Berechnung'!B5*12*'1. Eingaben'!B9</x:f>
         <x:v>4262.261363926237</x:v>
       </x:c>
@@ -1990,14 +1817,14 @@
       <x:c r="A9" s="20" t="str">
         <x:v>ROI Jahr 1</x:v>
       </x:c>
-      <x:c r="B9" s="57" t="n">
+      <x:c r="B9" s="70" t="n">
         <x:f>IF(B7=0,0,(B8-B7)/B7)</x:f>
         <x:v>1.3242613010009583</x:v>
       </x:c>
       <x:c r="D9" s="20" t="str">
         <x:v>Realisierter Nutzen pro Nutzer Jahr 1</x:v>
       </x:c>
-      <x:c r="E9" s="69" t="n">
+      <x:c r="E9" s="82" t="n">
         <x:f>'5. Berechnung'!B19/'1. Eingaben'!B8</x:f>
         <x:v>2131.1306819631186</x:v>
       </x:c>
@@ -2006,14 +1833,14 @@
       <x:c r="A10" s="20" t="str">
         <x:v>Gesamtkosten 3 Jahre</x:v>
       </x:c>
-      <x:c r="B10" s="69" t="n">
+      <x:c r="B10" s="82" t="n">
         <x:f>'5. Berechnung'!B9</x:f>
         <x:v>624736</x:v>
       </x:c>
       <x:c r="D10" s="20" t="str">
         <x:v>Gesamtkosten pro Nutzer Jahr 1</x:v>
       </x:c>
-      <x:c r="E10" s="69" t="n">
+      <x:c r="E10" s="82" t="n">
         <x:f>'5. Berechnung'!G19/'1. Eingaben'!B8</x:f>
         <x:v>916.9066666666666</x:v>
       </x:c>
@@ -2022,14 +1849,14 @@
       <x:c r="A11" s="20" t="str">
         <x:v>Realisierter Nutzen 3 Jahre</x:v>
       </x:c>
-      <x:c r="B11" s="69" t="n">
+      <x:c r="B11" s="82" t="n">
         <x:f>'5. Berechnung'!B8</x:f>
         <x:v>2078059.1870836332</x:v>
       </x:c>
       <x:c r="D11" s="20" t="str">
         <x:v>Netto-Nutzen pro Nutzer Jahr 1</x:v>
       </x:c>
-      <x:c r="E11" s="69" t="n">
+      <x:c r="E11" s="82" t="n">
         <x:f>('5. Berechnung'!B19-'5. Berechnung'!G19)/'1. Eingaben'!B8</x:f>
         <x:v>1214.224015296452</x:v>
       </x:c>
@@ -2038,14 +1865,14 @@
       <x:c r="A12" s="20" t="str">
         <x:v>Netto-Nutzen 3 Jahre</x:v>
       </x:c>
-      <x:c r="B12" s="69" t="n">
+      <x:c r="B12" s="82" t="n">
         <x:f>'5. Berechnung'!B10</x:f>
         <x:v>1453323.1870836332</x:v>
       </x:c>
       <x:c r="D12" s="20" t="str">
         <x:v>Wirtschaftlich realisierbar</x:v>
       </x:c>
-      <x:c r="E12" s="43" t="n">
+      <x:c r="E12" s="44" t="n">
         <x:f>'4. Szenarien'!D6</x:f>
         <x:v>0.5</x:v>
       </x:c>
@@ -2054,14 +1881,14 @@
       <x:c r="A13" s="20" t="str">
         <x:v>ROI 3 Jahre</x:v>
       </x:c>
-      <x:c r="B13" s="57" t="n">
+      <x:c r="B13" s="70" t="n">
         <x:f>'5. Berechnung'!B11</x:f>
         <x:v>2.3262997283390634</x:v>
       </x:c>
       <x:c r="D13" s="20" t="str">
         <x:v>IT-Setup automatisch</x:v>
       </x:c>
-      <x:c r="E13" s="69" t="n">
+      <x:c r="E13" s="82" t="n">
         <x:f>'5. Berechnung'!E19</x:f>
         <x:v>27000</x:v>
       </x:c>
@@ -2070,7 +1897,7 @@
       <x:c r="A14" s="20" t="str">
         <x:v>Break-even</x:v>
       </x:c>
-      <x:c r="B14" s="70" t="n">
+      <x:c r="B14" s="83" t="n">
         <x:f>'5. Berechnung'!B12</x:f>
         <x:v>5</x:v>
       </x:c>
@@ -2140,31 +1967,31 @@
         <x:f>'5. Berechnung'!A19</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="B17" s="55" t="n">
+      <x:c r="B17" s="68" t="n">
         <x:f>'5. Berechnung'!B19</x:f>
         <x:v>639339.2045889356</x:v>
       </x:c>
-      <x:c r="C17" s="55" t="n">
+      <x:c r="C17" s="68" t="n">
         <x:f>'5. Berechnung'!C19</x:f>
         <x:v>93600</x:v>
       </x:c>
-      <x:c r="D17" s="55" t="n">
+      <x:c r="D17" s="68" t="n">
         <x:f>'5. Berechnung'!D19</x:f>
         <x:v>125000</x:v>
       </x:c>
-      <x:c r="E17" s="55" t="n">
+      <x:c r="E17" s="68" t="n">
         <x:f>'5. Berechnung'!E19</x:f>
         <x:v>27000</x:v>
       </x:c>
-      <x:c r="F17" s="55" t="n">
+      <x:c r="F17" s="68" t="n">
         <x:f>'5. Berechnung'!F19</x:f>
         <x:v>29472</x:v>
       </x:c>
-      <x:c r="G17" s="55" t="n">
+      <x:c r="G17" s="68" t="n">
         <x:f>'5. Berechnung'!G19</x:f>
         <x:v>275072</x:v>
       </x:c>
-      <x:c r="H17" s="55" t="n">
+      <x:c r="H17" s="68" t="n">
         <x:f>'5. Berechnung'!H19</x:f>
         <x:v>364267.2045889356</x:v>
       </x:c>
@@ -2174,31 +2001,31 @@
         <x:f>'5. Berechnung'!A20</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="B18" s="55" t="n">
+      <x:c r="B18" s="68" t="n">
         <x:f>'5. Berechnung'!B20</x:f>
         <x:v>718739.6750717022</x:v>
       </x:c>
-      <x:c r="C18" s="55" t="n">
+      <x:c r="C18" s="68" t="n">
         <x:f>'5. Berechnung'!C20</x:f>
         <x:v>93600</x:v>
       </x:c>
-      <x:c r="D18" s="55" t="n">
+      <x:c r="D18" s="68" t="n">
         <x:f>'5. Berechnung'!D20</x:f>
         <x:v>62500</x:v>
       </x:c>
-      <x:c r="E18" s="55" t="n">
+      <x:c r="E18" s="68" t="n">
         <x:f>'5. Berechnung'!E20</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F18" s="55" t="n">
+      <x:c r="F18" s="68" t="n">
         <x:f>'5. Berechnung'!F20</x:f>
         <x:v>18732</x:v>
       </x:c>
-      <x:c r="G18" s="55" t="n">
+      <x:c r="G18" s="68" t="n">
         <x:f>'5. Berechnung'!G20</x:f>
         <x:v>174832</x:v>
       </x:c>
-      <x:c r="H18" s="55" t="n">
+      <x:c r="H18" s="68" t="n">
         <x:f>'5. Berechnung'!H20</x:f>
         <x:v>543907.6750717022</x:v>
       </x:c>
@@ -2208,31 +2035,31 @@
         <x:f>'5. Berechnung'!A21</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="B19" s="55" t="n">
+      <x:c r="B19" s="68" t="n">
         <x:f>'5. Berechnung'!B21</x:f>
         <x:v>719980.3074229953</x:v>
       </x:c>
-      <x:c r="C19" s="55" t="n">
+      <x:c r="C19" s="68" t="n">
         <x:f>'5. Berechnung'!C21</x:f>
         <x:v>93600</x:v>
       </x:c>
-      <x:c r="D19" s="55" t="n">
+      <x:c r="D19" s="68" t="n">
         <x:f>'5. Berechnung'!D21</x:f>
         <x:v>62500</x:v>
       </x:c>
-      <x:c r="E19" s="55" t="n">
+      <x:c r="E19" s="68" t="n">
         <x:f>'5. Berechnung'!E21</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F19" s="55" t="n">
+      <x:c r="F19" s="68" t="n">
         <x:f>'5. Berechnung'!F21</x:f>
         <x:v>18732</x:v>
       </x:c>
-      <x:c r="G19" s="55" t="n">
+      <x:c r="G19" s="68" t="n">
         <x:f>'5. Berechnung'!G21</x:f>
         <x:v>174832</x:v>
       </x:c>
-      <x:c r="H19" s="55" t="n">
+      <x:c r="H19" s="68" t="n">
         <x:f>'5. Berechnung'!H21</x:f>
         <x:v>545148.3074229953</x:v>
       </x:c>
@@ -2287,22 +2114,22 @@
       <x:c r="A24" s="20" t="str">
         <x:v>Lizenzen</x:v>
       </x:c>
-      <x:c r="B24" s="55" t="n">
+      <x:c r="B24" s="68" t="n">
         <x:f>SUM('5. Berechnung'!C19:C21)</x:f>
         <x:v>280800</x:v>
       </x:c>
-      <x:c r="C24" s="56" t="n">
+      <x:c r="C24" s="69" t="n">
         <x:f>IF($B$28=0,0,B24/$B$28)</x:f>
         <x:v>0.4494698560672028</x:v>
       </x:c>
-      <x:c r="D24" s="66" t="n">
+      <x:c r="D24" s="79" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="E24" s="55" t="n">
+      <x:c r="E24" s="68" t="n">
         <x:f>'6. Quellen &amp; Methodik'!B16+MIN(D24,50)*'6. Quellen &amp; Methodik'!B17+MAX(MIN(D24-50,200),0)*'6. Quellen &amp; Methodik'!B18+MAX(MIN(D24-250,750),0)*'6. Quellen &amp; Methodik'!B19+MAX(D24-1000,0)*'6. Quellen &amp; Methodik'!B20</x:f>
         <x:v>4000</x:v>
       </x:c>
-      <x:c r="F24" s="55" t="n">
+      <x:c r="F24" s="68" t="n">
         <x:f>E24/D24</x:f>
         <x:v>400</x:v>
       </x:c>
@@ -2311,22 +2138,22 @@
       <x:c r="A25" s="20" t="str">
         <x:v>Training &amp; Weiterbildung</x:v>
       </x:c>
-      <x:c r="B25" s="55" t="n">
+      <x:c r="B25" s="68" t="n">
         <x:f>SUM('5. Berechnung'!D19:D21)</x:f>
         <x:v>250000</x:v>
       </x:c>
-      <x:c r="C25" s="56" t="n">
+      <x:c r="C25" s="69" t="n">
         <x:f>IF($B$28=0,0,B25/$B$28)</x:f>
         <x:v>0.4001690313988629</x:v>
       </x:c>
-      <x:c r="D25" s="66" t="n">
+      <x:c r="D25" s="79" t="n">
         <x:v>300</x:v>
       </x:c>
-      <x:c r="E25" s="55" t="n">
+      <x:c r="E25" s="68" t="n">
         <x:f>'6. Quellen &amp; Methodik'!B16+MIN(D25,50)*'6. Quellen &amp; Methodik'!B17+MAX(MIN(D25-50,200),0)*'6. Quellen &amp; Methodik'!B18+MAX(MIN(D25-250,750),0)*'6. Quellen &amp; Methodik'!B19+MAX(D25-1000,0)*'6. Quellen &amp; Methodik'!B20</x:f>
         <x:v>27000</x:v>
       </x:c>
-      <x:c r="F25" s="55" t="n">
+      <x:c r="F25" s="68" t="n">
         <x:f>E25/D25</x:f>
         <x:v>90</x:v>
       </x:c>
@@ -2335,22 +2162,22 @@
       <x:c r="A26" s="20" t="str">
         <x:v>IT-Setup &amp; Einführung</x:v>
       </x:c>
-      <x:c r="B26" s="55" t="n">
+      <x:c r="B26" s="68" t="n">
         <x:f>SUM('5. Berechnung'!E19:E21)</x:f>
         <x:v>27000</x:v>
       </x:c>
-      <x:c r="C26" s="56" t="n">
+      <x:c r="C26" s="69" t="n">
         <x:f>IF($B$28=0,0,B26/$B$28)</x:f>
         <x:v>0.04321825539107719</x:v>
       </x:c>
-      <x:c r="D26" s="66" t="n">
+      <x:c r="D26" s="79" t="n">
         <x:v>1000</x:v>
       </x:c>
-      <x:c r="E26" s="55" t="n">
+      <x:c r="E26" s="68" t="n">
         <x:f>'6. Quellen &amp; Methodik'!B16+MIN(D26,50)*'6. Quellen &amp; Methodik'!B17+MAX(MIN(D26-50,200),0)*'6. Quellen &amp; Methodik'!B18+MAX(MIN(D26-250,750),0)*'6. Quellen &amp; Methodik'!B19+MAX(D26-1000,0)*'6. Quellen &amp; Methodik'!B20</x:f>
         <x:v>55000</x:v>
       </x:c>
-      <x:c r="F26" s="55" t="n">
+      <x:c r="F26" s="68" t="n">
         <x:f>E26/D26</x:f>
         <x:v>55</x:v>
       </x:c>
@@ -2359,22 +2186,22 @@
       <x:c r="A27" s="20" t="str">
         <x:v>Change &amp; Adoption</x:v>
       </x:c>
-      <x:c r="B27" s="55" t="n">
+      <x:c r="B27" s="68" t="n">
         <x:f>SUM('5. Berechnung'!F19:F21)</x:f>
         <x:v>66936</x:v>
       </x:c>
-      <x:c r="C27" s="56" t="n">
+      <x:c r="C27" s="69" t="n">
         <x:f>IF($B$28=0,0,B27/$B$28)</x:f>
         <x:v>0.10714285714285714</x:v>
       </x:c>
-      <x:c r="D27" s="66" t="n">
+      <x:c r="D27" s="79" t="n">
         <x:v>5000</x:v>
       </x:c>
-      <x:c r="E27" s="55" t="n">
+      <x:c r="E27" s="68" t="n">
         <x:f>'6. Quellen &amp; Methodik'!B16+MIN(D27,50)*'6. Quellen &amp; Methodik'!B17+MAX(MIN(D27-50,200),0)*'6. Quellen &amp; Methodik'!B18+MAX(MIN(D27-250,750),0)*'6. Quellen &amp; Methodik'!B19+MAX(D27-1000,0)*'6. Quellen &amp; Methodik'!B20</x:f>
         <x:v>135000</x:v>
       </x:c>
-      <x:c r="F27" s="55" t="n">
+      <x:c r="F27" s="68" t="n">
         <x:f>E27/D27</x:f>
         <x:v>27</x:v>
       </x:c>
@@ -2383,11 +2210,11 @@
       <x:c r="A28" s="20" t="str">
         <x:v>Gesamtkosten</x:v>
       </x:c>
-      <x:c r="B28" s="69" t="n">
+      <x:c r="B28" s="82" t="n">
         <x:f>SUM(B24:B27)</x:f>
         <x:v>624736</x:v>
       </x:c>
-      <x:c r="C28" s="43" t="n">
+      <x:c r="C28" s="44" t="n">
         <x:f>SUM(C24:C27)</x:f>
         <x:v>0.9999999999999999</x:v>
       </x:c>
@@ -2478,22 +2305,22 @@
       </x:c>
     </x:row>
     <x:row r="35">
-      <x:c r="A35" s="39" t="str">
+      <x:c r="A35" s="40" t="str">
         <x:v>Realistisch</x:v>
       </x:c>
-      <x:c r="B35" s="64" t="n">
+      <x:c r="B35" s="77" t="n">
         <x:f>'5. Berechnung'!B8</x:f>
         <x:v>2078059.1870836332</x:v>
       </x:c>
-      <x:c r="C35" s="64" t="n">
+      <x:c r="C35" s="77" t="n">
         <x:f>'5. Berechnung'!B9</x:f>
         <x:v>624736</x:v>
       </x:c>
-      <x:c r="D35" s="44" t="n">
+      <x:c r="D35" s="45" t="n">
         <x:f>'5. Berechnung'!B11</x:f>
         <x:v>2.3262997283390634</x:v>
       </x:c>
-      <x:c r="E35" s="65" t="n">
+      <x:c r="E35" s="78" t="n">
         <x:f>'5. Berechnung'!B12</x:f>
         <x:v>5</x:v>
       </x:c>
@@ -2502,156 +2329,156 @@
       <x:c r="A36" s="20" t="str">
         <x:v>Studiennah</x:v>
       </x:c>
-      <x:c r="B36" s="55" t="n">
+      <x:c r="B36" s="68" t="n">
         <x:f>'5. Berechnung'!C8</x:f>
         <x:v>2337816.585469087</x:v>
       </x:c>
-      <x:c r="C36" s="55" t="n">
+      <x:c r="C36" s="68" t="n">
         <x:f>'5. Berechnung'!C9</x:f>
         <x:v>624736</x:v>
       </x:c>
-      <x:c r="D36" s="57" t="n">
+      <x:c r="D36" s="70" t="n">
         <x:f>'5. Berechnung'!C11</x:f>
         <x:v>2.742087194381446</x:v>
       </x:c>
-      <x:c r="E36" s="58" t="n">
+      <x:c r="E36" s="71" t="n">
         <x:f>'5. Berechnung'!C12</x:f>
         <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="38">
-      <x:c r="A38" s="86" t="str">
+      <x:c r="A38" s="99" t="str">
         <x:v>ROI &gt; 0%: Der Nutzen übersteigt die Kosten; die Investition erzeugt Netto-Nutzen. ROI = 0%: Break-even. ROI &lt; 0%: Der Nutzen deckt die Kosten im betrachteten Zeitraum noch nicht. Beispiel: 69% ROI bedeutet 69 Cent Netto-Nutzen je investiertem Euro. 100% ROI ist nicht die Gewinnschwelle, sondern entspricht einem gesamten Nutzen in doppelter Höhe der Kosten.</x:v>
       </x:c>
-      <x:c r="B38" s="87" t="str">
+      <x:c r="B38" s="100" t="str">
         <x:v>ROI &gt; 0%: Der Nutzen übersteigt die Kosten; die Investition erzeugt Netto-Nutzen. ROI = 0%: Break-even. ROI &lt; 0%: Der Nutzen deckt die Kosten im betrachteten Zeitraum noch nicht. Beispiel: 69% ROI bedeutet 69 Cent Netto-Nutzen je investiertem Euro. 100% ROI ist nicht die Gewinnschwelle, sondern entspricht einem gesamten Nutzen in doppelter Höhe der Kosten.</x:v>
       </x:c>
-      <x:c r="C38" s="87" t="str">
+      <x:c r="C38" s="100" t="str">
         <x:v>ROI &gt; 0%: Der Nutzen übersteigt die Kosten; die Investition erzeugt Netto-Nutzen. ROI = 0%: Break-even. ROI &lt; 0%: Der Nutzen deckt die Kosten im betrachteten Zeitraum noch nicht. Beispiel: 69% ROI bedeutet 69 Cent Netto-Nutzen je investiertem Euro. 100% ROI ist nicht die Gewinnschwelle, sondern entspricht einem gesamten Nutzen in doppelter Höhe der Kosten.</x:v>
       </x:c>
-      <x:c r="D38" s="87" t="str">
+      <x:c r="D38" s="100" t="str">
         <x:v>ROI &gt; 0%: Der Nutzen übersteigt die Kosten; die Investition erzeugt Netto-Nutzen. ROI = 0%: Break-even. ROI &lt; 0%: Der Nutzen deckt die Kosten im betrachteten Zeitraum noch nicht. Beispiel: 69% ROI bedeutet 69 Cent Netto-Nutzen je investiertem Euro. 100% ROI ist nicht die Gewinnschwelle, sondern entspricht einem gesamten Nutzen in doppelter Höhe der Kosten.</x:v>
       </x:c>
-      <x:c r="E38" s="88" t="str">
+      <x:c r="E38" s="101" t="str">
         <x:v>ROI &gt; 0%: Der Nutzen übersteigt die Kosten; die Investition erzeugt Netto-Nutzen. ROI = 0%: Break-even. ROI &lt; 0%: Der Nutzen deckt die Kosten im betrachteten Zeitraum noch nicht. Beispiel: 69% ROI bedeutet 69 Cent Netto-Nutzen je investiertem Euro. 100% ROI ist nicht die Gewinnschwelle, sondern entspricht einem gesamten Nutzen in doppelter Höhe der Kosten.</x:v>
       </x:c>
     </x:row>
     <x:row r="39">
-      <x:c r="A39" s="89" t="str">
+      <x:c r="A39" s="102" t="str">
         <x:v>ROI &gt; 0%: Der Nutzen übersteigt die Kosten; die Investition erzeugt Netto-Nutzen. ROI = 0%: Break-even. ROI &lt; 0%: Der Nutzen deckt die Kosten im betrachteten Zeitraum noch nicht. Beispiel: 69% ROI bedeutet 69 Cent Netto-Nutzen je investiertem Euro. 100% ROI ist nicht die Gewinnschwelle, sondern entspricht einem gesamten Nutzen in doppelter Höhe der Kosten.</x:v>
       </x:c>
-      <x:c r="B39" s="90" t="str">
+      <x:c r="B39" s="103" t="str">
         <x:v>ROI &gt; 0%: Der Nutzen übersteigt die Kosten; die Investition erzeugt Netto-Nutzen. ROI = 0%: Break-even. ROI &lt; 0%: Der Nutzen deckt die Kosten im betrachteten Zeitraum noch nicht. Beispiel: 69% ROI bedeutet 69 Cent Netto-Nutzen je investiertem Euro. 100% ROI ist nicht die Gewinnschwelle, sondern entspricht einem gesamten Nutzen in doppelter Höhe der Kosten.</x:v>
       </x:c>
-      <x:c r="C39" s="90" t="str">
+      <x:c r="C39" s="103" t="str">
         <x:v>ROI &gt; 0%: Der Nutzen übersteigt die Kosten; die Investition erzeugt Netto-Nutzen. ROI = 0%: Break-even. ROI &lt; 0%: Der Nutzen deckt die Kosten im betrachteten Zeitraum noch nicht. Beispiel: 69% ROI bedeutet 69 Cent Netto-Nutzen je investiertem Euro. 100% ROI ist nicht die Gewinnschwelle, sondern entspricht einem gesamten Nutzen in doppelter Höhe der Kosten.</x:v>
       </x:c>
-      <x:c r="D39" s="90" t="str">
+      <x:c r="D39" s="103" t="str">
         <x:v>ROI &gt; 0%: Der Nutzen übersteigt die Kosten; die Investition erzeugt Netto-Nutzen. ROI = 0%: Break-even. ROI &lt; 0%: Der Nutzen deckt die Kosten im betrachteten Zeitraum noch nicht. Beispiel: 69% ROI bedeutet 69 Cent Netto-Nutzen je investiertem Euro. 100% ROI ist nicht die Gewinnschwelle, sondern entspricht einem gesamten Nutzen in doppelter Höhe der Kosten.</x:v>
       </x:c>
-      <x:c r="E39" s="91" t="str">
+      <x:c r="E39" s="104" t="str">
         <x:v>ROI &gt; 0%: Der Nutzen übersteigt die Kosten; die Investition erzeugt Netto-Nutzen. ROI = 0%: Break-even. ROI &lt; 0%: Der Nutzen deckt die Kosten im betrachteten Zeitraum noch nicht. Beispiel: 69% ROI bedeutet 69 Cent Netto-Nutzen je investiertem Euro. 100% ROI ist nicht die Gewinnschwelle, sondern entspricht einem gesamten Nutzen in doppelter Höhe der Kosten.</x:v>
       </x:c>
     </x:row>
     <x:row r="40">
-      <x:c r="A40" s="89" t="str">
+      <x:c r="A40" s="102" t="str">
         <x:v>ROI &gt; 0%: Der Nutzen übersteigt die Kosten; die Investition erzeugt Netto-Nutzen. ROI = 0%: Break-even. ROI &lt; 0%: Der Nutzen deckt die Kosten im betrachteten Zeitraum noch nicht. Beispiel: 69% ROI bedeutet 69 Cent Netto-Nutzen je investiertem Euro. 100% ROI ist nicht die Gewinnschwelle, sondern entspricht einem gesamten Nutzen in doppelter Höhe der Kosten.</x:v>
       </x:c>
-      <x:c r="B40" s="90" t="str">
+      <x:c r="B40" s="103" t="str">
         <x:v>ROI &gt; 0%: Der Nutzen übersteigt die Kosten; die Investition erzeugt Netto-Nutzen. ROI = 0%: Break-even. ROI &lt; 0%: Der Nutzen deckt die Kosten im betrachteten Zeitraum noch nicht. Beispiel: 69% ROI bedeutet 69 Cent Netto-Nutzen je investiertem Euro. 100% ROI ist nicht die Gewinnschwelle, sondern entspricht einem gesamten Nutzen in doppelter Höhe der Kosten.</x:v>
       </x:c>
-      <x:c r="C40" s="90" t="str">
+      <x:c r="C40" s="103" t="str">
         <x:v>ROI &gt; 0%: Der Nutzen übersteigt die Kosten; die Investition erzeugt Netto-Nutzen. ROI = 0%: Break-even. ROI &lt; 0%: Der Nutzen deckt die Kosten im betrachteten Zeitraum noch nicht. Beispiel: 69% ROI bedeutet 69 Cent Netto-Nutzen je investiertem Euro. 100% ROI ist nicht die Gewinnschwelle, sondern entspricht einem gesamten Nutzen in doppelter Höhe der Kosten.</x:v>
       </x:c>
-      <x:c r="D40" s="90" t="str">
+      <x:c r="D40" s="103" t="str">
         <x:v>ROI &gt; 0%: Der Nutzen übersteigt die Kosten; die Investition erzeugt Netto-Nutzen. ROI = 0%: Break-even. ROI &lt; 0%: Der Nutzen deckt die Kosten im betrachteten Zeitraum noch nicht. Beispiel: 69% ROI bedeutet 69 Cent Netto-Nutzen je investiertem Euro. 100% ROI ist nicht die Gewinnschwelle, sondern entspricht einem gesamten Nutzen in doppelter Höhe der Kosten.</x:v>
       </x:c>
-      <x:c r="E40" s="91" t="str">
+      <x:c r="E40" s="104" t="str">
         <x:v>ROI &gt; 0%: Der Nutzen übersteigt die Kosten; die Investition erzeugt Netto-Nutzen. ROI = 0%: Break-even. ROI &lt; 0%: Der Nutzen deckt die Kosten im betrachteten Zeitraum noch nicht. Beispiel: 69% ROI bedeutet 69 Cent Netto-Nutzen je investiertem Euro. 100% ROI ist nicht die Gewinnschwelle, sondern entspricht einem gesamten Nutzen in doppelter Höhe der Kosten.</x:v>
       </x:c>
     </x:row>
     <x:row r="41">
-      <x:c r="A41" s="92" t="str">
+      <x:c r="A41" s="105" t="str">
         <x:v>ROI &gt; 0%: Der Nutzen übersteigt die Kosten; die Investition erzeugt Netto-Nutzen. ROI = 0%: Break-even. ROI &lt; 0%: Der Nutzen deckt die Kosten im betrachteten Zeitraum noch nicht. Beispiel: 69% ROI bedeutet 69 Cent Netto-Nutzen je investiertem Euro. 100% ROI ist nicht die Gewinnschwelle, sondern entspricht einem gesamten Nutzen in doppelter Höhe der Kosten.</x:v>
       </x:c>
-      <x:c r="B41" s="93" t="str">
+      <x:c r="B41" s="106" t="str">
         <x:v>ROI &gt; 0%: Der Nutzen übersteigt die Kosten; die Investition erzeugt Netto-Nutzen. ROI = 0%: Break-even. ROI &lt; 0%: Der Nutzen deckt die Kosten im betrachteten Zeitraum noch nicht. Beispiel: 69% ROI bedeutet 69 Cent Netto-Nutzen je investiertem Euro. 100% ROI ist nicht die Gewinnschwelle, sondern entspricht einem gesamten Nutzen in doppelter Höhe der Kosten.</x:v>
       </x:c>
-      <x:c r="C41" s="93" t="str">
+      <x:c r="C41" s="106" t="str">
         <x:v>ROI &gt; 0%: Der Nutzen übersteigt die Kosten; die Investition erzeugt Netto-Nutzen. ROI = 0%: Break-even. ROI &lt; 0%: Der Nutzen deckt die Kosten im betrachteten Zeitraum noch nicht. Beispiel: 69% ROI bedeutet 69 Cent Netto-Nutzen je investiertem Euro. 100% ROI ist nicht die Gewinnschwelle, sondern entspricht einem gesamten Nutzen in doppelter Höhe der Kosten.</x:v>
       </x:c>
-      <x:c r="D41" s="93" t="str">
+      <x:c r="D41" s="106" t="str">
         <x:v>ROI &gt; 0%: Der Nutzen übersteigt die Kosten; die Investition erzeugt Netto-Nutzen. ROI = 0%: Break-even. ROI &lt; 0%: Der Nutzen deckt die Kosten im betrachteten Zeitraum noch nicht. Beispiel: 69% ROI bedeutet 69 Cent Netto-Nutzen je investiertem Euro. 100% ROI ist nicht die Gewinnschwelle, sondern entspricht einem gesamten Nutzen in doppelter Höhe der Kosten.</x:v>
       </x:c>
-      <x:c r="E41" s="94" t="str">
+      <x:c r="E41" s="107" t="str">
         <x:v>ROI &gt; 0%: Der Nutzen übersteigt die Kosten; die Investition erzeugt Netto-Nutzen. ROI = 0%: Break-even. ROI &lt; 0%: Der Nutzen deckt die Kosten im betrachteten Zeitraum noch nicht. Beispiel: 69% ROI bedeutet 69 Cent Netto-Nutzen je investiertem Euro. 100% ROI ist nicht die Gewinnschwelle, sondern entspricht einem gesamten Nutzen in doppelter Höhe der Kosten.</x:v>
       </x:c>
     </x:row>
     <x:row r="43">
-      <x:c r="A43" s="107" t="str">
+      <x:c r="A43" s="108" t="str">
         <x:v>Einordnung: Über drei Jahre wird die Lizenz typischerweise zum größten Kostenblock. Das Training bleibt substanziell, verteilt sich aber auf die Erstausbildung und zwei Folgejahre mit jeweils 50% Weiterbildungsbudget. Nutzen und Kosten sind Planungswerte, kein Wirkungsversprechen.</x:v>
       </x:c>
-      <x:c r="B43" s="108" t="str">
+      <x:c r="B43" s="109" t="str">
         <x:v>Einordnung: Über drei Jahre wird die Lizenz typischerweise zum größten Kostenblock. Das Training bleibt substanziell, verteilt sich aber auf die Erstausbildung und zwei Folgejahre mit jeweils 50% Weiterbildungsbudget. Nutzen und Kosten sind Planungswerte, kein Wirkungsversprechen.</x:v>
       </x:c>
-      <x:c r="C43" s="108" t="str">
+      <x:c r="C43" s="109" t="str">
         <x:v>Einordnung: Über drei Jahre wird die Lizenz typischerweise zum größten Kostenblock. Das Training bleibt substanziell, verteilt sich aber auf die Erstausbildung und zwei Folgejahre mit jeweils 50% Weiterbildungsbudget. Nutzen und Kosten sind Planungswerte, kein Wirkungsversprechen.</x:v>
       </x:c>
-      <x:c r="D43" s="108" t="str">
+      <x:c r="D43" s="109" t="str">
         <x:v>Einordnung: Über drei Jahre wird die Lizenz typischerweise zum größten Kostenblock. Das Training bleibt substanziell, verteilt sich aber auf die Erstausbildung und zwei Folgejahre mit jeweils 50% Weiterbildungsbudget. Nutzen und Kosten sind Planungswerte, kein Wirkungsversprechen.</x:v>
       </x:c>
-      <x:c r="E43" s="109" t="str">
+      <x:c r="E43" s="110" t="str">
         <x:v>Einordnung: Über drei Jahre wird die Lizenz typischerweise zum größten Kostenblock. Das Training bleibt substanziell, verteilt sich aber auf die Erstausbildung und zwei Folgejahre mit jeweils 50% Weiterbildungsbudget. Nutzen und Kosten sind Planungswerte, kein Wirkungsversprechen.</x:v>
       </x:c>
     </x:row>
     <x:row r="44">
-      <x:c r="A44" s="110" t="str">
+      <x:c r="A44" s="111" t="str">
         <x:v>Einordnung: Über drei Jahre wird die Lizenz typischerweise zum größten Kostenblock. Das Training bleibt substanziell, verteilt sich aber auf die Erstausbildung und zwei Folgejahre mit jeweils 50% Weiterbildungsbudget. Nutzen und Kosten sind Planungswerte, kein Wirkungsversprechen.</x:v>
       </x:c>
-      <x:c r="B44" s="111" t="str">
+      <x:c r="B44" s="112" t="str">
         <x:v>Einordnung: Über drei Jahre wird die Lizenz typischerweise zum größten Kostenblock. Das Training bleibt substanziell, verteilt sich aber auf die Erstausbildung und zwei Folgejahre mit jeweils 50% Weiterbildungsbudget. Nutzen und Kosten sind Planungswerte, kein Wirkungsversprechen.</x:v>
       </x:c>
-      <x:c r="C44" s="111" t="str">
+      <x:c r="C44" s="112" t="str">
         <x:v>Einordnung: Über drei Jahre wird die Lizenz typischerweise zum größten Kostenblock. Das Training bleibt substanziell, verteilt sich aber auf die Erstausbildung und zwei Folgejahre mit jeweils 50% Weiterbildungsbudget. Nutzen und Kosten sind Planungswerte, kein Wirkungsversprechen.</x:v>
       </x:c>
-      <x:c r="D44" s="111" t="str">
+      <x:c r="D44" s="112" t="str">
         <x:v>Einordnung: Über drei Jahre wird die Lizenz typischerweise zum größten Kostenblock. Das Training bleibt substanziell, verteilt sich aber auf die Erstausbildung und zwei Folgejahre mit jeweils 50% Weiterbildungsbudget. Nutzen und Kosten sind Planungswerte, kein Wirkungsversprechen.</x:v>
       </x:c>
-      <x:c r="E44" s="112" t="str">
+      <x:c r="E44" s="113" t="str">
         <x:v>Einordnung: Über drei Jahre wird die Lizenz typischerweise zum größten Kostenblock. Das Training bleibt substanziell, verteilt sich aber auf die Erstausbildung und zwei Folgejahre mit jeweils 50% Weiterbildungsbudget. Nutzen und Kosten sind Planungswerte, kein Wirkungsversprechen.</x:v>
       </x:c>
     </x:row>
     <x:row r="45">
-      <x:c r="A45" s="110" t="str">
+      <x:c r="A45" s="111" t="str">
         <x:v>Einordnung: Über drei Jahre wird die Lizenz typischerweise zum größten Kostenblock. Das Training bleibt substanziell, verteilt sich aber auf die Erstausbildung und zwei Folgejahre mit jeweils 50% Weiterbildungsbudget. Nutzen und Kosten sind Planungswerte, kein Wirkungsversprechen.</x:v>
       </x:c>
-      <x:c r="B45" s="111" t="str">
+      <x:c r="B45" s="112" t="str">
         <x:v>Einordnung: Über drei Jahre wird die Lizenz typischerweise zum größten Kostenblock. Das Training bleibt substanziell, verteilt sich aber auf die Erstausbildung und zwei Folgejahre mit jeweils 50% Weiterbildungsbudget. Nutzen und Kosten sind Planungswerte, kein Wirkungsversprechen.</x:v>
       </x:c>
-      <x:c r="C45" s="111" t="str">
+      <x:c r="C45" s="112" t="str">
         <x:v>Einordnung: Über drei Jahre wird die Lizenz typischerweise zum größten Kostenblock. Das Training bleibt substanziell, verteilt sich aber auf die Erstausbildung und zwei Folgejahre mit jeweils 50% Weiterbildungsbudget. Nutzen und Kosten sind Planungswerte, kein Wirkungsversprechen.</x:v>
       </x:c>
-      <x:c r="D45" s="111" t="str">
+      <x:c r="D45" s="112" t="str">
         <x:v>Einordnung: Über drei Jahre wird die Lizenz typischerweise zum größten Kostenblock. Das Training bleibt substanziell, verteilt sich aber auf die Erstausbildung und zwei Folgejahre mit jeweils 50% Weiterbildungsbudget. Nutzen und Kosten sind Planungswerte, kein Wirkungsversprechen.</x:v>
       </x:c>
-      <x:c r="E45" s="112" t="str">
+      <x:c r="E45" s="113" t="str">
         <x:v>Einordnung: Über drei Jahre wird die Lizenz typischerweise zum größten Kostenblock. Das Training bleibt substanziell, verteilt sich aber auf die Erstausbildung und zwei Folgejahre mit jeweils 50% Weiterbildungsbudget. Nutzen und Kosten sind Planungswerte, kein Wirkungsversprechen.</x:v>
       </x:c>
     </x:row>
     <x:row r="46">
-      <x:c r="A46" s="113" t="str">
+      <x:c r="A46" s="114" t="str">
         <x:v>Einordnung: Über drei Jahre wird die Lizenz typischerweise zum größten Kostenblock. Das Training bleibt substanziell, verteilt sich aber auf die Erstausbildung und zwei Folgejahre mit jeweils 50% Weiterbildungsbudget. Nutzen und Kosten sind Planungswerte, kein Wirkungsversprechen.</x:v>
       </x:c>
-      <x:c r="B46" s="114" t="str">
+      <x:c r="B46" s="115" t="str">
         <x:v>Einordnung: Über drei Jahre wird die Lizenz typischerweise zum größten Kostenblock. Das Training bleibt substanziell, verteilt sich aber auf die Erstausbildung und zwei Folgejahre mit jeweils 50% Weiterbildungsbudget. Nutzen und Kosten sind Planungswerte, kein Wirkungsversprechen.</x:v>
       </x:c>
-      <x:c r="C46" s="114" t="str">
+      <x:c r="C46" s="115" t="str">
         <x:v>Einordnung: Über drei Jahre wird die Lizenz typischerweise zum größten Kostenblock. Das Training bleibt substanziell, verteilt sich aber auf die Erstausbildung und zwei Folgejahre mit jeweils 50% Weiterbildungsbudget. Nutzen und Kosten sind Planungswerte, kein Wirkungsversprechen.</x:v>
       </x:c>
-      <x:c r="D46" s="114" t="str">
+      <x:c r="D46" s="115" t="str">
         <x:v>Einordnung: Über drei Jahre wird die Lizenz typischerweise zum größten Kostenblock. Das Training bleibt substanziell, verteilt sich aber auf die Erstausbildung und zwei Folgejahre mit jeweils 50% Weiterbildungsbudget. Nutzen und Kosten sind Planungswerte, kein Wirkungsversprechen.</x:v>
       </x:c>
-      <x:c r="E46" s="115" t="str">
+      <x:c r="E46" s="116" t="str">
         <x:v>Einordnung: Über drei Jahre wird die Lizenz typischerweise zum größten Kostenblock. Das Training bleibt substanziell, verteilt sich aber auf die Erstausbildung und zwei Folgejahre mit jeweils 50% Weiterbildungsbudget. Nutzen und Kosten sind Planungswerte, kein Wirkungsversprechen.</x:v>
       </x:c>
     </x:row>
@@ -2703,7 +2530,7 @@
     </x:cfRule>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdbdef059c327417e"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R06b9d6e4f8e743a9"/>
 </x:worksheet>
 </file>
 
@@ -2725,115 +2552,147 @@
     <x:col min="13" max="13" width="1" hidden="0" customWidth="1"/>
     <x:col min="14" max="14" width="1" hidden="0" customWidth="1"/>
     <x:col min="15" max="15" width="1" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="1" hidden="0" customWidth="1"/>
+    <x:col min="17" max="17" width="1" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
       <x:c r="A1" s="3" t="str">
-        <x:v>DREI JAHRE LERNKURVE UND WIRTSCHAFTLICHER NUTZEN</x:v>
+        <x:v>DREI JAHRE WIRTSCHAFTLICHE ENTWICKLUNG</x:v>
       </x:c>
       <x:c r="B1" s="3" t="str">
-        <x:v>DREI JAHRE LERNKURVE UND WIRTSCHAFTLICHER NUTZEN</x:v>
+        <x:v>DREI JAHRE WIRTSCHAFTLICHE ENTWICKLUNG</x:v>
       </x:c>
       <x:c r="C1" s="3" t="str">
-        <x:v>DREI JAHRE LERNKURVE UND WIRTSCHAFTLICHER NUTZEN</x:v>
+        <x:v>DREI JAHRE WIRTSCHAFTLICHE ENTWICKLUNG</x:v>
       </x:c>
       <x:c r="D1" s="3" t="str">
-        <x:v>DREI JAHRE LERNKURVE UND WIRTSCHAFTLICHER NUTZEN</x:v>
+        <x:v>DREI JAHRE WIRTSCHAFTLICHE ENTWICKLUNG</x:v>
       </x:c>
       <x:c r="E1" s="3" t="str">
-        <x:v>DREI JAHRE LERNKURVE UND WIRTSCHAFTLICHER NUTZEN</x:v>
+        <x:v>DREI JAHRE WIRTSCHAFTLICHE ENTWICKLUNG</x:v>
       </x:c>
       <x:c r="F1" s="3" t="str">
-        <x:v>DREI JAHRE LERNKURVE UND WIRTSCHAFTLICHER NUTZEN</x:v>
+        <x:v>DREI JAHRE WIRTSCHAFTLICHE ENTWICKLUNG</x:v>
       </x:c>
       <x:c r="G1" s="3" t="str">
-        <x:v>DREI JAHRE LERNKURVE UND WIRTSCHAFTLICHER NUTZEN</x:v>
+        <x:v>DREI JAHRE WIRTSCHAFTLICHE ENTWICKLUNG</x:v>
       </x:c>
       <x:c r="H1" s="3" t="str">
-        <x:v>DREI JAHRE LERNKURVE UND WIRTSCHAFTLICHER NUTZEN</x:v>
-      </x:c>
-      <x:c r="J1" s="130" t="str">
+        <x:v>DREI JAHRE WIRTSCHAFTLICHE ENTWICKLUNG</x:v>
+      </x:c>
+      <x:c r="J1" s="120" t="str">
         <x:v>Monat</x:v>
       </x:c>
-      <x:c r="K1" s="130" t="str">
-        <x:v>Brutto-Zeitersparnis je Nutzer</x:v>
-      </x:c>
-      <x:c r="L1" s="130"/>
-      <x:c r="M1" s="130" t="str">
+      <x:c r="K1" s="120" t="str">
+        <x:v>Kumulierter realisierter Nutzen</x:v>
+      </x:c>
+      <x:c r="L1" s="120" t="str">
+        <x:v>Kumulierte Kosten</x:v>
+      </x:c>
+      <x:c r="M1" s="120" t="str">
+        <x:v>Kumulierter Netto-Nutzen</x:v>
+      </x:c>
+      <x:c r="N1" s="120"/>
+      <x:c r="O1" s="120" t="str">
         <x:v>Jahr</x:v>
       </x:c>
-      <x:c r="N1" s="130" t="str">
+      <x:c r="P1" s="120" t="str">
         <x:v>Realisierter Nutzen</x:v>
       </x:c>
-      <x:c r="O1" s="130" t="str">
+      <x:c r="Q1" s="120" t="str">
         <x:v>Gesamtkosten</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
-      <x:c r="J2" s="130" t="n">
+      <x:c r="J2" s="120" t="n">
         <x:f>'5. Berechnung'!A26</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K2" s="130" t="n">
-        <x:f>'5. Berechnung'!I26</x:f>
-        <x:v>4.8</x:v>
-      </x:c>
-      <x:c r="L2" s="130"/>
-      <x:c r="M2" s="130" t="n">
+      <x:c r="K2" s="120" t="n">
+        <x:f>'5. Berechnung'!K26</x:f>
+        <x:v>36000</x:v>
+      </x:c>
+      <x:c r="L2" s="120" t="n">
+        <x:f>'5. Berechnung'!H26</x:f>
+        <x:v>189272</x:v>
+      </x:c>
+      <x:c r="M2" s="120" t="n">
+        <x:f>'5. Berechnung'!M26</x:f>
+        <x:v>-153272</x:v>
+      </x:c>
+      <x:c r="N2" s="120"/>
+      <x:c r="O2" s="120" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="N2" s="130" t="n">
+      <x:c r="P2" s="120" t="n">
         <x:f>C7</x:f>
         <x:v>639339.2045889356</x:v>
       </x:c>
-      <x:c r="O2" s="130" t="n">
+      <x:c r="Q2" s="120" t="n">
         <x:f>D7</x:f>
         <x:v>275072</x:v>
       </x:c>
     </x:row>
-    <x:row r="3">
-      <x:c r="A3" s="37" t="str">
-        <x:v>Ein früher Start baut Anwendungskompetenz auf, zieht den Break-even vor und verlängert den Zeitraum, in dem der wirtschaftliche Nutzen wirksam wird.</x:v>
-      </x:c>
-      <x:c r="J3" s="130" t="n">
+    <x:row r="3" ht="30" customHeight="1">
+      <x:c r="A3" s="38" t="str">
+        <x:v>Der kumulierte Nutzen wächst über den gesamten Zeitraum. Die Rechnung verwendet bewusst nur die heute besser belegbare Assistenz-Nutzung; zusätzliches Potenzial aus neuen Funktionen und agentischen Arbeitsabläufen ist nicht eingepreist.</x:v>
+      </x:c>
+      <x:c r="J3" s="120" t="n">
         <x:f>'5. Berechnung'!A27</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K3" s="130" t="n">
-        <x:f>'5. Berechnung'!I27</x:f>
-        <x:v>5.737258300203047</x:v>
-      </x:c>
-      <x:c r="L3" s="130"/>
-      <x:c r="M3" s="130" t="n">
+      <x:c r="K3" s="120" t="n">
+        <x:f>K2+'5. Berechnung'!K27</x:f>
+        <x:v>79029.43725152285</x:v>
+      </x:c>
+      <x:c r="L3" s="120" t="n">
+        <x:f>L2+'5. Berechnung'!H27</x:f>
+        <x:v>197072</x:v>
+      </x:c>
+      <x:c r="M3" s="120" t="n">
+        <x:f>'5. Berechnung'!M27</x:f>
+        <x:v>-118042.56274847715</x:v>
+      </x:c>
+      <x:c r="N3" s="120"/>
+      <x:c r="O3" s="120" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="N3" s="130" t="n">
+      <x:c r="P3" s="120" t="n">
         <x:f>C8</x:f>
         <x:v>718739.6750717022</x:v>
       </x:c>
-      <x:c r="O3" s="130" t="n">
+      <x:c r="Q3" s="120" t="n">
         <x:f>D8</x:f>
         <x:v>174832</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
-      <x:c r="J4" s="130" t="n">
+      <x:c r="J4" s="120" t="n">
         <x:f>'5. Berechnung'!A28</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="K4" s="130" t="n">
-        <x:f>'5. Berechnung'!I28</x:f>
-        <x:v>6.4</x:v>
-      </x:c>
-      <x:c r="L4" s="130"/>
-      <x:c r="M4" s="130" t="n">
+      <x:c r="K4" s="120" t="n">
+        <x:f>K3+'5. Berechnung'!K28</x:f>
+        <x:v>127029.43725152285</x:v>
+      </x:c>
+      <x:c r="L4" s="120" t="n">
+        <x:f>L3+'5. Berechnung'!H28</x:f>
+        <x:v>204872</x:v>
+      </x:c>
+      <x:c r="M4" s="120" t="n">
+        <x:f>'5. Berechnung'!M28</x:f>
+        <x:v>-77842.56274847715</x:v>
+      </x:c>
+      <x:c r="N4" s="120"/>
+      <x:c r="O4" s="120" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="N4" s="130" t="n">
+      <x:c r="P4" s="120" t="n">
         <x:f>C9</x:f>
         <x:v>719980.3074229953</x:v>
       </x:c>
-      <x:c r="O4" s="130" t="n">
+      <x:c r="Q4" s="120" t="n">
         <x:f>D9</x:f>
         <x:v>174832</x:v>
       </x:c>
@@ -2857,18 +2716,26 @@
       <x:c r="F5" s="14" t="str">
         <x:v>REALISTISCHES SZENARIO – ERGEBNISSE NACH JAHR</x:v>
       </x:c>
-      <x:c r="J5" s="130" t="n">
+      <x:c r="J5" s="120" t="n">
         <x:f>'5. Berechnung'!A29</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="K5" s="130" t="n">
-        <x:f>'5. Berechnung'!I29</x:f>
-        <x:v>6.8686291501015235</x:v>
-      </x:c>
-      <x:c r="L5" s="130"/>
-      <x:c r="M5" s="130"/>
-      <x:c r="N5" s="130"/>
-      <x:c r="O5" s="130"/>
+      <x:c r="K5" s="120" t="n">
+        <x:f>K4+'5. Berechnung'!K29</x:f>
+        <x:v>178544.15587728427</x:v>
+      </x:c>
+      <x:c r="L5" s="120" t="n">
+        <x:f>L4+'5. Berechnung'!H29</x:f>
+        <x:v>212672</x:v>
+      </x:c>
+      <x:c r="M5" s="120" t="n">
+        <x:f>'5. Berechnung'!M29</x:f>
+        <x:v>-34127.844122715724</x:v>
+      </x:c>
+      <x:c r="N5" s="120"/>
+      <x:c r="O5" s="120"/>
+      <x:c r="P5" s="120"/>
+      <x:c r="Q5" s="120"/>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="18" t="str">
@@ -2889,447 +2756,647 @@
       <x:c r="F6" s="18" t="str">
         <x:v>Kumulierter Netto-Nutzen</x:v>
       </x:c>
-      <x:c r="J6" s="130" t="n">
+      <x:c r="J6" s="120" t="n">
         <x:f>'5. Berechnung'!A30</x:f>
         <x:v>5</x:v>
       </x:c>
-      <x:c r="K6" s="130" t="n">
-        <x:f>'5. Berechnung'!I30</x:f>
-        <x:v>7.2</x:v>
-      </x:c>
-      <x:c r="L6" s="130"/>
-      <x:c r="M6" s="130"/>
-      <x:c r="N6" s="130"/>
-      <x:c r="O6" s="130"/>
+      <x:c r="K6" s="120" t="n">
+        <x:f>K5+'5. Berechnung'!K30</x:f>
+        <x:v>232544.15587728427</x:v>
+      </x:c>
+      <x:c r="L6" s="120" t="n">
+        <x:f>L5+'5. Berechnung'!H30</x:f>
+        <x:v>220472</x:v>
+      </x:c>
+      <x:c r="M6" s="120" t="n">
+        <x:f>'5. Berechnung'!M30</x:f>
+        <x:v>12072.155877284276</x:v>
+      </x:c>
+      <x:c r="N6" s="120"/>
+      <x:c r="O6" s="120"/>
+      <x:c r="P6" s="120"/>
+      <x:c r="Q6" s="120"/>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="38" t="n">
+      <x:c r="A7" s="39" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="B7" s="117" t="n">
+      <x:c r="B7" s="118" t="n">
         <x:f>'5. Berechnung'!B5</x:f>
         <x:v>7.103768939877063</x:v>
       </x:c>
-      <x:c r="C7" s="60" t="n">
+      <x:c r="C7" s="73" t="n">
         <x:f>'5. Berechnung'!B19</x:f>
         <x:v>639339.2045889356</x:v>
       </x:c>
-      <x:c r="D7" s="60" t="n">
+      <x:c r="D7" s="73" t="n">
         <x:f>'5. Berechnung'!G19</x:f>
         <x:v>275072</x:v>
       </x:c>
-      <x:c r="E7" s="60" t="n">
+      <x:c r="E7" s="73" t="n">
         <x:f>'5. Berechnung'!H19</x:f>
         <x:v>364267.2045889356</x:v>
       </x:c>
-      <x:c r="F7" s="60" t="n">
+      <x:c r="F7" s="73" t="n">
         <x:f>E7</x:f>
         <x:v>364267.2045889356</x:v>
       </x:c>
-      <x:c r="J7" s="130" t="n">
+      <x:c r="J7" s="120" t="n">
         <x:f>'5. Berechnung'!A31</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="K7" s="130" t="n">
-        <x:f>'5. Berechnung'!I31</x:f>
-        <x:v>7.434314575050762</x:v>
-      </x:c>
-      <x:c r="L7" s="130"/>
-      <x:c r="M7" s="130"/>
-      <x:c r="N7" s="130"/>
-      <x:c r="O7" s="130"/>
+      <x:c r="K7" s="120" t="n">
+        <x:f>K6+'5. Berechnung'!K31</x:f>
+        <x:v>288301.51519016497</x:v>
+      </x:c>
+      <x:c r="L7" s="120" t="n">
+        <x:f>L6+'5. Berechnung'!H31</x:f>
+        <x:v>228272</x:v>
+      </x:c>
+      <x:c r="M7" s="120" t="n">
+        <x:f>'5. Berechnung'!M31</x:f>
+        <x:v>60029.515190164995</x:v>
+      </x:c>
+      <x:c r="N7" s="120"/>
+      <x:c r="O7" s="120"/>
+      <x:c r="P7" s="120"/>
+      <x:c r="Q7" s="120"/>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="20" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="B8" s="116" t="n">
+      <x:c r="B8" s="117" t="n">
         <x:f>'5. Berechnung'!B6</x:f>
         <x:v>7.985996389685579</x:v>
       </x:c>
-      <x:c r="C8" s="55" t="n">
+      <x:c r="C8" s="68" t="n">
         <x:f>'5. Berechnung'!B20</x:f>
         <x:v>718739.6750717022</x:v>
       </x:c>
-      <x:c r="D8" s="55" t="n">
+      <x:c r="D8" s="68" t="n">
         <x:f>'5. Berechnung'!G20</x:f>
         <x:v>174832</x:v>
       </x:c>
-      <x:c r="E8" s="55" t="n">
+      <x:c r="E8" s="68" t="n">
         <x:f>'5. Berechnung'!H20</x:f>
         <x:v>543907.6750717022</x:v>
       </x:c>
-      <x:c r="F8" s="55" t="n">
+      <x:c r="F8" s="68" t="n">
         <x:f>F7+E8</x:f>
         <x:v>908174.8796606378</x:v>
       </x:c>
-      <x:c r="J8" s="130" t="n">
+      <x:c r="J8" s="120" t="n">
         <x:f>'5. Berechnung'!A32</x:f>
         <x:v>7</x:v>
       </x:c>
-      <x:c r="K8" s="130" t="n">
-        <x:f>'5. Berechnung'!I32</x:f>
-        <x:v>7.6</x:v>
-      </x:c>
-      <x:c r="L8" s="130"/>
-      <x:c r="M8" s="130"/>
-      <x:c r="N8" s="130"/>
-      <x:c r="O8" s="130"/>
+      <x:c r="K8" s="120" t="n">
+        <x:f>K7+'5. Berechnung'!K32</x:f>
+        <x:v>345301.51519016497</x:v>
+      </x:c>
+      <x:c r="L8" s="120" t="n">
+        <x:f>L7+'5. Berechnung'!H32</x:f>
+        <x:v>236072</x:v>
+      </x:c>
+      <x:c r="M8" s="120" t="n">
+        <x:f>'5. Berechnung'!M32</x:f>
+        <x:v>109229.515190165</x:v>
+      </x:c>
+      <x:c r="N8" s="120"/>
+      <x:c r="O8" s="120"/>
+      <x:c r="P8" s="120"/>
+      <x:c r="Q8" s="120"/>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="20" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="B9" s="116" t="n">
+      <x:c r="B9" s="117" t="n">
         <x:f>'5. Berechnung'!B7</x:f>
         <x:v>7.999781193588838</x:v>
       </x:c>
-      <x:c r="C9" s="55" t="n">
+      <x:c r="C9" s="68" t="n">
         <x:f>'5. Berechnung'!B21</x:f>
         <x:v>719980.3074229953</x:v>
       </x:c>
-      <x:c r="D9" s="55" t="n">
+      <x:c r="D9" s="68" t="n">
         <x:f>'5. Berechnung'!G21</x:f>
         <x:v>174832</x:v>
       </x:c>
-      <x:c r="E9" s="55" t="n">
+      <x:c r="E9" s="68" t="n">
         <x:f>'5. Berechnung'!H21</x:f>
         <x:v>545148.3074229953</x:v>
       </x:c>
-      <x:c r="F9" s="55" t="n">
+      <x:c r="F9" s="68" t="n">
         <x:f>F8+E9</x:f>
         <x:v>1453323.1870836332</x:v>
       </x:c>
-      <x:c r="J9" s="130" t="n">
+      <x:c r="J9" s="120" t="n">
         <x:f>'5. Berechnung'!A33</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="K9" s="130" t="n">
-        <x:f>'5. Berechnung'!I33</x:f>
-        <x:v>7.717157287525381</x:v>
-      </x:c>
-      <x:c r="L9" s="130"/>
-      <x:c r="M9" s="130"/>
-      <x:c r="N9" s="130"/>
-      <x:c r="O9" s="130"/>
+      <x:c r="K9" s="120" t="n">
+        <x:f>K8+'5. Berechnung'!K33</x:f>
+        <x:v>403180.1948466053</x:v>
+      </x:c>
+      <x:c r="L9" s="120" t="n">
+        <x:f>L8+'5. Berechnung'!H33</x:f>
+        <x:v>243872</x:v>
+      </x:c>
+      <x:c r="M9" s="120" t="n">
+        <x:f>'5. Berechnung'!M33</x:f>
+        <x:v>159308.19484660536</x:v>
+      </x:c>
+      <x:c r="N9" s="120"/>
+      <x:c r="O9" s="120"/>
+      <x:c r="P9" s="120"/>
+      <x:c r="Q9" s="120"/>
     </x:row>
     <x:row r="10">
-      <x:c r="J10" s="130" t="n">
+      <x:c r="J10" s="120" t="n">
         <x:f>'5. Berechnung'!A34</x:f>
         <x:v>9</x:v>
       </x:c>
-      <x:c r="K10" s="130" t="n">
-        <x:f>'5. Berechnung'!I34</x:f>
-        <x:v>7.8</x:v>
-      </x:c>
-      <x:c r="L10" s="130"/>
-      <x:c r="M10" s="130"/>
-      <x:c r="N10" s="130"/>
-      <x:c r="O10" s="130"/>
+      <x:c r="K10" s="120" t="n">
+        <x:f>K9+'5. Berechnung'!K34</x:f>
+        <x:v>461680.1948466053</x:v>
+      </x:c>
+      <x:c r="L10" s="120" t="n">
+        <x:f>L9+'5. Berechnung'!H34</x:f>
+        <x:v>251672</x:v>
+      </x:c>
+      <x:c r="M10" s="120" t="n">
+        <x:f>'5. Berechnung'!M34</x:f>
+        <x:v>210008.19484660536</x:v>
+      </x:c>
+      <x:c r="N10" s="120"/>
+      <x:c r="O10" s="120"/>
+      <x:c r="P10" s="120"/>
+      <x:c r="Q10" s="120"/>
     </x:row>
     <x:row r="11" ht="22" customHeight="1">
       <x:c r="A11" s="12" t="str">
-        <x:v>LERNKURVE ÜBER 36 MONATE</x:v>
+        <x:v>KUMULIERTER WIRTSCHAFTLICHER NUTZEN ÜBER 36 MONATE</x:v>
       </x:c>
       <x:c r="B11" s="13" t="str">
-        <x:v>LERNKURVE ÜBER 36 MONATE</x:v>
+        <x:v>KUMULIERTER WIRTSCHAFTLICHER NUTZEN ÜBER 36 MONATE</x:v>
       </x:c>
       <x:c r="C11" s="13" t="str">
-        <x:v>LERNKURVE ÜBER 36 MONATE</x:v>
+        <x:v>KUMULIERTER WIRTSCHAFTLICHER NUTZEN ÜBER 36 MONATE</x:v>
       </x:c>
       <x:c r="D11" s="13" t="str">
-        <x:v>LERNKURVE ÜBER 36 MONATE</x:v>
+        <x:v>KUMULIERTER WIRTSCHAFTLICHER NUTZEN ÜBER 36 MONATE</x:v>
       </x:c>
       <x:c r="E11" s="13" t="str">
-        <x:v>LERNKURVE ÜBER 36 MONATE</x:v>
+        <x:v>KUMULIERTER WIRTSCHAFTLICHER NUTZEN ÜBER 36 MONATE</x:v>
       </x:c>
       <x:c r="F11" s="13" t="str">
-        <x:v>LERNKURVE ÜBER 36 MONATE</x:v>
+        <x:v>KUMULIERTER WIRTSCHAFTLICHER NUTZEN ÜBER 36 MONATE</x:v>
       </x:c>
       <x:c r="G11" s="13" t="str">
-        <x:v>LERNKURVE ÜBER 36 MONATE</x:v>
+        <x:v>KUMULIERTER WIRTSCHAFTLICHER NUTZEN ÜBER 36 MONATE</x:v>
       </x:c>
       <x:c r="H11" s="14" t="str">
-        <x:v>LERNKURVE ÜBER 36 MONATE</x:v>
-      </x:c>
-      <x:c r="J11" s="130" t="n">
+        <x:v>KUMULIERTER WIRTSCHAFTLICHER NUTZEN ÜBER 36 MONATE</x:v>
+      </x:c>
+      <x:c r="J11" s="120" t="n">
         <x:f>'5. Berechnung'!A35</x:f>
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K11" s="130" t="n">
-        <x:f>'5. Berechnung'!I35</x:f>
-        <x:v>7.858578643762691</x:v>
-      </x:c>
-      <x:c r="L11" s="130"/>
-      <x:c r="M11" s="130"/>
-      <x:c r="N11" s="130"/>
-      <x:c r="O11" s="130"/>
+      <x:c r="K11" s="120" t="n">
+        <x:f>K10+'5. Berechnung'!K35</x:f>
+        <x:v>520619.5346748255</x:v>
+      </x:c>
+      <x:c r="L11" s="120" t="n">
+        <x:f>L10+'5. Berechnung'!H35</x:f>
+        <x:v>259472</x:v>
+      </x:c>
+      <x:c r="M11" s="120" t="n">
+        <x:f>'5. Berechnung'!M35</x:f>
+        <x:v>261147.53467482555</x:v>
+      </x:c>
+      <x:c r="N11" s="120"/>
+      <x:c r="O11" s="120"/>
+      <x:c r="P11" s="120"/>
+      <x:c r="Q11" s="120"/>
     </x:row>
     <x:row r="12">
-      <x:c r="J12" s="130" t="n">
+      <x:c r="J12" s="120" t="n">
         <x:f>'5. Berechnung'!A36</x:f>
         <x:v>11</x:v>
       </x:c>
-      <x:c r="K12" s="130" t="n">
-        <x:f>'5. Berechnung'!I36</x:f>
-        <x:v>7.9</x:v>
-      </x:c>
-      <x:c r="L12" s="130"/>
-      <x:c r="M12" s="130"/>
-      <x:c r="N12" s="130"/>
-      <x:c r="O12" s="130"/>
+      <x:c r="K12" s="120" t="n">
+        <x:f>K11+'5. Berechnung'!K36</x:f>
+        <x:v>579869.5346748255</x:v>
+      </x:c>
+      <x:c r="L12" s="120" t="n">
+        <x:f>L11+'5. Berechnung'!H36</x:f>
+        <x:v>267272</x:v>
+      </x:c>
+      <x:c r="M12" s="120" t="n">
+        <x:f>'5. Berechnung'!M36</x:f>
+        <x:v>312597.53467482555</x:v>
+      </x:c>
+      <x:c r="N12" s="120"/>
+      <x:c r="O12" s="120"/>
+      <x:c r="P12" s="120"/>
+      <x:c r="Q12" s="120"/>
     </x:row>
     <x:row r="13">
-      <x:c r="J13" s="130" t="n">
+      <x:c r="J13" s="120" t="n">
         <x:f>'5. Berechnung'!A37</x:f>
         <x:v>12</x:v>
       </x:c>
-      <x:c r="K13" s="130" t="n">
-        <x:f>'5. Berechnung'!I37</x:f>
-        <x:v>7.929289321881345</x:v>
-      </x:c>
-      <x:c r="L13" s="130"/>
-      <x:c r="M13" s="130"/>
-      <x:c r="N13" s="130"/>
-      <x:c r="O13" s="130"/>
+      <x:c r="K13" s="120" t="n">
+        <x:f>K12+'5. Berechnung'!K37</x:f>
+        <x:v>639339.2045889356</x:v>
+      </x:c>
+      <x:c r="L13" s="120" t="n">
+        <x:f>L12+'5. Berechnung'!H37</x:f>
+        <x:v>275072</x:v>
+      </x:c>
+      <x:c r="M13" s="120" t="n">
+        <x:f>'5. Berechnung'!M37</x:f>
+        <x:v>364267.20458893565</x:v>
+      </x:c>
+      <x:c r="N13" s="120"/>
+      <x:c r="O13" s="120"/>
+      <x:c r="P13" s="120"/>
+      <x:c r="Q13" s="120"/>
     </x:row>
     <x:row r="14">
-      <x:c r="J14" s="130" t="n">
+      <x:c r="J14" s="120" t="n">
         <x:f>'5. Berechnung'!A38</x:f>
         <x:v>13</x:v>
       </x:c>
-      <x:c r="K14" s="130" t="n">
-        <x:f>'5. Berechnung'!I38</x:f>
-        <x:v>7.95</x:v>
-      </x:c>
-      <x:c r="L14" s="130"/>
-      <x:c r="M14" s="130"/>
-      <x:c r="N14" s="130"/>
-      <x:c r="O14" s="130"/>
+      <x:c r="K14" s="120" t="n">
+        <x:f>K13+'5. Berechnung'!K38</x:f>
+        <x:v>698964.2045889356</x:v>
+      </x:c>
+      <x:c r="L14" s="120" t="n">
+        <x:f>L13+'5. Berechnung'!H38</x:f>
+        <x:v>364104</x:v>
+      </x:c>
+      <x:c r="M14" s="120" t="n">
+        <x:f>'5. Berechnung'!M38</x:f>
+        <x:v>334860.20458893565</x:v>
+      </x:c>
+      <x:c r="N14" s="120"/>
+      <x:c r="O14" s="120"/>
+      <x:c r="P14" s="120"/>
+      <x:c r="Q14" s="120"/>
     </x:row>
     <x:row r="15">
-      <x:c r="J15" s="130" t="n">
+      <x:c r="J15" s="120" t="n">
         <x:f>'5. Berechnung'!A39</x:f>
         <x:v>14</x:v>
       </x:c>
-      <x:c r="K15" s="130" t="n">
-        <x:f>'5. Berechnung'!I39</x:f>
-        <x:v>7.964644660940673</x:v>
-      </x:c>
-      <x:c r="L15" s="130"/>
-      <x:c r="M15" s="130"/>
-      <x:c r="N15" s="130"/>
-      <x:c r="O15" s="130"/>
+      <x:c r="K15" s="120" t="n">
+        <x:f>K14+'5. Berechnung'!K39</x:f>
+        <x:v>758699.0395459906</x:v>
+      </x:c>
+      <x:c r="L15" s="120" t="n">
+        <x:f>L14+'5. Berechnung'!H39</x:f>
+        <x:v>371904</x:v>
+      </x:c>
+      <x:c r="M15" s="120" t="n">
+        <x:f>'5. Berechnung'!M39</x:f>
+        <x:v>386795.0395459907</x:v>
+      </x:c>
+      <x:c r="N15" s="120"/>
+      <x:c r="O15" s="120"/>
+      <x:c r="P15" s="120"/>
+      <x:c r="Q15" s="120"/>
     </x:row>
     <x:row r="16">
-      <x:c r="J16" s="130" t="n">
+      <x:c r="J16" s="120" t="n">
         <x:f>'5. Berechnung'!A40</x:f>
         <x:v>15</x:v>
       </x:c>
-      <x:c r="K16" s="130" t="n">
-        <x:f>'5. Berechnung'!I40</x:f>
-        <x:v>7.975</x:v>
-      </x:c>
-      <x:c r="L16" s="130"/>
-      <x:c r="M16" s="130"/>
-      <x:c r="N16" s="130"/>
-      <x:c r="O16" s="130"/>
+      <x:c r="K16" s="120" t="n">
+        <x:f>K15+'5. Berechnung'!K40</x:f>
+        <x:v>818511.5395459906</x:v>
+      </x:c>
+      <x:c r="L16" s="120" t="n">
+        <x:f>L15+'5. Berechnung'!H40</x:f>
+        <x:v>379704</x:v>
+      </x:c>
+      <x:c r="M16" s="120" t="n">
+        <x:f>'5. Berechnung'!M40</x:f>
+        <x:v>438807.5395459907</x:v>
+      </x:c>
+      <x:c r="N16" s="120"/>
+      <x:c r="O16" s="120"/>
+      <x:c r="P16" s="120"/>
+      <x:c r="Q16" s="120"/>
     </x:row>
     <x:row r="17">
-      <x:c r="J17" s="130" t="n">
+      <x:c r="J17" s="120" t="n">
         <x:f>'5. Berechnung'!A41</x:f>
         <x:v>16</x:v>
       </x:c>
-      <x:c r="K17" s="130" t="n">
-        <x:f>'5. Berechnung'!I41</x:f>
-        <x:v>7.982322330470336</x:v>
-      </x:c>
-      <x:c r="L17" s="130"/>
-      <x:c r="M17" s="130"/>
-      <x:c r="N17" s="130"/>
-      <x:c r="O17" s="130"/>
+      <x:c r="K17" s="120" t="n">
+        <x:f>K16+'5. Berechnung'!K41</x:f>
+        <x:v>878378.9570245182</x:v>
+      </x:c>
+      <x:c r="L17" s="120" t="n">
+        <x:f>L16+'5. Berechnung'!H41</x:f>
+        <x:v>387504</x:v>
+      </x:c>
+      <x:c r="M17" s="120" t="n">
+        <x:f>'5. Berechnung'!M41</x:f>
+        <x:v>490874.9570245182</x:v>
+      </x:c>
+      <x:c r="N17" s="120"/>
+      <x:c r="O17" s="120"/>
+      <x:c r="P17" s="120"/>
+      <x:c r="Q17" s="120"/>
     </x:row>
     <x:row r="18">
-      <x:c r="J18" s="130" t="n">
+      <x:c r="J18" s="120" t="n">
         <x:f>'5. Berechnung'!A42</x:f>
         <x:v>17</x:v>
       </x:c>
-      <x:c r="K18" s="130" t="n">
-        <x:f>'5. Berechnung'!I42</x:f>
-        <x:v>7.9875</x:v>
-      </x:c>
-      <x:c r="L18" s="130"/>
-      <x:c r="M18" s="130"/>
-      <x:c r="N18" s="130"/>
-      <x:c r="O18" s="130"/>
+      <x:c r="K18" s="120" t="n">
+        <x:f>K17+'5. Berechnung'!K42</x:f>
+        <x:v>938285.2070245182</x:v>
+      </x:c>
+      <x:c r="L18" s="120" t="n">
+        <x:f>L17+'5. Berechnung'!H42</x:f>
+        <x:v>395304</x:v>
+      </x:c>
+      <x:c r="M18" s="120" t="n">
+        <x:f>'5. Berechnung'!M42</x:f>
+        <x:v>542981.2070245182</x:v>
+      </x:c>
+      <x:c r="N18" s="120"/>
+      <x:c r="O18" s="120"/>
+      <x:c r="P18" s="120"/>
+      <x:c r="Q18" s="120"/>
     </x:row>
     <x:row r="19">
-      <x:c r="J19" s="130" t="n">
+      <x:c r="J19" s="120" t="n">
         <x:f>'5. Berechnung'!A43</x:f>
         <x:v>18</x:v>
       </x:c>
-      <x:c r="K19" s="130" t="n">
-        <x:f>'5. Berechnung'!I43</x:f>
-        <x:v>7.991161165235168</x:v>
-      </x:c>
-      <x:c r="L19" s="130"/>
-      <x:c r="M19" s="130"/>
-      <x:c r="N19" s="130"/>
-      <x:c r="O19" s="130"/>
+      <x:c r="K19" s="120" t="n">
+        <x:f>K18+'5. Berechnung'!K43</x:f>
+        <x:v>998218.9157637819</x:v>
+      </x:c>
+      <x:c r="L19" s="120" t="n">
+        <x:f>L18+'5. Berechnung'!H43</x:f>
+        <x:v>403104</x:v>
+      </x:c>
+      <x:c r="M19" s="120" t="n">
+        <x:f>'5. Berechnung'!M43</x:f>
+        <x:v>595114.9157637819</x:v>
+      </x:c>
+      <x:c r="N19" s="120"/>
+      <x:c r="O19" s="120"/>
+      <x:c r="P19" s="120"/>
+      <x:c r="Q19" s="120"/>
     </x:row>
     <x:row r="20">
-      <x:c r="J20" s="130" t="n">
+      <x:c r="J20" s="120" t="n">
         <x:f>'5. Berechnung'!A44</x:f>
         <x:v>19</x:v>
       </x:c>
-      <x:c r="K20" s="130" t="n">
-        <x:f>'5. Berechnung'!I44</x:f>
-        <x:v>7.99375</x:v>
-      </x:c>
-      <x:c r="L20" s="130"/>
-      <x:c r="M20" s="130"/>
-      <x:c r="N20" s="130"/>
-      <x:c r="O20" s="130"/>
+      <x:c r="K20" s="120" t="n">
+        <x:f>K19+'5. Berechnung'!K44</x:f>
+        <x:v>1058172.0407637819</x:v>
+      </x:c>
+      <x:c r="L20" s="120" t="n">
+        <x:f>L19+'5. Berechnung'!H44</x:f>
+        <x:v>410904</x:v>
+      </x:c>
+      <x:c r="M20" s="120" t="n">
+        <x:f>'5. Berechnung'!M44</x:f>
+        <x:v>647268.0407637819</x:v>
+      </x:c>
+      <x:c r="N20" s="120"/>
+      <x:c r="O20" s="120"/>
+      <x:c r="P20" s="120"/>
+      <x:c r="Q20" s="120"/>
     </x:row>
     <x:row r="21">
-      <x:c r="J21" s="130" t="n">
+      <x:c r="J21" s="120" t="n">
         <x:f>'5. Berechnung'!A45</x:f>
         <x:v>20</x:v>
       </x:c>
-      <x:c r="K21" s="130" t="n">
-        <x:f>'5. Berechnung'!I45</x:f>
-        <x:v>7.995580582617584</x:v>
-      </x:c>
-      <x:c r="L21" s="130"/>
-      <x:c r="M21" s="130"/>
-      <x:c r="N21" s="130"/>
-      <x:c r="O21" s="130"/>
+      <x:c r="K21" s="120" t="n">
+        <x:f>K20+'5. Berechnung'!K45</x:f>
+        <x:v>1118138.8951334138</x:v>
+      </x:c>
+      <x:c r="L21" s="120" t="n">
+        <x:f>L20+'5. Berechnung'!H45</x:f>
+        <x:v>418704</x:v>
+      </x:c>
+      <x:c r="M21" s="120" t="n">
+        <x:f>'5. Berechnung'!M45</x:f>
+        <x:v>699434.8951334137</x:v>
+      </x:c>
+      <x:c r="N21" s="120"/>
+      <x:c r="O21" s="120"/>
+      <x:c r="P21" s="120"/>
+      <x:c r="Q21" s="120"/>
     </x:row>
     <x:row r="22">
-      <x:c r="J22" s="130" t="n">
+      <x:c r="J22" s="120" t="n">
         <x:f>'5. Berechnung'!A46</x:f>
         <x:v>21</x:v>
       </x:c>
-      <x:c r="K22" s="130" t="n">
-        <x:f>'5. Berechnung'!I46</x:f>
-        <x:v>7.996875</x:v>
-      </x:c>
-      <x:c r="L22" s="130"/>
-      <x:c r="M22" s="130"/>
-      <x:c r="N22" s="130"/>
-      <x:c r="O22" s="130"/>
+      <x:c r="K22" s="120" t="n">
+        <x:f>K21+'5. Berechnung'!K46</x:f>
+        <x:v>1178115.4576334138</x:v>
+      </x:c>
+      <x:c r="L22" s="120" t="n">
+        <x:f>L21+'5. Berechnung'!H46</x:f>
+        <x:v>426504</x:v>
+      </x:c>
+      <x:c r="M22" s="120" t="n">
+        <x:f>'5. Berechnung'!M46</x:f>
+        <x:v>751611.4576334137</x:v>
+      </x:c>
+      <x:c r="N22" s="120"/>
+      <x:c r="O22" s="120"/>
+      <x:c r="P22" s="120"/>
+      <x:c r="Q22" s="120"/>
     </x:row>
     <x:row r="23">
-      <x:c r="J23" s="130" t="n">
+      <x:c r="J23" s="120" t="n">
         <x:f>'5. Berechnung'!A47</x:f>
         <x:v>22</x:v>
       </x:c>
-      <x:c r="K23" s="130" t="n">
-        <x:f>'5. Berechnung'!I47</x:f>
-        <x:v>7.997790291308792</x:v>
-      </x:c>
-      <x:c r="L23" s="130"/>
-      <x:c r="M23" s="130"/>
-      <x:c r="N23" s="130"/>
-      <x:c r="O23" s="130"/>
+      <x:c r="K23" s="120" t="n">
+        <x:f>K22+'5. Berechnung'!K47</x:f>
+        <x:v>1238098.8848182298</x:v>
+      </x:c>
+      <x:c r="L23" s="120" t="n">
+        <x:f>L22+'5. Berechnung'!H47</x:f>
+        <x:v>434304</x:v>
+      </x:c>
+      <x:c r="M23" s="120" t="n">
+        <x:f>'5. Berechnung'!M47</x:f>
+        <x:v>803794.8848182297</x:v>
+      </x:c>
+      <x:c r="N23" s="120"/>
+      <x:c r="O23" s="120"/>
+      <x:c r="P23" s="120"/>
+      <x:c r="Q23" s="120"/>
     </x:row>
     <x:row r="24">
-      <x:c r="J24" s="130" t="n">
+      <x:c r="J24" s="120" t="n">
         <x:f>'5. Berechnung'!A48</x:f>
         <x:v>23</x:v>
       </x:c>
-      <x:c r="K24" s="130" t="n">
-        <x:f>'5. Berechnung'!I48</x:f>
-        <x:v>7.9984375</x:v>
-      </x:c>
-      <x:c r="L24" s="130"/>
-      <x:c r="M24" s="130"/>
-      <x:c r="N24" s="130"/>
-      <x:c r="O24" s="130"/>
+      <x:c r="K24" s="120" t="n">
+        <x:f>K23+'5. Berechnung'!K48</x:f>
+        <x:v>1298087.1660682298</x:v>
+      </x:c>
+      <x:c r="L24" s="120" t="n">
+        <x:f>L23+'5. Berechnung'!H48</x:f>
+        <x:v>442104</x:v>
+      </x:c>
+      <x:c r="M24" s="120" t="n">
+        <x:f>'5. Berechnung'!M48</x:f>
+        <x:v>855983.1660682297</x:v>
+      </x:c>
+      <x:c r="N24" s="120"/>
+      <x:c r="O24" s="120"/>
+      <x:c r="P24" s="120"/>
+      <x:c r="Q24" s="120"/>
     </x:row>
     <x:row r="25">
-      <x:c r="J25" s="130" t="n">
+      <x:c r="J25" s="120" t="n">
         <x:f>'5. Berechnung'!A49</x:f>
         <x:v>24</x:v>
       </x:c>
-      <x:c r="K25" s="130" t="n">
-        <x:f>'5. Berechnung'!I49</x:f>
-        <x:v>7.998895145654396</x:v>
-      </x:c>
-      <x:c r="L25" s="130"/>
-      <x:c r="M25" s="130"/>
-      <x:c r="N25" s="130"/>
-      <x:c r="O25" s="130"/>
+      <x:c r="K25" s="120" t="n">
+        <x:f>K24+'5. Berechnung'!K49</x:f>
+        <x:v>1358078.8796606378</x:v>
+      </x:c>
+      <x:c r="L25" s="120" t="n">
+        <x:f>L24+'5. Berechnung'!H49</x:f>
+        <x:v>449904</x:v>
+      </x:c>
+      <x:c r="M25" s="120" t="n">
+        <x:f>'5. Berechnung'!M49</x:f>
+        <x:v>908174.8796606377</x:v>
+      </x:c>
+      <x:c r="N25" s="120"/>
+      <x:c r="O25" s="120"/>
+      <x:c r="P25" s="120"/>
+      <x:c r="Q25" s="120"/>
     </x:row>
     <x:row r="26">
-      <x:c r="J26" s="130" t="n">
+      <x:c r="J26" s="120" t="n">
         <x:f>'5. Berechnung'!A50</x:f>
         <x:v>25</x:v>
       </x:c>
-      <x:c r="K26" s="130" t="n">
-        <x:f>'5. Berechnung'!I50</x:f>
-        <x:v>7.99921875</x:v>
-      </x:c>
-      <x:c r="L26" s="130"/>
-      <x:c r="M26" s="130"/>
-      <x:c r="N26" s="130"/>
-      <x:c r="O26" s="130"/>
+      <x:c r="K26" s="120" t="n">
+        <x:f>K25+'5. Berechnung'!K50</x:f>
+        <x:v>1418073.0202856378</x:v>
+      </x:c>
+      <x:c r="L26" s="120" t="n">
+        <x:f>L25+'5. Berechnung'!H50</x:f>
+        <x:v>538936</x:v>
+      </x:c>
+      <x:c r="M26" s="120" t="n">
+        <x:f>'5. Berechnung'!M50</x:f>
+        <x:v>879137.0202856377</x:v>
+      </x:c>
+      <x:c r="N26" s="120"/>
+      <x:c r="O26" s="120"/>
+      <x:c r="P26" s="120"/>
+      <x:c r="Q26" s="120"/>
     </x:row>
     <x:row r="27">
-      <x:c r="J27" s="130" t="n">
+      <x:c r="J27" s="120" t="n">
         <x:f>'5. Berechnung'!A51</x:f>
         <x:v>26</x:v>
       </x:c>
-      <x:c r="K27" s="130" t="n">
-        <x:f>'5. Berechnung'!I51</x:f>
-        <x:v>7.999447572827198</x:v>
-      </x:c>
-      <x:c r="L27" s="130"/>
-      <x:c r="M27" s="130"/>
-      <x:c r="N27" s="130"/>
-      <x:c r="O27" s="130"/>
+      <x:c r="K27" s="120" t="n">
+        <x:f>K26+'5. Berechnung'!K51</x:f>
+        <x:v>1478068.8770818417</x:v>
+      </x:c>
+      <x:c r="L27" s="120" t="n">
+        <x:f>L26+'5. Berechnung'!H51</x:f>
+        <x:v>546736</x:v>
+      </x:c>
+      <x:c r="M27" s="120" t="n">
+        <x:f>'5. Berechnung'!M51</x:f>
+        <x:v>931332.8770818417</x:v>
+      </x:c>
+      <x:c r="N27" s="120"/>
+      <x:c r="O27" s="120"/>
+      <x:c r="P27" s="120"/>
+      <x:c r="Q27" s="120"/>
     </x:row>
     <x:row r="28">
-      <x:c r="J28" s="130" t="n">
+      <x:c r="J28" s="120" t="n">
         <x:f>'5. Berechnung'!A52</x:f>
         <x:v>27</x:v>
       </x:c>
-      <x:c r="K28" s="130" t="n">
-        <x:f>'5. Berechnung'!I52</x:f>
-        <x:v>7.999609375</x:v>
-      </x:c>
-      <x:c r="L28" s="130"/>
-      <x:c r="M28" s="130"/>
-      <x:c r="N28" s="130"/>
-      <x:c r="O28" s="130"/>
+      <x:c r="K28" s="120" t="n">
+        <x:f>K27+'5. Berechnung'!K52</x:f>
+        <x:v>1538065.9473943417</x:v>
+      </x:c>
+      <x:c r="L28" s="120" t="n">
+        <x:f>L27+'5. Berechnung'!H52</x:f>
+        <x:v>554536</x:v>
+      </x:c>
+      <x:c r="M28" s="120" t="n">
+        <x:f>'5. Berechnung'!M52</x:f>
+        <x:v>983529.9473943417</x:v>
+      </x:c>
+      <x:c r="N28" s="120"/>
+      <x:c r="O28" s="120"/>
+      <x:c r="P28" s="120"/>
+      <x:c r="Q28" s="120"/>
     </x:row>
     <x:row r="29">
-      <x:c r="J29" s="130" t="n">
+      <x:c r="J29" s="120" t="n">
         <x:f>'5. Berechnung'!A53</x:f>
         <x:v>28</x:v>
       </x:c>
-      <x:c r="K29" s="130" t="n">
-        <x:f>'5. Berechnung'!I53</x:f>
-        <x:v>7.999723786413599</x:v>
-      </x:c>
-      <x:c r="L29" s="130"/>
-      <x:c r="M29" s="130"/>
-      <x:c r="N29" s="130"/>
-      <x:c r="O29" s="130"/>
+      <x:c r="K29" s="120" t="n">
+        <x:f>K28+'5. Berechnung'!K53</x:f>
+        <x:v>1598063.8757924438</x:v>
+      </x:c>
+      <x:c r="L29" s="120" t="n">
+        <x:f>L28+'5. Berechnung'!H53</x:f>
+        <x:v>562336</x:v>
+      </x:c>
+      <x:c r="M29" s="120" t="n">
+        <x:f>'5. Berechnung'!M53</x:f>
+        <x:v>1035727.8757924436</x:v>
+      </x:c>
+      <x:c r="N29" s="120"/>
+      <x:c r="O29" s="120"/>
+      <x:c r="P29" s="120"/>
+      <x:c r="Q29" s="120"/>
     </x:row>
     <x:row r="30">
-      <x:c r="J30" s="130" t="n">
+      <x:c r="J30" s="120" t="n">
         <x:f>'5. Berechnung'!A54</x:f>
         <x:v>29</x:v>
       </x:c>
-      <x:c r="K30" s="130" t="n">
-        <x:f>'5. Berechnung'!I54</x:f>
-        <x:v>7.9998046875</x:v>
-      </x:c>
-      <x:c r="L30" s="130"/>
-      <x:c r="M30" s="130"/>
-      <x:c r="N30" s="130"/>
-      <x:c r="O30" s="130"/>
+      <x:c r="K30" s="120" t="n">
+        <x:f>K29+'5. Berechnung'!K54</x:f>
+        <x:v>1658062.4109486938</x:v>
+      </x:c>
+      <x:c r="L30" s="120" t="n">
+        <x:f>L29+'5. Berechnung'!H54</x:f>
+        <x:v>570136</x:v>
+      </x:c>
+      <x:c r="M30" s="120" t="n">
+        <x:f>'5. Berechnung'!M54</x:f>
+        <x:v>1087926.4109486938</x:v>
+      </x:c>
+      <x:c r="N30" s="120"/>
+      <x:c r="O30" s="120"/>
+      <x:c r="P30" s="120"/>
+      <x:c r="Q30" s="120"/>
     </x:row>
     <x:row r="31" ht="22" customHeight="1">
       <x:c r="A31" s="12" t="str">
@@ -3356,145 +3423,314 @@
       <x:c r="H31" s="14" t="str">
         <x:v>NUTZEN UND KOSTEN NACH JAHR</x:v>
       </x:c>
-      <x:c r="J31" s="130" t="n">
+      <x:c r="J31" s="120" t="n">
         <x:f>'5. Berechnung'!A55</x:f>
         <x:v>30</x:v>
       </x:c>
-      <x:c r="K31" s="130" t="n">
-        <x:f>'5. Berechnung'!I55</x:f>
-        <x:v>7.999861893206799</x:v>
-      </x:c>
-      <x:c r="L31" s="130"/>
-      <x:c r="M31" s="130"/>
-      <x:c r="N31" s="130"/>
-      <x:c r="O31" s="130"/>
+      <x:c r="K31" s="120" t="n">
+        <x:f>K30+'5. Berechnung'!K55</x:f>
+        <x:v>1718061.3751477448</x:v>
+      </x:c>
+      <x:c r="L31" s="120" t="n">
+        <x:f>L30+'5. Berechnung'!H55</x:f>
+        <x:v>577936</x:v>
+      </x:c>
+      <x:c r="M31" s="120" t="n">
+        <x:f>'5. Berechnung'!M55</x:f>
+        <x:v>1140125.3751477448</x:v>
+      </x:c>
+      <x:c r="N31" s="120"/>
+      <x:c r="O31" s="120"/>
+      <x:c r="P31" s="120"/>
+      <x:c r="Q31" s="120"/>
     </x:row>
     <x:row r="32">
-      <x:c r="J32" s="130" t="n">
+      <x:c r="J32" s="120" t="n">
         <x:f>'5. Berechnung'!A56</x:f>
         <x:v>31</x:v>
       </x:c>
-      <x:c r="K32" s="130" t="n">
-        <x:f>'5. Berechnung'!I56</x:f>
-        <x:v>7.99990234375</x:v>
-      </x:c>
-      <x:c r="L32" s="130"/>
-      <x:c r="M32" s="130"/>
-      <x:c r="N32" s="130"/>
-      <x:c r="O32" s="130"/>
+      <x:c r="K32" s="120" t="n">
+        <x:f>K31+'5. Berechnung'!K56</x:f>
+        <x:v>1778060.6427258698</x:v>
+      </x:c>
+      <x:c r="L32" s="120" t="n">
+        <x:f>L31+'5. Berechnung'!H56</x:f>
+        <x:v>585736</x:v>
+      </x:c>
+      <x:c r="M32" s="120" t="n">
+        <x:f>'5. Berechnung'!M56</x:f>
+        <x:v>1192324.6427258698</x:v>
+      </x:c>
+      <x:c r="N32" s="120"/>
+      <x:c r="O32" s="120"/>
+      <x:c r="P32" s="120"/>
+      <x:c r="Q32" s="120"/>
     </x:row>
     <x:row r="33">
-      <x:c r="J33" s="130" t="n">
+      <x:c r="J33" s="120" t="n">
         <x:f>'5. Berechnung'!A57</x:f>
         <x:v>32</x:v>
       </x:c>
-      <x:c r="K33" s="130" t="n">
-        <x:f>'5. Berechnung'!I57</x:f>
-        <x:v>7.9999309466034</x:v>
-      </x:c>
-      <x:c r="L33" s="130"/>
-      <x:c r="M33" s="130"/>
-      <x:c r="N33" s="130"/>
-      <x:c r="O33" s="130"/>
+      <x:c r="K33" s="120" t="n">
+        <x:f>K32+'5. Berechnung'!K57</x:f>
+        <x:v>1838060.1248253952</x:v>
+      </x:c>
+      <x:c r="L33" s="120" t="n">
+        <x:f>L32+'5. Berechnung'!H57</x:f>
+        <x:v>593536</x:v>
+      </x:c>
+      <x:c r="M33" s="120" t="n">
+        <x:f>'5. Berechnung'!M57</x:f>
+        <x:v>1244524.1248253952</x:v>
+      </x:c>
+      <x:c r="N33" s="120"/>
+      <x:c r="O33" s="120"/>
+      <x:c r="P33" s="120"/>
+      <x:c r="Q33" s="120"/>
     </x:row>
     <x:row r="34">
-      <x:c r="J34" s="130" t="n">
+      <x:c r="J34" s="120" t="n">
         <x:f>'5. Berechnung'!A58</x:f>
         <x:v>33</x:v>
       </x:c>
-      <x:c r="K34" s="130" t="n">
-        <x:f>'5. Berechnung'!I58</x:f>
-        <x:v>7.999951171875</x:v>
-      </x:c>
-      <x:c r="L34" s="130"/>
-      <x:c r="M34" s="130"/>
-      <x:c r="N34" s="130"/>
-      <x:c r="O34" s="130"/>
+      <x:c r="K34" s="120" t="n">
+        <x:f>K33+'5. Berechnung'!K58</x:f>
+        <x:v>1898059.7586144577</x:v>
+      </x:c>
+      <x:c r="L34" s="120" t="n">
+        <x:f>L33+'5. Berechnung'!H58</x:f>
+        <x:v>601336</x:v>
+      </x:c>
+      <x:c r="M34" s="120" t="n">
+        <x:f>'5. Berechnung'!M58</x:f>
+        <x:v>1296723.7586144577</x:v>
+      </x:c>
+      <x:c r="N34" s="120"/>
+      <x:c r="O34" s="120"/>
+      <x:c r="P34" s="120"/>
+      <x:c r="Q34" s="120"/>
     </x:row>
     <x:row r="35">
-      <x:c r="J35" s="130" t="n">
+      <x:c r="J35" s="120" t="n">
         <x:f>'5. Berechnung'!A59</x:f>
         <x:v>34</x:v>
       </x:c>
-      <x:c r="K35" s="130" t="n">
-        <x:f>'5. Berechnung'!I59</x:f>
-        <x:v>7.9999654733017</x:v>
-      </x:c>
-      <x:c r="L35" s="130"/>
-      <x:c r="M35" s="130"/>
-      <x:c r="N35" s="130"/>
-      <x:c r="O35" s="130"/>
+      <x:c r="K35" s="120" t="n">
+        <x:f>K34+'5. Berechnung'!K59</x:f>
+        <x:v>1958059.4996642205</x:v>
+      </x:c>
+      <x:c r="L35" s="120" t="n">
+        <x:f>L34+'5. Berechnung'!H59</x:f>
+        <x:v>609136</x:v>
+      </x:c>
+      <x:c r="M35" s="120" t="n">
+        <x:f>'5. Berechnung'!M59</x:f>
+        <x:v>1348923.4996642205</x:v>
+      </x:c>
+      <x:c r="N35" s="120"/>
+      <x:c r="O35" s="120"/>
+      <x:c r="P35" s="120"/>
+      <x:c r="Q35" s="120"/>
     </x:row>
     <x:row r="36">
-      <x:c r="J36" s="130" t="n">
+      <x:c r="J36" s="120" t="n">
         <x:f>'5. Berechnung'!A60</x:f>
         <x:v>35</x:v>
       </x:c>
-      <x:c r="K36" s="130" t="n">
-        <x:f>'5. Berechnung'!I60</x:f>
-        <x:v>7.9999755859375</x:v>
-      </x:c>
-      <x:c r="L36" s="130"/>
-      <x:c r="M36" s="130"/>
-      <x:c r="N36" s="130"/>
-      <x:c r="O36" s="130"/>
+      <x:c r="K36" s="120" t="n">
+        <x:f>K35+'5. Berechnung'!K60</x:f>
+        <x:v>2018059.3165587517</x:v>
+      </x:c>
+      <x:c r="L36" s="120" t="n">
+        <x:f>L35+'5. Berechnung'!H60</x:f>
+        <x:v>616936</x:v>
+      </x:c>
+      <x:c r="M36" s="120" t="n">
+        <x:f>'5. Berechnung'!M60</x:f>
+        <x:v>1401123.3165587517</x:v>
+      </x:c>
+      <x:c r="N36" s="120"/>
+      <x:c r="O36" s="120"/>
+      <x:c r="P36" s="120"/>
+      <x:c r="Q36" s="120"/>
     </x:row>
     <x:row r="37">
-      <x:c r="J37" s="130" t="n">
+      <x:c r="J37" s="120" t="n">
         <x:f>'5. Berechnung'!A61</x:f>
         <x:v>36</x:v>
       </x:c>
-      <x:c r="K37" s="130" t="n">
-        <x:f>'5. Berechnung'!I61</x:f>
-        <x:v>7.99998273665085</x:v>
-      </x:c>
-      <x:c r="L37" s="130"/>
-      <x:c r="M37" s="130"/>
-      <x:c r="N37" s="130"/>
-      <x:c r="O37" s="130"/>
-    </x:row>
-    <x:row r="50">
-      <x:c r="A50" s="121" t="str">
-        <x:f>"Im realistischen Szenario entstehen bereits im ersten Jahr "&amp;TEXT(C7,"#,##0 €")&amp;" realisierter Nutzen. In Jahr 2 steigt der Jahresnutzen auf "&amp;TEXT(C8,"#,##0 €")&amp;", weil die Lernkurve weitgehend aufgebaut ist. Ein späterer Beginn verschiebt diese Entwicklung und den Break-even entsprechend nach hinten."</x:f>
-        <x:v>Im realistischen Szenario entstehen bereits im ersten Jahr 639,339 € realisierter Nutzen. In Jahr 2 steigt der Jahresnutzen auf 718,740 €, weil die Lernkurve weitgehend aufgebaut ist. Ein späterer Beginn verschiebt diese Entwicklung und den Break-even entsprechend nach hinten.</x:v>
-      </x:c>
-      <x:c r="B50" s="122"/>
-      <x:c r="C50" s="122"/>
-      <x:c r="D50" s="122"/>
-      <x:c r="E50" s="122"/>
-      <x:c r="F50" s="122"/>
-      <x:c r="G50" s="122"/>
-      <x:c r="H50" s="123"/>
+      <x:c r="K37" s="120" t="n">
+        <x:f>K36+'5. Berechnung'!K61</x:f>
+        <x:v>2078059.1870836332</x:v>
+      </x:c>
+      <x:c r="L37" s="120" t="n">
+        <x:f>L36+'5. Berechnung'!H61</x:f>
+        <x:v>624736</x:v>
+      </x:c>
+      <x:c r="M37" s="120" t="n">
+        <x:f>'5. Berechnung'!M61</x:f>
+        <x:v>1453323.1870836332</x:v>
+      </x:c>
+      <x:c r="N37" s="120"/>
+      <x:c r="O37" s="120"/>
+      <x:c r="P37" s="120"/>
+      <x:c r="Q37" s="120"/>
+    </x:row>
+    <x:row r="50" ht="22" customHeight="1">
+      <x:c r="A50" s="12" t="str">
+        <x:v>WAS DIE DREI-JAHRES-PERSPEKTIVE BEWUSST NICHT DECKELT</x:v>
+      </x:c>
+      <x:c r="B50" s="13" t="str">
+        <x:v>WAS DIE DREI-JAHRES-PERSPEKTIVE BEWUSST NICHT DECKELT</x:v>
+      </x:c>
+      <x:c r="C50" s="13" t="str">
+        <x:v>WAS DIE DREI-JAHRES-PERSPEKTIVE BEWUSST NICHT DECKELT</x:v>
+      </x:c>
+      <x:c r="D50" s="13" t="str">
+        <x:v>WAS DIE DREI-JAHRES-PERSPEKTIVE BEWUSST NICHT DECKELT</x:v>
+      </x:c>
+      <x:c r="E50" s="13" t="str">
+        <x:v>WAS DIE DREI-JAHRES-PERSPEKTIVE BEWUSST NICHT DECKELT</x:v>
+      </x:c>
+      <x:c r="F50" s="13" t="str">
+        <x:v>WAS DIE DREI-JAHRES-PERSPEKTIVE BEWUSST NICHT DECKELT</x:v>
+      </x:c>
+      <x:c r="G50" s="13" t="str">
+        <x:v>WAS DIE DREI-JAHRES-PERSPEKTIVE BEWUSST NICHT DECKELT</x:v>
+      </x:c>
+      <x:c r="H50" s="14" t="str">
+        <x:v>WAS DIE DREI-JAHRES-PERSPEKTIVE BEWUSST NICHT DECKELT</x:v>
+      </x:c>
     </x:row>
     <x:row r="51">
-      <x:c r="A51" s="124"/>
-      <x:c r="B51" s="120"/>
-      <x:c r="C51" s="120"/>
-      <x:c r="D51" s="120"/>
-      <x:c r="E51" s="120"/>
-      <x:c r="F51" s="120"/>
-      <x:c r="G51" s="120"/>
-      <x:c r="H51" s="125"/>
+      <x:c r="A51" s="60" t="str">
+        <x:v>Die 8 beziehungsweise 9 Stunden sind eine konservativ festgehaltene Assistenz-Baseline – keine langfristige Obergrenze. Leistungsfähigere Modelle, zusätzliche Werkzeuge, bessere Prozessintegration und der Übergang zu agentischen, mehrstufigen Tätigkeiten können den Nutzen künftig weiter erhöhen. Weil dafür noch keine belastbaren, allgemein übertragbaren Benchmarks vorliegen, wird dieses zusätzliche Potenzial nicht in den ROI hineingerechnet. So bleibt der Business Case nachvollziehbar, ohne die technologische Entwicklung kleinzurechnen.</x:v>
+      </x:c>
+      <x:c r="B51" s="61" t="str">
+        <x:v>Die 8 beziehungsweise 9 Stunden sind eine konservativ festgehaltene Assistenz-Baseline – keine langfristige Obergrenze. Leistungsfähigere Modelle, zusätzliche Werkzeuge, bessere Prozessintegration und der Übergang zu agentischen, mehrstufigen Tätigkeiten können den Nutzen künftig weiter erhöhen. Weil dafür noch keine belastbaren, allgemein übertragbaren Benchmarks vorliegen, wird dieses zusätzliche Potenzial nicht in den ROI hineingerechnet. So bleibt der Business Case nachvollziehbar, ohne die technologische Entwicklung kleinzurechnen.</x:v>
+      </x:c>
+      <x:c r="C51" s="61" t="str">
+        <x:v>Die 8 beziehungsweise 9 Stunden sind eine konservativ festgehaltene Assistenz-Baseline – keine langfristige Obergrenze. Leistungsfähigere Modelle, zusätzliche Werkzeuge, bessere Prozessintegration und der Übergang zu agentischen, mehrstufigen Tätigkeiten können den Nutzen künftig weiter erhöhen. Weil dafür noch keine belastbaren, allgemein übertragbaren Benchmarks vorliegen, wird dieses zusätzliche Potenzial nicht in den ROI hineingerechnet. So bleibt der Business Case nachvollziehbar, ohne die technologische Entwicklung kleinzurechnen.</x:v>
+      </x:c>
+      <x:c r="D51" s="61" t="str">
+        <x:v>Die 8 beziehungsweise 9 Stunden sind eine konservativ festgehaltene Assistenz-Baseline – keine langfristige Obergrenze. Leistungsfähigere Modelle, zusätzliche Werkzeuge, bessere Prozessintegration und der Übergang zu agentischen, mehrstufigen Tätigkeiten können den Nutzen künftig weiter erhöhen. Weil dafür noch keine belastbaren, allgemein übertragbaren Benchmarks vorliegen, wird dieses zusätzliche Potenzial nicht in den ROI hineingerechnet. So bleibt der Business Case nachvollziehbar, ohne die technologische Entwicklung kleinzurechnen.</x:v>
+      </x:c>
+      <x:c r="E51" s="61" t="str">
+        <x:v>Die 8 beziehungsweise 9 Stunden sind eine konservativ festgehaltene Assistenz-Baseline – keine langfristige Obergrenze. Leistungsfähigere Modelle, zusätzliche Werkzeuge, bessere Prozessintegration und der Übergang zu agentischen, mehrstufigen Tätigkeiten können den Nutzen künftig weiter erhöhen. Weil dafür noch keine belastbaren, allgemein übertragbaren Benchmarks vorliegen, wird dieses zusätzliche Potenzial nicht in den ROI hineingerechnet. So bleibt der Business Case nachvollziehbar, ohne die technologische Entwicklung kleinzurechnen.</x:v>
+      </x:c>
+      <x:c r="F51" s="61" t="str">
+        <x:v>Die 8 beziehungsweise 9 Stunden sind eine konservativ festgehaltene Assistenz-Baseline – keine langfristige Obergrenze. Leistungsfähigere Modelle, zusätzliche Werkzeuge, bessere Prozessintegration und der Übergang zu agentischen, mehrstufigen Tätigkeiten können den Nutzen künftig weiter erhöhen. Weil dafür noch keine belastbaren, allgemein übertragbaren Benchmarks vorliegen, wird dieses zusätzliche Potenzial nicht in den ROI hineingerechnet. So bleibt der Business Case nachvollziehbar, ohne die technologische Entwicklung kleinzurechnen.</x:v>
+      </x:c>
+      <x:c r="G51" s="61" t="str">
+        <x:v>Die 8 beziehungsweise 9 Stunden sind eine konservativ festgehaltene Assistenz-Baseline – keine langfristige Obergrenze. Leistungsfähigere Modelle, zusätzliche Werkzeuge, bessere Prozessintegration und der Übergang zu agentischen, mehrstufigen Tätigkeiten können den Nutzen künftig weiter erhöhen. Weil dafür noch keine belastbaren, allgemein übertragbaren Benchmarks vorliegen, wird dieses zusätzliche Potenzial nicht in den ROI hineingerechnet. So bleibt der Business Case nachvollziehbar, ohne die technologische Entwicklung kleinzurechnen.</x:v>
+      </x:c>
+      <x:c r="H51" s="62" t="str">
+        <x:v>Die 8 beziehungsweise 9 Stunden sind eine konservativ festgehaltene Assistenz-Baseline – keine langfristige Obergrenze. Leistungsfähigere Modelle, zusätzliche Werkzeuge, bessere Prozessintegration und der Übergang zu agentischen, mehrstufigen Tätigkeiten können den Nutzen künftig weiter erhöhen. Weil dafür noch keine belastbaren, allgemein übertragbaren Benchmarks vorliegen, wird dieses zusätzliche Potenzial nicht in den ROI hineingerechnet. So bleibt der Business Case nachvollziehbar, ohne die technologische Entwicklung kleinzurechnen.</x:v>
+      </x:c>
     </x:row>
     <x:row r="52">
-      <x:c r="A52" s="124"/>
-      <x:c r="B52" s="120"/>
-      <x:c r="C52" s="120"/>
-      <x:c r="D52" s="120"/>
-      <x:c r="E52" s="120"/>
-      <x:c r="F52" s="120"/>
-      <x:c r="G52" s="120"/>
-      <x:c r="H52" s="125"/>
+      <x:c r="A52" s="63" t="str">
+        <x:v>Die 8 beziehungsweise 9 Stunden sind eine konservativ festgehaltene Assistenz-Baseline – keine langfristige Obergrenze. Leistungsfähigere Modelle, zusätzliche Werkzeuge, bessere Prozessintegration und der Übergang zu agentischen, mehrstufigen Tätigkeiten können den Nutzen künftig weiter erhöhen. Weil dafür noch keine belastbaren, allgemein übertragbaren Benchmarks vorliegen, wird dieses zusätzliche Potenzial nicht in den ROI hineingerechnet. So bleibt der Business Case nachvollziehbar, ohne die technologische Entwicklung kleinzurechnen.</x:v>
+      </x:c>
+      <x:c r="B52" s="59" t="str">
+        <x:v>Die 8 beziehungsweise 9 Stunden sind eine konservativ festgehaltene Assistenz-Baseline – keine langfristige Obergrenze. Leistungsfähigere Modelle, zusätzliche Werkzeuge, bessere Prozessintegration und der Übergang zu agentischen, mehrstufigen Tätigkeiten können den Nutzen künftig weiter erhöhen. Weil dafür noch keine belastbaren, allgemein übertragbaren Benchmarks vorliegen, wird dieses zusätzliche Potenzial nicht in den ROI hineingerechnet. So bleibt der Business Case nachvollziehbar, ohne die technologische Entwicklung kleinzurechnen.</x:v>
+      </x:c>
+      <x:c r="C52" s="59" t="str">
+        <x:v>Die 8 beziehungsweise 9 Stunden sind eine konservativ festgehaltene Assistenz-Baseline – keine langfristige Obergrenze. Leistungsfähigere Modelle, zusätzliche Werkzeuge, bessere Prozessintegration und der Übergang zu agentischen, mehrstufigen Tätigkeiten können den Nutzen künftig weiter erhöhen. Weil dafür noch keine belastbaren, allgemein übertragbaren Benchmarks vorliegen, wird dieses zusätzliche Potenzial nicht in den ROI hineingerechnet. So bleibt der Business Case nachvollziehbar, ohne die technologische Entwicklung kleinzurechnen.</x:v>
+      </x:c>
+      <x:c r="D52" s="59" t="str">
+        <x:v>Die 8 beziehungsweise 9 Stunden sind eine konservativ festgehaltene Assistenz-Baseline – keine langfristige Obergrenze. Leistungsfähigere Modelle, zusätzliche Werkzeuge, bessere Prozessintegration und der Übergang zu agentischen, mehrstufigen Tätigkeiten können den Nutzen künftig weiter erhöhen. Weil dafür noch keine belastbaren, allgemein übertragbaren Benchmarks vorliegen, wird dieses zusätzliche Potenzial nicht in den ROI hineingerechnet. So bleibt der Business Case nachvollziehbar, ohne die technologische Entwicklung kleinzurechnen.</x:v>
+      </x:c>
+      <x:c r="E52" s="59" t="str">
+        <x:v>Die 8 beziehungsweise 9 Stunden sind eine konservativ festgehaltene Assistenz-Baseline – keine langfristige Obergrenze. Leistungsfähigere Modelle, zusätzliche Werkzeuge, bessere Prozessintegration und der Übergang zu agentischen, mehrstufigen Tätigkeiten können den Nutzen künftig weiter erhöhen. Weil dafür noch keine belastbaren, allgemein übertragbaren Benchmarks vorliegen, wird dieses zusätzliche Potenzial nicht in den ROI hineingerechnet. So bleibt der Business Case nachvollziehbar, ohne die technologische Entwicklung kleinzurechnen.</x:v>
+      </x:c>
+      <x:c r="F52" s="59" t="str">
+        <x:v>Die 8 beziehungsweise 9 Stunden sind eine konservativ festgehaltene Assistenz-Baseline – keine langfristige Obergrenze. Leistungsfähigere Modelle, zusätzliche Werkzeuge, bessere Prozessintegration und der Übergang zu agentischen, mehrstufigen Tätigkeiten können den Nutzen künftig weiter erhöhen. Weil dafür noch keine belastbaren, allgemein übertragbaren Benchmarks vorliegen, wird dieses zusätzliche Potenzial nicht in den ROI hineingerechnet. So bleibt der Business Case nachvollziehbar, ohne die technologische Entwicklung kleinzurechnen.</x:v>
+      </x:c>
+      <x:c r="G52" s="59" t="str">
+        <x:v>Die 8 beziehungsweise 9 Stunden sind eine konservativ festgehaltene Assistenz-Baseline – keine langfristige Obergrenze. Leistungsfähigere Modelle, zusätzliche Werkzeuge, bessere Prozessintegration und der Übergang zu agentischen, mehrstufigen Tätigkeiten können den Nutzen künftig weiter erhöhen. Weil dafür noch keine belastbaren, allgemein übertragbaren Benchmarks vorliegen, wird dieses zusätzliche Potenzial nicht in den ROI hineingerechnet. So bleibt der Business Case nachvollziehbar, ohne die technologische Entwicklung kleinzurechnen.</x:v>
+      </x:c>
+      <x:c r="H52" s="64" t="str">
+        <x:v>Die 8 beziehungsweise 9 Stunden sind eine konservativ festgehaltene Assistenz-Baseline – keine langfristige Obergrenze. Leistungsfähigere Modelle, zusätzliche Werkzeuge, bessere Prozessintegration und der Übergang zu agentischen, mehrstufigen Tätigkeiten können den Nutzen künftig weiter erhöhen. Weil dafür noch keine belastbaren, allgemein übertragbaren Benchmarks vorliegen, wird dieses zusätzliche Potenzial nicht in den ROI hineingerechnet. So bleibt der Business Case nachvollziehbar, ohne die technologische Entwicklung kleinzurechnen.</x:v>
+      </x:c>
     </x:row>
     <x:row r="53">
-      <x:c r="A53" s="126"/>
-      <x:c r="B53" s="127"/>
-      <x:c r="C53" s="127"/>
-      <x:c r="D53" s="127"/>
-      <x:c r="E53" s="127"/>
-      <x:c r="F53" s="127"/>
-      <x:c r="G53" s="127"/>
-      <x:c r="H53" s="128"/>
+      <x:c r="A53" s="63" t="str">
+        <x:v>Die 8 beziehungsweise 9 Stunden sind eine konservativ festgehaltene Assistenz-Baseline – keine langfristige Obergrenze. Leistungsfähigere Modelle, zusätzliche Werkzeuge, bessere Prozessintegration und der Übergang zu agentischen, mehrstufigen Tätigkeiten können den Nutzen künftig weiter erhöhen. Weil dafür noch keine belastbaren, allgemein übertragbaren Benchmarks vorliegen, wird dieses zusätzliche Potenzial nicht in den ROI hineingerechnet. So bleibt der Business Case nachvollziehbar, ohne die technologische Entwicklung kleinzurechnen.</x:v>
+      </x:c>
+      <x:c r="B53" s="59" t="str">
+        <x:v>Die 8 beziehungsweise 9 Stunden sind eine konservativ festgehaltene Assistenz-Baseline – keine langfristige Obergrenze. Leistungsfähigere Modelle, zusätzliche Werkzeuge, bessere Prozessintegration und der Übergang zu agentischen, mehrstufigen Tätigkeiten können den Nutzen künftig weiter erhöhen. Weil dafür noch keine belastbaren, allgemein übertragbaren Benchmarks vorliegen, wird dieses zusätzliche Potenzial nicht in den ROI hineingerechnet. So bleibt der Business Case nachvollziehbar, ohne die technologische Entwicklung kleinzurechnen.</x:v>
+      </x:c>
+      <x:c r="C53" s="59" t="str">
+        <x:v>Die 8 beziehungsweise 9 Stunden sind eine konservativ festgehaltene Assistenz-Baseline – keine langfristige Obergrenze. Leistungsfähigere Modelle, zusätzliche Werkzeuge, bessere Prozessintegration und der Übergang zu agentischen, mehrstufigen Tätigkeiten können den Nutzen künftig weiter erhöhen. Weil dafür noch keine belastbaren, allgemein übertragbaren Benchmarks vorliegen, wird dieses zusätzliche Potenzial nicht in den ROI hineingerechnet. So bleibt der Business Case nachvollziehbar, ohne die technologische Entwicklung kleinzurechnen.</x:v>
+      </x:c>
+      <x:c r="D53" s="59" t="str">
+        <x:v>Die 8 beziehungsweise 9 Stunden sind eine konservativ festgehaltene Assistenz-Baseline – keine langfristige Obergrenze. Leistungsfähigere Modelle, zusätzliche Werkzeuge, bessere Prozessintegration und der Übergang zu agentischen, mehrstufigen Tätigkeiten können den Nutzen künftig weiter erhöhen. Weil dafür noch keine belastbaren, allgemein übertragbaren Benchmarks vorliegen, wird dieses zusätzliche Potenzial nicht in den ROI hineingerechnet. So bleibt der Business Case nachvollziehbar, ohne die technologische Entwicklung kleinzurechnen.</x:v>
+      </x:c>
+      <x:c r="E53" s="59" t="str">
+        <x:v>Die 8 beziehungsweise 9 Stunden sind eine konservativ festgehaltene Assistenz-Baseline – keine langfristige Obergrenze. Leistungsfähigere Modelle, zusätzliche Werkzeuge, bessere Prozessintegration und der Übergang zu agentischen, mehrstufigen Tätigkeiten können den Nutzen künftig weiter erhöhen. Weil dafür noch keine belastbaren, allgemein übertragbaren Benchmarks vorliegen, wird dieses zusätzliche Potenzial nicht in den ROI hineingerechnet. So bleibt der Business Case nachvollziehbar, ohne die technologische Entwicklung kleinzurechnen.</x:v>
+      </x:c>
+      <x:c r="F53" s="59" t="str">
+        <x:v>Die 8 beziehungsweise 9 Stunden sind eine konservativ festgehaltene Assistenz-Baseline – keine langfristige Obergrenze. Leistungsfähigere Modelle, zusätzliche Werkzeuge, bessere Prozessintegration und der Übergang zu agentischen, mehrstufigen Tätigkeiten können den Nutzen künftig weiter erhöhen. Weil dafür noch keine belastbaren, allgemein übertragbaren Benchmarks vorliegen, wird dieses zusätzliche Potenzial nicht in den ROI hineingerechnet. So bleibt der Business Case nachvollziehbar, ohne die technologische Entwicklung kleinzurechnen.</x:v>
+      </x:c>
+      <x:c r="G53" s="59" t="str">
+        <x:v>Die 8 beziehungsweise 9 Stunden sind eine konservativ festgehaltene Assistenz-Baseline – keine langfristige Obergrenze. Leistungsfähigere Modelle, zusätzliche Werkzeuge, bessere Prozessintegration und der Übergang zu agentischen, mehrstufigen Tätigkeiten können den Nutzen künftig weiter erhöhen. Weil dafür noch keine belastbaren, allgemein übertragbaren Benchmarks vorliegen, wird dieses zusätzliche Potenzial nicht in den ROI hineingerechnet. So bleibt der Business Case nachvollziehbar, ohne die technologische Entwicklung kleinzurechnen.</x:v>
+      </x:c>
+      <x:c r="H53" s="64" t="str">
+        <x:v>Die 8 beziehungsweise 9 Stunden sind eine konservativ festgehaltene Assistenz-Baseline – keine langfristige Obergrenze. Leistungsfähigere Modelle, zusätzliche Werkzeuge, bessere Prozessintegration und der Übergang zu agentischen, mehrstufigen Tätigkeiten können den Nutzen künftig weiter erhöhen. Weil dafür noch keine belastbaren, allgemein übertragbaren Benchmarks vorliegen, wird dieses zusätzliche Potenzial nicht in den ROI hineingerechnet. So bleibt der Business Case nachvollziehbar, ohne die technologische Entwicklung kleinzurechnen.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54">
+      <x:c r="A54" s="63" t="str">
+        <x:v>Die 8 beziehungsweise 9 Stunden sind eine konservativ festgehaltene Assistenz-Baseline – keine langfristige Obergrenze. Leistungsfähigere Modelle, zusätzliche Werkzeuge, bessere Prozessintegration und der Übergang zu agentischen, mehrstufigen Tätigkeiten können den Nutzen künftig weiter erhöhen. Weil dafür noch keine belastbaren, allgemein übertragbaren Benchmarks vorliegen, wird dieses zusätzliche Potenzial nicht in den ROI hineingerechnet. So bleibt der Business Case nachvollziehbar, ohne die technologische Entwicklung kleinzurechnen.</x:v>
+      </x:c>
+      <x:c r="B54" s="59" t="str">
+        <x:v>Die 8 beziehungsweise 9 Stunden sind eine konservativ festgehaltene Assistenz-Baseline – keine langfristige Obergrenze. Leistungsfähigere Modelle, zusätzliche Werkzeuge, bessere Prozessintegration und der Übergang zu agentischen, mehrstufigen Tätigkeiten können den Nutzen künftig weiter erhöhen. Weil dafür noch keine belastbaren, allgemein übertragbaren Benchmarks vorliegen, wird dieses zusätzliche Potenzial nicht in den ROI hineingerechnet. So bleibt der Business Case nachvollziehbar, ohne die technologische Entwicklung kleinzurechnen.</x:v>
+      </x:c>
+      <x:c r="C54" s="59" t="str">
+        <x:v>Die 8 beziehungsweise 9 Stunden sind eine konservativ festgehaltene Assistenz-Baseline – keine langfristige Obergrenze. Leistungsfähigere Modelle, zusätzliche Werkzeuge, bessere Prozessintegration und der Übergang zu agentischen, mehrstufigen Tätigkeiten können den Nutzen künftig weiter erhöhen. Weil dafür noch keine belastbaren, allgemein übertragbaren Benchmarks vorliegen, wird dieses zusätzliche Potenzial nicht in den ROI hineingerechnet. So bleibt der Business Case nachvollziehbar, ohne die technologische Entwicklung kleinzurechnen.</x:v>
+      </x:c>
+      <x:c r="D54" s="59" t="str">
+        <x:v>Die 8 beziehungsweise 9 Stunden sind eine konservativ festgehaltene Assistenz-Baseline – keine langfristige Obergrenze. Leistungsfähigere Modelle, zusätzliche Werkzeuge, bessere Prozessintegration und der Übergang zu agentischen, mehrstufigen Tätigkeiten können den Nutzen künftig weiter erhöhen. Weil dafür noch keine belastbaren, allgemein übertragbaren Benchmarks vorliegen, wird dieses zusätzliche Potenzial nicht in den ROI hineingerechnet. So bleibt der Business Case nachvollziehbar, ohne die technologische Entwicklung kleinzurechnen.</x:v>
+      </x:c>
+      <x:c r="E54" s="59" t="str">
+        <x:v>Die 8 beziehungsweise 9 Stunden sind eine konservativ festgehaltene Assistenz-Baseline – keine langfristige Obergrenze. Leistungsfähigere Modelle, zusätzliche Werkzeuge, bessere Prozessintegration und der Übergang zu agentischen, mehrstufigen Tätigkeiten können den Nutzen künftig weiter erhöhen. Weil dafür noch keine belastbaren, allgemein übertragbaren Benchmarks vorliegen, wird dieses zusätzliche Potenzial nicht in den ROI hineingerechnet. So bleibt der Business Case nachvollziehbar, ohne die technologische Entwicklung kleinzurechnen.</x:v>
+      </x:c>
+      <x:c r="F54" s="59" t="str">
+        <x:v>Die 8 beziehungsweise 9 Stunden sind eine konservativ festgehaltene Assistenz-Baseline – keine langfristige Obergrenze. Leistungsfähigere Modelle, zusätzliche Werkzeuge, bessere Prozessintegration und der Übergang zu agentischen, mehrstufigen Tätigkeiten können den Nutzen künftig weiter erhöhen. Weil dafür noch keine belastbaren, allgemein übertragbaren Benchmarks vorliegen, wird dieses zusätzliche Potenzial nicht in den ROI hineingerechnet. So bleibt der Business Case nachvollziehbar, ohne die technologische Entwicklung kleinzurechnen.</x:v>
+      </x:c>
+      <x:c r="G54" s="59" t="str">
+        <x:v>Die 8 beziehungsweise 9 Stunden sind eine konservativ festgehaltene Assistenz-Baseline – keine langfristige Obergrenze. Leistungsfähigere Modelle, zusätzliche Werkzeuge, bessere Prozessintegration und der Übergang zu agentischen, mehrstufigen Tätigkeiten können den Nutzen künftig weiter erhöhen. Weil dafür noch keine belastbaren, allgemein übertragbaren Benchmarks vorliegen, wird dieses zusätzliche Potenzial nicht in den ROI hineingerechnet. So bleibt der Business Case nachvollziehbar, ohne die technologische Entwicklung kleinzurechnen.</x:v>
+      </x:c>
+      <x:c r="H54" s="64" t="str">
+        <x:v>Die 8 beziehungsweise 9 Stunden sind eine konservativ festgehaltene Assistenz-Baseline – keine langfristige Obergrenze. Leistungsfähigere Modelle, zusätzliche Werkzeuge, bessere Prozessintegration und der Übergang zu agentischen, mehrstufigen Tätigkeiten können den Nutzen künftig weiter erhöhen. Weil dafür noch keine belastbaren, allgemein übertragbaren Benchmarks vorliegen, wird dieses zusätzliche Potenzial nicht in den ROI hineingerechnet. So bleibt der Business Case nachvollziehbar, ohne die technologische Entwicklung kleinzurechnen.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55">
+      <x:c r="A55" s="65" t="str">
+        <x:v>Die 8 beziehungsweise 9 Stunden sind eine konservativ festgehaltene Assistenz-Baseline – keine langfristige Obergrenze. Leistungsfähigere Modelle, zusätzliche Werkzeuge, bessere Prozessintegration und der Übergang zu agentischen, mehrstufigen Tätigkeiten können den Nutzen künftig weiter erhöhen. Weil dafür noch keine belastbaren, allgemein übertragbaren Benchmarks vorliegen, wird dieses zusätzliche Potenzial nicht in den ROI hineingerechnet. So bleibt der Business Case nachvollziehbar, ohne die technologische Entwicklung kleinzurechnen.</x:v>
+      </x:c>
+      <x:c r="B55" s="66" t="str">
+        <x:v>Die 8 beziehungsweise 9 Stunden sind eine konservativ festgehaltene Assistenz-Baseline – keine langfristige Obergrenze. Leistungsfähigere Modelle, zusätzliche Werkzeuge, bessere Prozessintegration und der Übergang zu agentischen, mehrstufigen Tätigkeiten können den Nutzen künftig weiter erhöhen. Weil dafür noch keine belastbaren, allgemein übertragbaren Benchmarks vorliegen, wird dieses zusätzliche Potenzial nicht in den ROI hineingerechnet. So bleibt der Business Case nachvollziehbar, ohne die technologische Entwicklung kleinzurechnen.</x:v>
+      </x:c>
+      <x:c r="C55" s="66" t="str">
+        <x:v>Die 8 beziehungsweise 9 Stunden sind eine konservativ festgehaltene Assistenz-Baseline – keine langfristige Obergrenze. Leistungsfähigere Modelle, zusätzliche Werkzeuge, bessere Prozessintegration und der Übergang zu agentischen, mehrstufigen Tätigkeiten können den Nutzen künftig weiter erhöhen. Weil dafür noch keine belastbaren, allgemein übertragbaren Benchmarks vorliegen, wird dieses zusätzliche Potenzial nicht in den ROI hineingerechnet. So bleibt der Business Case nachvollziehbar, ohne die technologische Entwicklung kleinzurechnen.</x:v>
+      </x:c>
+      <x:c r="D55" s="66" t="str">
+        <x:v>Die 8 beziehungsweise 9 Stunden sind eine konservativ festgehaltene Assistenz-Baseline – keine langfristige Obergrenze. Leistungsfähigere Modelle, zusätzliche Werkzeuge, bessere Prozessintegration und der Übergang zu agentischen, mehrstufigen Tätigkeiten können den Nutzen künftig weiter erhöhen. Weil dafür noch keine belastbaren, allgemein übertragbaren Benchmarks vorliegen, wird dieses zusätzliche Potenzial nicht in den ROI hineingerechnet. So bleibt der Business Case nachvollziehbar, ohne die technologische Entwicklung kleinzurechnen.</x:v>
+      </x:c>
+      <x:c r="E55" s="66" t="str">
+        <x:v>Die 8 beziehungsweise 9 Stunden sind eine konservativ festgehaltene Assistenz-Baseline – keine langfristige Obergrenze. Leistungsfähigere Modelle, zusätzliche Werkzeuge, bessere Prozessintegration und der Übergang zu agentischen, mehrstufigen Tätigkeiten können den Nutzen künftig weiter erhöhen. Weil dafür noch keine belastbaren, allgemein übertragbaren Benchmarks vorliegen, wird dieses zusätzliche Potenzial nicht in den ROI hineingerechnet. So bleibt der Business Case nachvollziehbar, ohne die technologische Entwicklung kleinzurechnen.</x:v>
+      </x:c>
+      <x:c r="F55" s="66" t="str">
+        <x:v>Die 8 beziehungsweise 9 Stunden sind eine konservativ festgehaltene Assistenz-Baseline – keine langfristige Obergrenze. Leistungsfähigere Modelle, zusätzliche Werkzeuge, bessere Prozessintegration und der Übergang zu agentischen, mehrstufigen Tätigkeiten können den Nutzen künftig weiter erhöhen. Weil dafür noch keine belastbaren, allgemein übertragbaren Benchmarks vorliegen, wird dieses zusätzliche Potenzial nicht in den ROI hineingerechnet. So bleibt der Business Case nachvollziehbar, ohne die technologische Entwicklung kleinzurechnen.</x:v>
+      </x:c>
+      <x:c r="G55" s="66" t="str">
+        <x:v>Die 8 beziehungsweise 9 Stunden sind eine konservativ festgehaltene Assistenz-Baseline – keine langfristige Obergrenze. Leistungsfähigere Modelle, zusätzliche Werkzeuge, bessere Prozessintegration und der Übergang zu agentischen, mehrstufigen Tätigkeiten können den Nutzen künftig weiter erhöhen. Weil dafür noch keine belastbaren, allgemein übertragbaren Benchmarks vorliegen, wird dieses zusätzliche Potenzial nicht in den ROI hineingerechnet. So bleibt der Business Case nachvollziehbar, ohne die technologische Entwicklung kleinzurechnen.</x:v>
+      </x:c>
+      <x:c r="H55" s="67" t="str">
+        <x:v>Die 8 beziehungsweise 9 Stunden sind eine konservativ festgehaltene Assistenz-Baseline – keine langfristige Obergrenze. Leistungsfähigere Modelle, zusätzliche Werkzeuge, bessere Prozessintegration und der Übergang zu agentischen, mehrstufigen Tätigkeiten können den Nutzen künftig weiter erhöhen. Weil dafür noch keine belastbaren, allgemein übertragbaren Benchmarks vorliegen, wird dieses zusätzliche Potenzial nicht in den ROI hineingerechnet. So bleibt der Business Case nachvollziehbar, ohne die technologische Entwicklung kleinzurechnen.</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:sheetProtection sheet="1" objects="1" scenarios="1" formatCells="1" formatColumns="1" formatRows="1" insertColumns="1" insertRows="1" insertHyperlinks="1" deleteColumns="1" deleteRows="1" sort="1" autoFilter="1" pivotTables="1"/>
@@ -3504,10 +3740,11 @@
     <x:mergeCell ref="A5:F5"/>
     <x:mergeCell ref="A11:H11"/>
     <x:mergeCell ref="A31:H31"/>
-    <x:mergeCell ref="A50:H53"/>
+    <x:mergeCell ref="A50:H50"/>
+    <x:mergeCell ref="A51:H55"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R84216830ec3d4763"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R55c0a7cb74aa4ead"/>
 </x:worksheet>
 </file>
 
@@ -3543,9 +3780,9 @@
         <x:v>PLANUNGSSZENARIEN</x:v>
       </x:c>
     </x:row>
-    <x:row r="3">
-      <x:c r="A3" s="37" t="str">
-        <x:v>Alle geschulten Personen werden berücksichtigt. Die Szenarien unterscheiden sich durch die durchschnittlich erreichte Brutto-Zeitersparnis je Person.</x:v>
+    <x:row r="3" ht="30" customHeight="1">
+      <x:c r="A3" s="38" t="str">
+        <x:v>Alle geschulten Personen werden berücksichtigt. Die modellierte Kurve beschreibt nur den Kompetenzaufbau zur heute belegbaren Assistenz-Nutzung – nicht die langfristige Grenze des KI-Potenzials.</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -3569,24 +3806,24 @@
       </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="38" t="str">
+      <x:c r="A6" s="39" t="str">
         <x:v>Realistisch</x:v>
       </x:c>
-      <x:c r="B6" s="40" t="n">
+      <x:c r="B6" s="41" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C6" s="43" t="n">
+      <x:c r="C6" s="44" t="n">
         <x:f>B6/9</x:f>
         <x:v>0.8888888888888888</x:v>
       </x:c>
-      <x:c r="D6" s="44" t="n">
+      <x:c r="D6" s="45" t="n">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="E6" s="47" t="n">
+      <x:c r="E6" s="48" t="n">
         <x:f>'1. Eingaben'!B8</x:f>
         <x:v>300</x:v>
       </x:c>
-      <x:c r="F6" s="38" t="str">
+      <x:c r="F6" s="39" t="str">
         <x:v>Forrester: typische allgemeine Nutzer sparen etwa 8 Std./Monat</x:v>
       </x:c>
     </x:row>
@@ -3594,17 +3831,17 @@
       <x:c r="A7" s="20" t="str">
         <x:v>Studiennah</x:v>
       </x:c>
-      <x:c r="B7" s="40" t="n">
+      <x:c r="B7" s="41" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="C7" s="43" t="n">
+      <x:c r="C7" s="44" t="n">
         <x:f>B7/9</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D7" s="44" t="n">
+      <x:c r="D7" s="45" t="n">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="E7" s="45" t="n">
+      <x:c r="E7" s="46" t="n">
         <x:f>'1. Eingaben'!B8</x:f>
         <x:v>300</x:v>
       </x:c>
@@ -3652,47 +3889,47 @@
       <x:c r="A13" s="20" t="str">
         <x:v>Startniveau direkt nach Kick-off</x:v>
       </x:c>
-      <x:c r="B13" s="44" t="n">
+      <x:c r="B13" s="45" t="n">
         <x:v>0.6</x:v>
       </x:c>
       <x:c r="C13" s="20" t="str">
         <x:v>% der Ziel-Zeitersparnis</x:v>
       </x:c>
-      <x:c r="D13" s="49" t="str">
+      <x:c r="D13" s="50" t="str">
         <x:v>Sofortiger Kompetenz- und Motivationsimpuls</x:v>
       </x:c>
-      <x:c r="E13" s="49"/>
-      <x:c r="F13" s="49"/>
+      <x:c r="E13" s="50"/>
+      <x:c r="F13" s="50"/>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="20" t="str">
         <x:v>Halbwertszeit der verbleibenden Lücke</x:v>
       </x:c>
-      <x:c r="B14" s="48" t="n">
+      <x:c r="B14" s="49" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="C14" s="20" t="str">
         <x:v>Monate</x:v>
       </x:c>
-      <x:c r="D14" s="49" t="str">
+      <x:c r="D14" s="50" t="str">
         <x:v>Alle 2 Monate halbiert sich die noch offene Lücke zur Ziel-Zeitersparnis</x:v>
       </x:c>
-      <x:c r="E14" s="49"/>
-      <x:c r="F14" s="49"/>
+      <x:c r="E14" s="50"/>
+      <x:c r="F14" s="50"/>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="20" t="str">
         <x:v>Kurvenform</x:v>
       </x:c>
       <x:c r="B15" s="20" t="str">
-        <x:v>Sättigungskurve</x:v>
+        <x:v>Ramp-up zur Assistenz-Baseline</x:v>
       </x:c>
       <x:c r="C15" s="20" t="str"/>
-      <x:c r="D15" s="49" t="str">
-        <x:v>Schneller Start, danach abnehmende Zuwächse</x:v>
-      </x:c>
-      <x:c r="E15" s="49"/>
-      <x:c r="F15" s="49"/>
+      <x:c r="D15" s="50" t="str">
+        <x:v>Schneller Kompetenzaufbau; keine Aussage über das langfristige Gesamtpotenzial</x:v>
+      </x:c>
+      <x:c r="E15" s="50"/>
+      <x:c r="F15" s="50"/>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="20" t="str">
@@ -3702,35 +3939,44 @@
         <x:v>Ca. 12 Wochen bis Vertrautheit/Kompetenz</x:v>
       </x:c>
       <x:c r="C16" s="20" t="str"/>
-      <x:c r="D16" s="49" t="str">
+      <x:c r="D16" s="50" t="str">
         <x:v>Forrester-Interviews; genaue Kurve ist eine Modellannahme</x:v>
       </x:c>
-      <x:c r="E16" s="49"/>
-      <x:c r="F16" s="49"/>
+      <x:c r="E16" s="50"/>
+      <x:c r="F16" s="50"/>
     </x:row>
     <x:row r="17">
-      <x:c r="A17" s="52" t="str">
+      <x:c r="A17" s="53" t="str">
         <x:v>Wichtig</x:v>
       </x:c>
-      <x:c r="B17" s="52" t="str">
+      <x:c r="B17" s="53" t="str">
         <x:v>Alle geschulten Personen zählen</x:v>
       </x:c>
-      <x:c r="C17" s="52" t="str"/>
-      <x:c r="D17" s="53" t="str">
+      <x:c r="C17" s="53" t="str"/>
+      <x:c r="D17" s="54" t="str">
         <x:v>Die Zeitersparnis gilt je Person – sie ist keine Quote aktiver Personen.</x:v>
       </x:c>
-      <x:c r="E17" s="53"/>
-      <x:c r="F17" s="53"/>
+      <x:c r="E17" s="54"/>
+      <x:c r="F17" s="54"/>
     </x:row>
     <x:row r="20" ht="22" customHeight="1">
       <x:c r="A20" s="12" t="str">
-        <x:v>ENTWICKLUNG DER BRUTTO-ZEITERSPARNIS JE PERSON</x:v>
+        <x:v>KOMPETENZAUFBAU ZUR HEUTIGEN ASSISTENZ-BASELINE</x:v>
       </x:c>
       <x:c r="B20" s="13" t="str">
-        <x:v>ENTWICKLUNG DER BRUTTO-ZEITERSPARNIS JE PERSON</x:v>
+        <x:v>KOMPETENZAUFBAU ZUR HEUTIGEN ASSISTENZ-BASELINE</x:v>
       </x:c>
       <x:c r="C20" s="14" t="str">
-        <x:v>ENTWICKLUNG DER BRUTTO-ZEITERSPARNIS JE PERSON</x:v>
+        <x:v>KOMPETENZAUFBAU ZUR HEUTIGEN ASSISTENZ-BASELINE</x:v>
+      </x:c>
+      <x:c r="D20" s="12" t="str">
+        <x:v>WARUM DAS POTENZIAL DANACH WEITER STEIGEN KANN</x:v>
+      </x:c>
+      <x:c r="E20" s="13" t="str">
+        <x:v>WARUM DAS POTENZIAL DANACH WEITER STEIGEN KANN</x:v>
+      </x:c>
+      <x:c r="F20" s="14" t="str">
+        <x:v>WARUM DAS POTENZIAL DANACH WEITER STEIGEN KANN</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -3743,42 +3989,69 @@
       <x:c r="C21" s="18" t="str">
         <x:v>Studiennah</x:v>
       </x:c>
+      <x:c r="D21" s="29" t="str">
+        <x:v>Die Baseline bildet heute belegbare Assistenz-Nutzung ab: Schreiben, Zusammenfassen, Analysieren, Recherchieren und Vorbereiten. Der Kompetenzaufbau zu diesem Niveau wird vorsichtig modelliert.</x:v>
+      </x:c>
+      <x:c r="E21" s="30" t="str">
+        <x:v>Die Baseline bildet heute belegbare Assistenz-Nutzung ab: Schreiben, Zusammenfassen, Analysieren, Recherchieren und Vorbereiten. Der Kompetenzaufbau zu diesem Niveau wird vorsichtig modelliert.</x:v>
+      </x:c>
+      <x:c r="F21" s="31" t="str">
+        <x:v>Die Baseline bildet heute belegbare Assistenz-Nutzung ab: Schreiben, Zusammenfassen, Analysieren, Recherchieren und Vorbereiten. Der Kompetenzaufbau zu diesem Niveau wird vorsichtig modelliert.</x:v>
+      </x:c>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="20" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="B22" s="54" t="n">
+      <x:c r="B22" s="55" t="n">
         <x:f>'5. Berechnung'!I26</x:f>
         <x:v>4.8</x:v>
       </x:c>
-      <x:c r="C22" s="54" t="n">
+      <x:c r="C22" s="55" t="n">
         <x:f>'5. Berechnung'!J26</x:f>
         <x:v>5.3999999999999995</x:v>
+      </x:c>
+      <x:c r="D22" s="32" t="str">
+        <x:v>Die Baseline bildet heute belegbare Assistenz-Nutzung ab: Schreiben, Zusammenfassen, Analysieren, Recherchieren und Vorbereiten. Der Kompetenzaufbau zu diesem Niveau wird vorsichtig modelliert.</x:v>
+      </x:c>
+      <x:c r="E22" s="28" t="str">
+        <x:v>Die Baseline bildet heute belegbare Assistenz-Nutzung ab: Schreiben, Zusammenfassen, Analysieren, Recherchieren und Vorbereiten. Der Kompetenzaufbau zu diesem Niveau wird vorsichtig modelliert.</x:v>
+      </x:c>
+      <x:c r="F22" s="33" t="str">
+        <x:v>Die Baseline bildet heute belegbare Assistenz-Nutzung ab: Schreiben, Zusammenfassen, Analysieren, Recherchieren und Vorbereiten. Der Kompetenzaufbau zu diesem Niveau wird vorsichtig modelliert.</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="20" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="B23" s="54" t="n">
+      <x:c r="B23" s="55" t="n">
         <x:f>'5. Berechnung'!I28</x:f>
         <x:v>6.4</x:v>
       </x:c>
-      <x:c r="C23" s="54" t="n">
+      <x:c r="C23" s="55" t="n">
         <x:f>'5. Berechnung'!J28</x:f>
         <x:v>7.2</x:v>
+      </x:c>
+      <x:c r="D23" s="34" t="str">
+        <x:v>Die Baseline bildet heute belegbare Assistenz-Nutzung ab: Schreiben, Zusammenfassen, Analysieren, Recherchieren und Vorbereiten. Der Kompetenzaufbau zu diesem Niveau wird vorsichtig modelliert.</x:v>
+      </x:c>
+      <x:c r="E23" s="35" t="str">
+        <x:v>Die Baseline bildet heute belegbare Assistenz-Nutzung ab: Schreiben, Zusammenfassen, Analysieren, Recherchieren und Vorbereiten. Der Kompetenzaufbau zu diesem Niveau wird vorsichtig modelliert.</x:v>
+      </x:c>
+      <x:c r="F23" s="36" t="str">
+        <x:v>Die Baseline bildet heute belegbare Assistenz-Nutzung ab: Schreiben, Zusammenfassen, Analysieren, Recherchieren und Vorbereiten. Der Kompetenzaufbau zu diesem Niveau wird vorsichtig modelliert.</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="20" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="B24" s="54" t="n">
+      <x:c r="B24" s="55" t="n">
         <x:f>'5. Berechnung'!I31</x:f>
         <x:v>7.434314575050762</x:v>
       </x:c>
-      <x:c r="C24" s="54" t="n">
+      <x:c r="C24" s="55" t="n">
         <x:f>'5. Berechnung'!J31</x:f>
         <x:v>8.363603896932107</x:v>
       </x:c>
@@ -3787,39 +4060,66 @@
       <x:c r="A25" s="20" t="n">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="B25" s="54" t="n">
+      <x:c r="B25" s="55" t="n">
         <x:f>'5. Berechnung'!I37</x:f>
         <x:v>7.929289321881345</x:v>
       </x:c>
-      <x:c r="C25" s="54" t="n">
+      <x:c r="C25" s="55" t="n">
         <x:f>'5. Berechnung'!J37</x:f>
         <x:v>8.920450487116513</x:v>
+      </x:c>
+      <x:c r="D25" s="60" t="str">
+        <x:v>Nicht eingepreist sind leistungsfähigere Modelle, neue Funktionen und Tools, tiefere Prozessintegration sowie agentische, mehrstufige Arbeitsabläufe. Diese können die Zeitersparnis später zusätzlich erhöhen, sind heute aber noch nicht belastbar genug für eine feste Formel.</x:v>
+      </x:c>
+      <x:c r="E25" s="61" t="str">
+        <x:v>Nicht eingepreist sind leistungsfähigere Modelle, neue Funktionen und Tools, tiefere Prozessintegration sowie agentische, mehrstufige Arbeitsabläufe. Diese können die Zeitersparnis später zusätzlich erhöhen, sind heute aber noch nicht belastbar genug für eine feste Formel.</x:v>
+      </x:c>
+      <x:c r="F25" s="62" t="str">
+        <x:v>Nicht eingepreist sind leistungsfähigere Modelle, neue Funktionen und Tools, tiefere Prozessintegration sowie agentische, mehrstufige Arbeitsabläufe. Diese können die Zeitersparnis später zusätzlich erhöhen, sind heute aber noch nicht belastbar genug für eine feste Formel.</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="20" t="n">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="B26" s="54" t="n">
+      <x:c r="B26" s="55" t="n">
         <x:f>'5. Berechnung'!I49</x:f>
         <x:v>7.998895145654396</x:v>
       </x:c>
-      <x:c r="C26" s="54" t="n">
+      <x:c r="C26" s="55" t="n">
         <x:f>'5. Berechnung'!J49</x:f>
         <x:v>8.998757038861196</x:v>
+      </x:c>
+      <x:c r="D26" s="63" t="str">
+        <x:v>Nicht eingepreist sind leistungsfähigere Modelle, neue Funktionen und Tools, tiefere Prozessintegration sowie agentische, mehrstufige Arbeitsabläufe. Diese können die Zeitersparnis später zusätzlich erhöhen, sind heute aber noch nicht belastbar genug für eine feste Formel.</x:v>
+      </x:c>
+      <x:c r="E26" s="59" t="str">
+        <x:v>Nicht eingepreist sind leistungsfähigere Modelle, neue Funktionen und Tools, tiefere Prozessintegration sowie agentische, mehrstufige Arbeitsabläufe. Diese können die Zeitersparnis später zusätzlich erhöhen, sind heute aber noch nicht belastbar genug für eine feste Formel.</x:v>
+      </x:c>
+      <x:c r="F26" s="64" t="str">
+        <x:v>Nicht eingepreist sind leistungsfähigere Modelle, neue Funktionen und Tools, tiefere Prozessintegration sowie agentische, mehrstufige Arbeitsabläufe. Diese können die Zeitersparnis später zusätzlich erhöhen, sind heute aber noch nicht belastbar genug für eine feste Formel.</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="20" t="n">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="B27" s="54" t="n">
+      <x:c r="B27" s="55" t="n">
         <x:f>'5. Berechnung'!I61</x:f>
         <x:v>7.99998273665085</x:v>
       </x:c>
-      <x:c r="C27" s="54" t="n">
+      <x:c r="C27" s="55" t="n">
         <x:f>'5. Berechnung'!J61</x:f>
         <x:v>8.999980578732206</x:v>
+      </x:c>
+      <x:c r="D27" s="65" t="str">
+        <x:v>Nicht eingepreist sind leistungsfähigere Modelle, neue Funktionen und Tools, tiefere Prozessintegration sowie agentische, mehrstufige Arbeitsabläufe. Diese können die Zeitersparnis später zusätzlich erhöhen, sind heute aber noch nicht belastbar genug für eine feste Formel.</x:v>
+      </x:c>
+      <x:c r="E27" s="66" t="str">
+        <x:v>Nicht eingepreist sind leistungsfähigere Modelle, neue Funktionen und Tools, tiefere Prozessintegration sowie agentische, mehrstufige Arbeitsabläufe. Diese können die Zeitersparnis später zusätzlich erhöhen, sind heute aber noch nicht belastbar genug für eine feste Formel.</x:v>
+      </x:c>
+      <x:c r="F27" s="67" t="str">
+        <x:v>Nicht eingepreist sind leistungsfähigere Modelle, neue Funktionen und Tools, tiefere Prozessintegration sowie agentische, mehrstufige Arbeitsabläufe. Diese können die Zeitersparnis später zusätzlich erhöhen, sind heute aber noch nicht belastbar genug für eine feste Formel.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3834,6 +4134,9 @@
     <x:mergeCell ref="D16:F16"/>
     <x:mergeCell ref="D17:F17"/>
     <x:mergeCell ref="A20:C20"/>
+    <x:mergeCell ref="D20:F20"/>
+    <x:mergeCell ref="D21:F23"/>
+    <x:mergeCell ref="D25:F27"/>
   </x:mergeCells>
   <x:dataValidations count="4">
     <x:dataValidation type="decimal" operator="between" sqref="B6:B7">
@@ -3854,7 +4157,6 @@
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R048d6b7516f74969"/>
 </x:worksheet>
 </file>
 
@@ -3945,11 +4247,11 @@
       <x:c r="A4" s="20" t="str">
         <x:v>Ziel-Zeitersparnis je Person / Monat</x:v>
       </x:c>
-      <x:c r="B4" s="63" t="n">
+      <x:c r="B4" s="76" t="n">
         <x:f>'4. Szenarien'!B6</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C4" s="54" t="n">
+      <x:c r="C4" s="55" t="n">
         <x:f>'4. Szenarien'!B7</x:f>
         <x:v>9</x:v>
       </x:c>
@@ -3958,11 +4260,11 @@
       <x:c r="A5" s="20" t="str">
         <x:v>Ø Brutto-Zeitersparnis Jahr 1 / Monat</x:v>
       </x:c>
-      <x:c r="B5" s="63" t="n">
+      <x:c r="B5" s="76" t="n">
         <x:f>AVERAGE(I26:I37)</x:f>
         <x:v>7.103768939877063</x:v>
       </x:c>
-      <x:c r="C5" s="54" t="n">
+      <x:c r="C5" s="55" t="n">
         <x:f>AVERAGE(J26:J37)</x:f>
         <x:v>7.991740057361695</x:v>
       </x:c>
@@ -3971,11 +4273,11 @@
       <x:c r="A6" s="20" t="str">
         <x:v>Ø Brutto-Zeitersparnis Jahr 2 / Monat</x:v>
       </x:c>
-      <x:c r="B6" s="63" t="n">
+      <x:c r="B6" s="76" t="n">
         <x:f>AVERAGE(I38:I49)</x:f>
         <x:v>7.985996389685579</x:v>
       </x:c>
-      <x:c r="C6" s="54" t="n">
+      <x:c r="C6" s="55" t="n">
         <x:f>AVERAGE(J38:J49)</x:f>
         <x:v>8.984245938396276</x:v>
       </x:c>
@@ -3984,11 +4286,11 @@
       <x:c r="A7" s="20" t="str">
         <x:v>Ø Brutto-Zeitersparnis Jahr 3 / Monat</x:v>
       </x:c>
-      <x:c r="B7" s="63" t="n">
+      <x:c r="B7" s="76" t="n">
         <x:f>AVERAGE(I50:I61)</x:f>
         <x:v>7.999781193588838</x:v>
       </x:c>
-      <x:c r="C7" s="54" t="n">
+      <x:c r="C7" s="55" t="n">
         <x:f>AVERAGE(J50:J61)</x:f>
         <x:v>8.999753842787444</x:v>
       </x:c>
@@ -3997,11 +4299,11 @@
       <x:c r="A8" s="20" t="str">
         <x:v>Realisierter Nutzen 3 Jahre</x:v>
       </x:c>
-      <x:c r="B8" s="64" t="n">
+      <x:c r="B8" s="77" t="n">
         <x:f>SUM(K26:K61)</x:f>
         <x:v>2078059.1870836332</x:v>
       </x:c>
-      <x:c r="C8" s="55" t="n">
+      <x:c r="C8" s="68" t="n">
         <x:f>SUM(L26:L61)</x:f>
         <x:v>2337816.585469087</x:v>
       </x:c>
@@ -4010,11 +4312,11 @@
       <x:c r="A9" s="20" t="str">
         <x:v>Gesamtkosten 3 Jahre</x:v>
       </x:c>
-      <x:c r="B9" s="64" t="n">
+      <x:c r="B9" s="77" t="n">
         <x:f>SUM(H26:H61)</x:f>
         <x:v>624736</x:v>
       </x:c>
-      <x:c r="C9" s="55" t="n">
+      <x:c r="C9" s="68" t="n">
         <x:f>SUM(H26:H61)</x:f>
         <x:v>624736</x:v>
       </x:c>
@@ -4023,11 +4325,11 @@
       <x:c r="A10" s="20" t="str">
         <x:v>Netto-Nutzen 3 Jahre</x:v>
       </x:c>
-      <x:c r="B10" s="64" t="n">
+      <x:c r="B10" s="77" t="n">
         <x:f>B8-B9</x:f>
         <x:v>1453323.1870836332</x:v>
       </x:c>
-      <x:c r="C10" s="55" t="n">
+      <x:c r="C10" s="68" t="n">
         <x:f>C8-C9</x:f>
         <x:v>1713080.5854690871</x:v>
       </x:c>
@@ -4036,11 +4338,11 @@
       <x:c r="A11" s="20" t="str">
         <x:v>ROI 3 Jahre</x:v>
       </x:c>
-      <x:c r="B11" s="44" t="n">
+      <x:c r="B11" s="45" t="n">
         <x:f>IF(B9=0,0,B10/B9)</x:f>
         <x:v>2.3262997283390634</x:v>
       </x:c>
-      <x:c r="C11" s="57" t="n">
+      <x:c r="C11" s="70" t="n">
         <x:f>IF(C9=0,0,C10/C9)</x:f>
         <x:v>2.742087194381446</x:v>
       </x:c>
@@ -4049,11 +4351,11 @@
       <x:c r="A12" s="20" t="str">
         <x:v>Break-even</x:v>
       </x:c>
-      <x:c r="B12" s="65" t="n">
+      <x:c r="B12" s="78" t="n">
         <x:f>IF(MIN(O26:O61)=99,"&gt; 36 Monate",MIN(O26:O61))</x:f>
         <x:v>5</x:v>
       </x:c>
-      <x:c r="C12" s="58" t="n">
+      <x:c r="C12" s="71" t="n">
         <x:f>IF(MIN(P26:P61)=99,"&gt; 36 Monate",MIN(P26:P61))</x:f>
         <x:v>5</x:v>
       </x:c>
@@ -4062,11 +4364,11 @@
       <x:c r="A13" s="20" t="str">
         <x:v>Kosten pro Nutzer / 3 Jahre</x:v>
       </x:c>
-      <x:c r="B13" s="64" t="n">
+      <x:c r="B13" s="77" t="n">
         <x:f>IF('1. Eingaben'!B8=0,0,B9/'1. Eingaben'!B8)</x:f>
         <x:v>2082.4533333333334</x:v>
       </x:c>
-      <x:c r="C13" s="55" t="n">
+      <x:c r="C13" s="68" t="n">
         <x:f>IF('1. Eingaben'!B8=0,0,C9/'1. Eingaben'!B8)</x:f>
         <x:v>2082.4533333333334</x:v>
       </x:c>
@@ -4075,11 +4377,11 @@
       <x:c r="A14" s="20" t="str">
         <x:v>Realisierter Nutzen pro Nutzer / 3 Jahre</x:v>
       </x:c>
-      <x:c r="B14" s="64" t="n">
+      <x:c r="B14" s="77" t="n">
         <x:f>IF('1. Eingaben'!B8=0,0,B8/'1. Eingaben'!B8)</x:f>
         <x:v>6926.8639569454435</x:v>
       </x:c>
-      <x:c r="C14" s="55" t="n">
+      <x:c r="C14" s="68" t="n">
         <x:f>IF('1. Eingaben'!B8=0,0,C8/'1. Eingaben'!B8)</x:f>
         <x:v>7792.721951563623</x:v>
       </x:c>
@@ -4140,31 +4442,31 @@
       <x:c r="A19" s="20" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="B19" s="55" t="n">
+      <x:c r="B19" s="68" t="n">
         <x:f>SUMIF($B$26:$B$61,A19,$K$26:$K$61)</x:f>
         <x:v>639339.2045889356</x:v>
       </x:c>
-      <x:c r="C19" s="55" t="n">
+      <x:c r="C19" s="68" t="n">
         <x:f>SUMIF($B$26:$B$61,A19,$D$26:$D$61)</x:f>
         <x:v>93600</x:v>
       </x:c>
-      <x:c r="D19" s="55" t="n">
+      <x:c r="D19" s="68" t="n">
         <x:f>SUMIF($B$26:$B$61,A19,$E$26:$E$61)</x:f>
         <x:v>125000</x:v>
       </x:c>
-      <x:c r="E19" s="55" t="n">
+      <x:c r="E19" s="68" t="n">
         <x:f>SUMIF($B$26:$B$61,A19,$F$26:$F$61)</x:f>
         <x:v>27000</x:v>
       </x:c>
-      <x:c r="F19" s="55" t="n">
+      <x:c r="F19" s="68" t="n">
         <x:f>SUMIF($B$26:$B$61,A19,$G$26:$G$61)</x:f>
         <x:v>29472</x:v>
       </x:c>
-      <x:c r="G19" s="55" t="n">
+      <x:c r="G19" s="68" t="n">
         <x:f>SUMIF($B$26:$B$61,A19,$H$26:$H$61)</x:f>
         <x:v>275072</x:v>
       </x:c>
-      <x:c r="H19" s="55" t="n">
+      <x:c r="H19" s="68" t="n">
         <x:f>B19-G19</x:f>
         <x:v>364267.2045889356</x:v>
       </x:c>
@@ -4173,31 +4475,31 @@
       <x:c r="A20" s="20" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="B20" s="55" t="n">
+      <x:c r="B20" s="68" t="n">
         <x:f>SUMIF($B$26:$B$61,A20,$K$26:$K$61)</x:f>
         <x:v>718739.6750717022</x:v>
       </x:c>
-      <x:c r="C20" s="55" t="n">
+      <x:c r="C20" s="68" t="n">
         <x:f>SUMIF($B$26:$B$61,A20,$D$26:$D$61)</x:f>
         <x:v>93600</x:v>
       </x:c>
-      <x:c r="D20" s="55" t="n">
+      <x:c r="D20" s="68" t="n">
         <x:f>SUMIF($B$26:$B$61,A20,$E$26:$E$61)</x:f>
         <x:v>62500</x:v>
       </x:c>
-      <x:c r="E20" s="55" t="n">
+      <x:c r="E20" s="68" t="n">
         <x:f>SUMIF($B$26:$B$61,A20,$F$26:$F$61)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F20" s="55" t="n">
+      <x:c r="F20" s="68" t="n">
         <x:f>SUMIF($B$26:$B$61,A20,$G$26:$G$61)</x:f>
         <x:v>18732</x:v>
       </x:c>
-      <x:c r="G20" s="55" t="n">
+      <x:c r="G20" s="68" t="n">
         <x:f>SUMIF($B$26:$B$61,A20,$H$26:$H$61)</x:f>
         <x:v>174832</x:v>
       </x:c>
-      <x:c r="H20" s="55" t="n">
+      <x:c r="H20" s="68" t="n">
         <x:f>B20-G20</x:f>
         <x:v>543907.6750717022</x:v>
       </x:c>
@@ -4206,31 +4508,31 @@
       <x:c r="A21" s="20" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="B21" s="55" t="n">
+      <x:c r="B21" s="68" t="n">
         <x:f>SUMIF($B$26:$B$61,A21,$K$26:$K$61)</x:f>
         <x:v>719980.3074229953</x:v>
       </x:c>
-      <x:c r="C21" s="55" t="n">
+      <x:c r="C21" s="68" t="n">
         <x:f>SUMIF($B$26:$B$61,A21,$D$26:$D$61)</x:f>
         <x:v>93600</x:v>
       </x:c>
-      <x:c r="D21" s="55" t="n">
+      <x:c r="D21" s="68" t="n">
         <x:f>SUMIF($B$26:$B$61,A21,$E$26:$E$61)</x:f>
         <x:v>62500</x:v>
       </x:c>
-      <x:c r="E21" s="55" t="n">
+      <x:c r="E21" s="68" t="n">
         <x:f>SUMIF($B$26:$B$61,A21,$F$26:$F$61)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F21" s="55" t="n">
+      <x:c r="F21" s="68" t="n">
         <x:f>SUMIF($B$26:$B$61,A21,$G$26:$G$61)</x:f>
         <x:v>18732</x:v>
       </x:c>
-      <x:c r="G21" s="55" t="n">
+      <x:c r="G21" s="68" t="n">
         <x:f>SUMIF($B$26:$B$61,A21,$H$26:$H$61)</x:f>
         <x:v>174832</x:v>
       </x:c>
-      <x:c r="H21" s="55" t="n">
+      <x:c r="H21" s="68" t="n">
         <x:f>B21-G21</x:f>
         <x:v>545148.3074229953</x:v>
       </x:c>
@@ -4324,2341 +4626,2341 @@
       </x:c>
     </x:row>
     <x:row r="26">
-      <x:c r="A26" s="66" t="n">
+      <x:c r="A26" s="79" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="B26" s="66" t="n">
+      <x:c r="B26" s="79" t="n">
         <x:f>INT((A26-1)/12)+1</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C26" s="66" t="n">
+      <x:c r="C26" s="79" t="n">
         <x:f>'1. Eingaben'!B8</x:f>
         <x:v>300</x:v>
       </x:c>
-      <x:c r="D26" s="55" t="n">
+      <x:c r="D26" s="68" t="n">
         <x:f>C26*'1. Eingaben'!B10</x:f>
         <x:v>7800</x:v>
       </x:c>
-      <x:c r="E26" s="55" t="n">
+      <x:c r="E26" s="68" t="n">
         <x:f>IF(A26=1,INT(('1. Eingaben'!B8+'6. Quellen &amp; Methodik'!B33-1)/'6. Quellen &amp; Methodik'!B33)*('6. Quellen &amp; Methodik'!B31+'6. Quellen &amp; Methodik'!B32*'6. Quellen &amp; Methodik'!B35),IF(OR(A26=13,A26=25),INT(('1. Eingaben'!B8+'6. Quellen &amp; Methodik'!B33-1)/'6. Quellen &amp; Methodik'!B33)*('6. Quellen &amp; Methodik'!B31+'6. Quellen &amp; Methodik'!B32*'6. Quellen &amp; Methodik'!B35)*'6. Quellen &amp; Methodik'!B34,0))</x:f>
         <x:v>125000</x:v>
       </x:c>
-      <x:c r="F26" s="55" t="n">
+      <x:c r="F26" s="68" t="n">
         <x:f>IF(A26=1,'6. Quellen &amp; Methodik'!B16+MIN(C26,50)*'6. Quellen &amp; Methodik'!B17+MAX(MIN(C26-50,200),0)*'6. Quellen &amp; Methodik'!B18+MAX(MIN(C26-250,750),0)*'6. Quellen &amp; Methodik'!B19+MAX(C26-1000,0)*'6. Quellen &amp; Methodik'!B20,0)</x:f>
         <x:v>27000</x:v>
       </x:c>
-      <x:c r="G26" s="55" t="n">
+      <x:c r="G26" s="68" t="n">
         <x:f>IF(OR(A26=1,A26=13,A26=25),'6. Quellen &amp; Methodik'!B36*(C26*'1. Eingaben'!B10*12+E26+F26),0)</x:f>
         <x:v>29472</x:v>
       </x:c>
-      <x:c r="H26" s="55" t="n">
+      <x:c r="H26" s="68" t="n">
         <x:f>SUM(D26:G26)</x:f>
         <x:v>189272</x:v>
       </x:c>
-      <x:c r="I26" s="54" t="n">
+      <x:c r="I26" s="55" t="n">
         <x:f>'4. Szenarien'!B6*(1-(1-'4. Szenarien'!B13)*POWER(0.5,(A26-1)/'4. Szenarien'!B14))</x:f>
         <x:v>4.8</x:v>
       </x:c>
-      <x:c r="J26" s="54" t="n">
+      <x:c r="J26" s="55" t="n">
         <x:f>'4. Szenarien'!B7*(1-(1-'4. Szenarien'!B13)*POWER(0.5,(A26-1)/'4. Szenarien'!B14))</x:f>
         <x:v>5.3999999999999995</x:v>
       </x:c>
-      <x:c r="K26" s="55" t="n">
+      <x:c r="K26" s="68" t="n">
         <x:f>C26*I26*'4. Szenarien'!D6*'1. Eingaben'!B9</x:f>
         <x:v>36000</x:v>
       </x:c>
-      <x:c r="L26" s="55" t="n">
+      <x:c r="L26" s="68" t="n">
         <x:f>C26*J26*'4. Szenarien'!D7*'1. Eingaben'!B9</x:f>
         <x:v>40499.99999999999</x:v>
       </x:c>
-      <x:c r="M26" s="55" t="n">
+      <x:c r="M26" s="68" t="n">
         <x:f>K26-H26</x:f>
         <x:v>-153272</x:v>
       </x:c>
-      <x:c r="N26" s="55" t="n">
+      <x:c r="N26" s="68" t="n">
         <x:f>L26-H26</x:f>
         <x:v>-148772</x:v>
       </x:c>
-      <x:c r="O26" s="68" t="n">
+      <x:c r="O26" s="81" t="n">
         <x:f>IF(M26&gt;=0,A26,99)</x:f>
         <x:v>99</x:v>
       </x:c>
-      <x:c r="P26" s="68" t="n">
+      <x:c r="P26" s="81" t="n">
         <x:f>IF(N26&gt;=0,A26,99)</x:f>
         <x:v>99</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
-      <x:c r="A27" s="66" t="n">
+      <x:c r="A27" s="79" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="B27" s="66" t="n">
+      <x:c r="B27" s="79" t="n">
         <x:f>INT((A27-1)/12)+1</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C27" s="66" t="n">
+      <x:c r="C27" s="79" t="n">
         <x:f>'1. Eingaben'!B8</x:f>
         <x:v>300</x:v>
       </x:c>
-      <x:c r="D27" s="55" t="n">
+      <x:c r="D27" s="68" t="n">
         <x:f>C27*'1. Eingaben'!B10</x:f>
         <x:v>7800</x:v>
       </x:c>
-      <x:c r="E27" s="55" t="n">
+      <x:c r="E27" s="68" t="n">
         <x:f>IF(A27=1,INT(('1. Eingaben'!B8+'6. Quellen &amp; Methodik'!B33-1)/'6. Quellen &amp; Methodik'!B33)*('6. Quellen &amp; Methodik'!B31+'6. Quellen &amp; Methodik'!B32*'6. Quellen &amp; Methodik'!B35),IF(OR(A27=13,A27=25),INT(('1. Eingaben'!B8+'6. Quellen &amp; Methodik'!B33-1)/'6. Quellen &amp; Methodik'!B33)*('6. Quellen &amp; Methodik'!B31+'6. Quellen &amp; Methodik'!B32*'6. Quellen &amp; Methodik'!B35)*'6. Quellen &amp; Methodik'!B34,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F27" s="55" t="n">
+      <x:c r="F27" s="68" t="n">
         <x:f>IF(A27=1,'6. Quellen &amp; Methodik'!B16+MIN(C27,50)*'6. Quellen &amp; Methodik'!B17+MAX(MIN(C27-50,200),0)*'6. Quellen &amp; Methodik'!B18+MAX(MIN(C27-250,750),0)*'6. Quellen &amp; Methodik'!B19+MAX(C27-1000,0)*'6. Quellen &amp; Methodik'!B20,0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G27" s="55" t="n">
+      <x:c r="G27" s="68" t="n">
         <x:f>IF(OR(A27=1,A27=13,A27=25),'6. Quellen &amp; Methodik'!B36*(C27*'1. Eingaben'!B10*12+E27+F27),0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H27" s="55" t="n">
+      <x:c r="H27" s="68" t="n">
         <x:f>SUM(D27:G27)</x:f>
         <x:v>7800</x:v>
       </x:c>
-      <x:c r="I27" s="54" t="n">
+      <x:c r="I27" s="55" t="n">
         <x:f>'4. Szenarien'!B6*(1-(1-'4. Szenarien'!B13)*POWER(0.5,(A27-1)/'4. Szenarien'!B14))</x:f>
         <x:v>5.737258300203047</x:v>
       </x:c>
-      <x:c r="J27" s="54" t="n">
+      <x:c r="J27" s="55" t="n">
         <x:f>'4. Szenarien'!B7*(1-(1-'4. Szenarien'!B13)*POWER(0.5,(A27-1)/'4. Szenarien'!B14))</x:f>
         <x:v>6.454415587728428</x:v>
       </x:c>
-      <x:c r="K27" s="55" t="n">
+      <x:c r="K27" s="68" t="n">
         <x:f>C27*I27*'4. Szenarien'!D6*'1. Eingaben'!B9</x:f>
         <x:v>43029.43725152285</x:v>
       </x:c>
-      <x:c r="L27" s="55" t="n">
+      <x:c r="L27" s="68" t="n">
         <x:f>C27*J27*'4. Szenarien'!D7*'1. Eingaben'!B9</x:f>
         <x:v>48408.11690796321</x:v>
       </x:c>
-      <x:c r="M27" s="55" t="n">
+      <x:c r="M27" s="68" t="n">
         <x:f>M26+K27-H27</x:f>
         <x:v>-118042.56274847715</x:v>
       </x:c>
-      <x:c r="N27" s="55" t="n">
+      <x:c r="N27" s="68" t="n">
         <x:f>N26+L27-H27</x:f>
         <x:v>-108163.88309203679</x:v>
       </x:c>
-      <x:c r="O27" s="68" t="n">
+      <x:c r="O27" s="81" t="n">
         <x:f>IF(M27&gt;=0,A27,99)</x:f>
         <x:v>99</x:v>
       </x:c>
-      <x:c r="P27" s="68" t="n">
+      <x:c r="P27" s="81" t="n">
         <x:f>IF(N27&gt;=0,A27,99)</x:f>
         <x:v>99</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
-      <x:c r="A28" s="66" t="n">
+      <x:c r="A28" s="79" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="B28" s="66" t="n">
+      <x:c r="B28" s="79" t="n">
         <x:f>INT((A28-1)/12)+1</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C28" s="66" t="n">
+      <x:c r="C28" s="79" t="n">
         <x:f>'1. Eingaben'!B8</x:f>
         <x:v>300</x:v>
       </x:c>
-      <x:c r="D28" s="55" t="n">
+      <x:c r="D28" s="68" t="n">
         <x:f>C28*'1. Eingaben'!B10</x:f>
         <x:v>7800</x:v>
       </x:c>
-      <x:c r="E28" s="55" t="n">
+      <x:c r="E28" s="68" t="n">
         <x:f>IF(A28=1,INT(('1. Eingaben'!B8+'6. Quellen &amp; Methodik'!B33-1)/'6. Quellen &amp; Methodik'!B33)*('6. Quellen &amp; Methodik'!B31+'6. Quellen &amp; Methodik'!B32*'6. Quellen &amp; Methodik'!B35),IF(OR(A28=13,A28=25),INT(('1. Eingaben'!B8+'6. Quellen &amp; Methodik'!B33-1)/'6. Quellen &amp; Methodik'!B33)*('6. Quellen &amp; Methodik'!B31+'6. Quellen &amp; Methodik'!B32*'6. Quellen &amp; Methodik'!B35)*'6. Quellen &amp; Methodik'!B34,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F28" s="55" t="n">
+      <x:c r="F28" s="68" t="n">
         <x:f>IF(A28=1,'6. Quellen &amp; Methodik'!B16+MIN(C28,50)*'6. Quellen &amp; Methodik'!B17+MAX(MIN(C28-50,200),0)*'6. Quellen &amp; Methodik'!B18+MAX(MIN(C28-250,750),0)*'6. Quellen &amp; Methodik'!B19+MAX(C28-1000,0)*'6. Quellen &amp; Methodik'!B20,0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G28" s="55" t="n">
+      <x:c r="G28" s="68" t="n">
         <x:f>IF(OR(A28=1,A28=13,A28=25),'6. Quellen &amp; Methodik'!B36*(C28*'1. Eingaben'!B10*12+E28+F28),0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H28" s="55" t="n">
+      <x:c r="H28" s="68" t="n">
         <x:f>SUM(D28:G28)</x:f>
         <x:v>7800</x:v>
       </x:c>
-      <x:c r="I28" s="54" t="n">
+      <x:c r="I28" s="55" t="n">
         <x:f>'4. Szenarien'!B6*(1-(1-'4. Szenarien'!B13)*POWER(0.5,(A28-1)/'4. Szenarien'!B14))</x:f>
         <x:v>6.4</x:v>
       </x:c>
-      <x:c r="J28" s="54" t="n">
+      <x:c r="J28" s="55" t="n">
         <x:f>'4. Szenarien'!B7*(1-(1-'4. Szenarien'!B13)*POWER(0.5,(A28-1)/'4. Szenarien'!B14))</x:f>
         <x:v>7.2</x:v>
       </x:c>
-      <x:c r="K28" s="55" t="n">
+      <x:c r="K28" s="68" t="n">
         <x:f>C28*I28*'4. Szenarien'!D6*'1. Eingaben'!B9</x:f>
         <x:v>48000</x:v>
       </x:c>
-      <x:c r="L28" s="55" t="n">
+      <x:c r="L28" s="68" t="n">
         <x:f>C28*J28*'4. Szenarien'!D7*'1. Eingaben'!B9</x:f>
         <x:v>54000</x:v>
       </x:c>
-      <x:c r="M28" s="55" t="n">
+      <x:c r="M28" s="68" t="n">
         <x:f>M27+K28-H28</x:f>
         <x:v>-77842.56274847715</x:v>
       </x:c>
-      <x:c r="N28" s="55" t="n">
+      <x:c r="N28" s="68" t="n">
         <x:f>N27+L28-H28</x:f>
         <x:v>-61963.88309203679</x:v>
       </x:c>
-      <x:c r="O28" s="68" t="n">
+      <x:c r="O28" s="81" t="n">
         <x:f>IF(M28&gt;=0,A28,99)</x:f>
         <x:v>99</x:v>
       </x:c>
-      <x:c r="P28" s="68" t="n">
+      <x:c r="P28" s="81" t="n">
         <x:f>IF(N28&gt;=0,A28,99)</x:f>
         <x:v>99</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
-      <x:c r="A29" s="66" t="n">
+      <x:c r="A29" s="79" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="B29" s="66" t="n">
+      <x:c r="B29" s="79" t="n">
         <x:f>INT((A29-1)/12)+1</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C29" s="66" t="n">
+      <x:c r="C29" s="79" t="n">
         <x:f>'1. Eingaben'!B8</x:f>
         <x:v>300</x:v>
       </x:c>
-      <x:c r="D29" s="55" t="n">
+      <x:c r="D29" s="68" t="n">
         <x:f>C29*'1. Eingaben'!B10</x:f>
         <x:v>7800</x:v>
       </x:c>
-      <x:c r="E29" s="55" t="n">
+      <x:c r="E29" s="68" t="n">
         <x:f>IF(A29=1,INT(('1. Eingaben'!B8+'6. Quellen &amp; Methodik'!B33-1)/'6. Quellen &amp; Methodik'!B33)*('6. Quellen &amp; Methodik'!B31+'6. Quellen &amp; Methodik'!B32*'6. Quellen &amp; Methodik'!B35),IF(OR(A29=13,A29=25),INT(('1. Eingaben'!B8+'6. Quellen &amp; Methodik'!B33-1)/'6. Quellen &amp; Methodik'!B33)*('6. Quellen &amp; Methodik'!B31+'6. Quellen &amp; Methodik'!B32*'6. Quellen &amp; Methodik'!B35)*'6. Quellen &amp; Methodik'!B34,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F29" s="55" t="n">
+      <x:c r="F29" s="68" t="n">
         <x:f>IF(A29=1,'6. Quellen &amp; Methodik'!B16+MIN(C29,50)*'6. Quellen &amp; Methodik'!B17+MAX(MIN(C29-50,200),0)*'6. Quellen &amp; Methodik'!B18+MAX(MIN(C29-250,750),0)*'6. Quellen &amp; Methodik'!B19+MAX(C29-1000,0)*'6. Quellen &amp; Methodik'!B20,0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G29" s="55" t="n">
+      <x:c r="G29" s="68" t="n">
         <x:f>IF(OR(A29=1,A29=13,A29=25),'6. Quellen &amp; Methodik'!B36*(C29*'1. Eingaben'!B10*12+E29+F29),0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H29" s="55" t="n">
+      <x:c r="H29" s="68" t="n">
         <x:f>SUM(D29:G29)</x:f>
         <x:v>7800</x:v>
       </x:c>
-      <x:c r="I29" s="54" t="n">
+      <x:c r="I29" s="55" t="n">
         <x:f>'4. Szenarien'!B6*(1-(1-'4. Szenarien'!B13)*POWER(0.5,(A29-1)/'4. Szenarien'!B14))</x:f>
         <x:v>6.8686291501015235</x:v>
       </x:c>
-      <x:c r="J29" s="54" t="n">
+      <x:c r="J29" s="55" t="n">
         <x:f>'4. Szenarien'!B7*(1-(1-'4. Szenarien'!B13)*POWER(0.5,(A29-1)/'4. Szenarien'!B14))</x:f>
         <x:v>7.727207793864214</x:v>
       </x:c>
-      <x:c r="K29" s="55" t="n">
+      <x:c r="K29" s="68" t="n">
         <x:f>C29*I29*'4. Szenarien'!D6*'1. Eingaben'!B9</x:f>
         <x:v>51514.71862576143</x:v>
       </x:c>
-      <x:c r="L29" s="55" t="n">
+      <x:c r="L29" s="68" t="n">
         <x:f>C29*J29*'4. Szenarien'!D7*'1. Eingaben'!B9</x:f>
         <x:v>57954.05845398161</x:v>
       </x:c>
-      <x:c r="M29" s="55" t="n">
+      <x:c r="M29" s="68" t="n">
         <x:f>M28+K29-H29</x:f>
         <x:v>-34127.844122715724</x:v>
       </x:c>
-      <x:c r="N29" s="55" t="n">
+      <x:c r="N29" s="68" t="n">
         <x:f>N28+L29-H29</x:f>
         <x:v>-11809.82463805518</x:v>
       </x:c>
-      <x:c r="O29" s="68" t="n">
+      <x:c r="O29" s="81" t="n">
         <x:f>IF(M29&gt;=0,A29,99)</x:f>
         <x:v>99</x:v>
       </x:c>
-      <x:c r="P29" s="68" t="n">
+      <x:c r="P29" s="81" t="n">
         <x:f>IF(N29&gt;=0,A29,99)</x:f>
         <x:v>99</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
-      <x:c r="A30" s="66" t="n">
+      <x:c r="A30" s="79" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="B30" s="66" t="n">
+      <x:c r="B30" s="79" t="n">
         <x:f>INT((A30-1)/12)+1</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C30" s="66" t="n">
+      <x:c r="C30" s="79" t="n">
         <x:f>'1. Eingaben'!B8</x:f>
         <x:v>300</x:v>
       </x:c>
-      <x:c r="D30" s="55" t="n">
+      <x:c r="D30" s="68" t="n">
         <x:f>C30*'1. Eingaben'!B10</x:f>
         <x:v>7800</x:v>
       </x:c>
-      <x:c r="E30" s="55" t="n">
+      <x:c r="E30" s="68" t="n">
         <x:f>IF(A30=1,INT(('1. Eingaben'!B8+'6. Quellen &amp; Methodik'!B33-1)/'6. Quellen &amp; Methodik'!B33)*('6. Quellen &amp; Methodik'!B31+'6. Quellen &amp; Methodik'!B32*'6. Quellen &amp; Methodik'!B35),IF(OR(A30=13,A30=25),INT(('1. Eingaben'!B8+'6. Quellen &amp; Methodik'!B33-1)/'6. Quellen &amp; Methodik'!B33)*('6. Quellen &amp; Methodik'!B31+'6. Quellen &amp; Methodik'!B32*'6. Quellen &amp; Methodik'!B35)*'6. Quellen &amp; Methodik'!B34,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F30" s="55" t="n">
+      <x:c r="F30" s="68" t="n">
         <x:f>IF(A30=1,'6. Quellen &amp; Methodik'!B16+MIN(C30,50)*'6. Quellen &amp; Methodik'!B17+MAX(MIN(C30-50,200),0)*'6. Quellen &amp; Methodik'!B18+MAX(MIN(C30-250,750),0)*'6. Quellen &amp; Methodik'!B19+MAX(C30-1000,0)*'6. Quellen &amp; Methodik'!B20,0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G30" s="55" t="n">
+      <x:c r="G30" s="68" t="n">
         <x:f>IF(OR(A30=1,A30=13,A30=25),'6. Quellen &amp; Methodik'!B36*(C30*'1. Eingaben'!B10*12+E30+F30),0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H30" s="55" t="n">
+      <x:c r="H30" s="68" t="n">
         <x:f>SUM(D30:G30)</x:f>
         <x:v>7800</x:v>
       </x:c>
-      <x:c r="I30" s="54" t="n">
+      <x:c r="I30" s="55" t="n">
         <x:f>'4. Szenarien'!B6*(1-(1-'4. Szenarien'!B13)*POWER(0.5,(A30-1)/'4. Szenarien'!B14))</x:f>
         <x:v>7.2</x:v>
       </x:c>
-      <x:c r="J30" s="54" t="n">
+      <x:c r="J30" s="55" t="n">
         <x:f>'4. Szenarien'!B7*(1-(1-'4. Szenarien'!B13)*POWER(0.5,(A30-1)/'4. Szenarien'!B14))</x:f>
         <x:v>8.1</x:v>
       </x:c>
-      <x:c r="K30" s="55" t="n">
+      <x:c r="K30" s="68" t="n">
         <x:f>C30*I30*'4. Szenarien'!D6*'1. Eingaben'!B9</x:f>
         <x:v>54000</x:v>
       </x:c>
-      <x:c r="L30" s="55" t="n">
+      <x:c r="L30" s="68" t="n">
         <x:f>C30*J30*'4. Szenarien'!D7*'1. Eingaben'!B9</x:f>
         <x:v>60750</x:v>
       </x:c>
-      <x:c r="M30" s="55" t="n">
+      <x:c r="M30" s="68" t="n">
         <x:f>M29+K30-H30</x:f>
         <x:v>12072.155877284276</x:v>
       </x:c>
-      <x:c r="N30" s="55" t="n">
+      <x:c r="N30" s="68" t="n">
         <x:f>N29+L30-H30</x:f>
         <x:v>41140.17536194482</x:v>
       </x:c>
-      <x:c r="O30" s="68" t="n">
+      <x:c r="O30" s="81" t="n">
         <x:f>IF(M30&gt;=0,A30,99)</x:f>
         <x:v>5</x:v>
       </x:c>
-      <x:c r="P30" s="68" t="n">
+      <x:c r="P30" s="81" t="n">
         <x:f>IF(N30&gt;=0,A30,99)</x:f>
         <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
-      <x:c r="A31" s="66" t="n">
+      <x:c r="A31" s="79" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="B31" s="66" t="n">
+      <x:c r="B31" s="79" t="n">
         <x:f>INT((A31-1)/12)+1</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C31" s="66" t="n">
+      <x:c r="C31" s="79" t="n">
         <x:f>'1. Eingaben'!B8</x:f>
         <x:v>300</x:v>
       </x:c>
-      <x:c r="D31" s="55" t="n">
+      <x:c r="D31" s="68" t="n">
         <x:f>C31*'1. Eingaben'!B10</x:f>
         <x:v>7800</x:v>
       </x:c>
-      <x:c r="E31" s="55" t="n">
+      <x:c r="E31" s="68" t="n">
         <x:f>IF(A31=1,INT(('1. Eingaben'!B8+'6. Quellen &amp; Methodik'!B33-1)/'6. Quellen &amp; Methodik'!B33)*('6. Quellen &amp; Methodik'!B31+'6. Quellen &amp; Methodik'!B32*'6. Quellen &amp; Methodik'!B35),IF(OR(A31=13,A31=25),INT(('1. Eingaben'!B8+'6. Quellen &amp; Methodik'!B33-1)/'6. Quellen &amp; Methodik'!B33)*('6. Quellen &amp; Methodik'!B31+'6. Quellen &amp; Methodik'!B32*'6. Quellen &amp; Methodik'!B35)*'6. Quellen &amp; Methodik'!B34,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F31" s="55" t="n">
+      <x:c r="F31" s="68" t="n">
         <x:f>IF(A31=1,'6. Quellen &amp; Methodik'!B16+MIN(C31,50)*'6. Quellen &amp; Methodik'!B17+MAX(MIN(C31-50,200),0)*'6. Quellen &amp; Methodik'!B18+MAX(MIN(C31-250,750),0)*'6. Quellen &amp; Methodik'!B19+MAX(C31-1000,0)*'6. Quellen &amp; Methodik'!B20,0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G31" s="55" t="n">
+      <x:c r="G31" s="68" t="n">
         <x:f>IF(OR(A31=1,A31=13,A31=25),'6. Quellen &amp; Methodik'!B36*(C31*'1. Eingaben'!B10*12+E31+F31),0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H31" s="55" t="n">
+      <x:c r="H31" s="68" t="n">
         <x:f>SUM(D31:G31)</x:f>
         <x:v>7800</x:v>
       </x:c>
-      <x:c r="I31" s="54" t="n">
+      <x:c r="I31" s="55" t="n">
         <x:f>'4. Szenarien'!B6*(1-(1-'4. Szenarien'!B13)*POWER(0.5,(A31-1)/'4. Szenarien'!B14))</x:f>
         <x:v>7.434314575050762</x:v>
       </x:c>
-      <x:c r="J31" s="54" t="n">
+      <x:c r="J31" s="55" t="n">
         <x:f>'4. Szenarien'!B7*(1-(1-'4. Szenarien'!B13)*POWER(0.5,(A31-1)/'4. Szenarien'!B14))</x:f>
         <x:v>8.363603896932107</x:v>
       </x:c>
-      <x:c r="K31" s="55" t="n">
+      <x:c r="K31" s="68" t="n">
         <x:f>C31*I31*'4. Szenarien'!D6*'1. Eingaben'!B9</x:f>
         <x:v>55757.35931288071</x:v>
       </x:c>
-      <x:c r="L31" s="55" t="n">
+      <x:c r="L31" s="68" t="n">
         <x:f>C31*J31*'4. Szenarien'!D7*'1. Eingaben'!B9</x:f>
         <x:v>62727.0292269908</x:v>
       </x:c>
-      <x:c r="M31" s="55" t="n">
+      <x:c r="M31" s="68" t="n">
         <x:f>M30+K31-H31</x:f>
         <x:v>60029.515190164995</x:v>
       </x:c>
-      <x:c r="N31" s="55" t="n">
+      <x:c r="N31" s="68" t="n">
         <x:f>N30+L31-H31</x:f>
         <x:v>96067.20458893562</x:v>
       </x:c>
-      <x:c r="O31" s="68" t="n">
+      <x:c r="O31" s="81" t="n">
         <x:f>IF(M31&gt;=0,A31,99)</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="P31" s="68" t="n">
+      <x:c r="P31" s="81" t="n">
         <x:f>IF(N31&gt;=0,A31,99)</x:f>
         <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
-      <x:c r="A32" s="66" t="n">
+      <x:c r="A32" s="79" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="B32" s="66" t="n">
+      <x:c r="B32" s="79" t="n">
         <x:f>INT((A32-1)/12)+1</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C32" s="66" t="n">
+      <x:c r="C32" s="79" t="n">
         <x:f>'1. Eingaben'!B8</x:f>
         <x:v>300</x:v>
       </x:c>
-      <x:c r="D32" s="55" t="n">
+      <x:c r="D32" s="68" t="n">
         <x:f>C32*'1. Eingaben'!B10</x:f>
         <x:v>7800</x:v>
       </x:c>
-      <x:c r="E32" s="55" t="n">
+      <x:c r="E32" s="68" t="n">
         <x:f>IF(A32=1,INT(('1. Eingaben'!B8+'6. Quellen &amp; Methodik'!B33-1)/'6. Quellen &amp; Methodik'!B33)*('6. Quellen &amp; Methodik'!B31+'6. Quellen &amp; Methodik'!B32*'6. Quellen &amp; Methodik'!B35),IF(OR(A32=13,A32=25),INT(('1. Eingaben'!B8+'6. Quellen &amp; Methodik'!B33-1)/'6. Quellen &amp; Methodik'!B33)*('6. Quellen &amp; Methodik'!B31+'6. Quellen &amp; Methodik'!B32*'6. Quellen &amp; Methodik'!B35)*'6. Quellen &amp; Methodik'!B34,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F32" s="55" t="n">
+      <x:c r="F32" s="68" t="n">
         <x:f>IF(A32=1,'6. Quellen &amp; Methodik'!B16+MIN(C32,50)*'6. Quellen &amp; Methodik'!B17+MAX(MIN(C32-50,200),0)*'6. Quellen &amp; Methodik'!B18+MAX(MIN(C32-250,750),0)*'6. Quellen &amp; Methodik'!B19+MAX(C32-1000,0)*'6. Quellen &amp; Methodik'!B20,0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G32" s="55" t="n">
+      <x:c r="G32" s="68" t="n">
         <x:f>IF(OR(A32=1,A32=13,A32=25),'6. Quellen &amp; Methodik'!B36*(C32*'1. Eingaben'!B10*12+E32+F32),0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H32" s="55" t="n">
+      <x:c r="H32" s="68" t="n">
         <x:f>SUM(D32:G32)</x:f>
         <x:v>7800</x:v>
       </x:c>
-      <x:c r="I32" s="54" t="n">
+      <x:c r="I32" s="55" t="n">
         <x:f>'4. Szenarien'!B6*(1-(1-'4. Szenarien'!B13)*POWER(0.5,(A32-1)/'4. Szenarien'!B14))</x:f>
         <x:v>7.6</x:v>
       </x:c>
-      <x:c r="J32" s="54" t="n">
+      <x:c r="J32" s="55" t="n">
         <x:f>'4. Szenarien'!B7*(1-(1-'4. Szenarien'!B13)*POWER(0.5,(A32-1)/'4. Szenarien'!B14))</x:f>
         <x:v>8.549999999999999</x:v>
       </x:c>
-      <x:c r="K32" s="55" t="n">
+      <x:c r="K32" s="68" t="n">
         <x:f>C32*I32*'4. Szenarien'!D6*'1. Eingaben'!B9</x:f>
         <x:v>57000</x:v>
       </x:c>
-      <x:c r="L32" s="55" t="n">
+      <x:c r="L32" s="68" t="n">
         <x:f>C32*J32*'4. Szenarien'!D7*'1. Eingaben'!B9</x:f>
         <x:v>64124.999999999985</x:v>
       </x:c>
-      <x:c r="M32" s="55" t="n">
+      <x:c r="M32" s="68" t="n">
         <x:f>M31+K32-H32</x:f>
         <x:v>109229.515190165</x:v>
       </x:c>
-      <x:c r="N32" s="55" t="n">
+      <x:c r="N32" s="68" t="n">
         <x:f>N31+L32-H32</x:f>
         <x:v>152392.2045889356</x:v>
       </x:c>
-      <x:c r="O32" s="68" t="n">
+      <x:c r="O32" s="81" t="n">
         <x:f>IF(M32&gt;=0,A32,99)</x:f>
         <x:v>7</x:v>
       </x:c>
-      <x:c r="P32" s="68" t="n">
+      <x:c r="P32" s="81" t="n">
         <x:f>IF(N32&gt;=0,A32,99)</x:f>
         <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="33">
-      <x:c r="A33" s="66" t="n">
+      <x:c r="A33" s="79" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="B33" s="66" t="n">
+      <x:c r="B33" s="79" t="n">
         <x:f>INT((A33-1)/12)+1</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C33" s="66" t="n">
+      <x:c r="C33" s="79" t="n">
         <x:f>'1. Eingaben'!B8</x:f>
         <x:v>300</x:v>
       </x:c>
-      <x:c r="D33" s="55" t="n">
+      <x:c r="D33" s="68" t="n">
         <x:f>C33*'1. Eingaben'!B10</x:f>
         <x:v>7800</x:v>
       </x:c>
-      <x:c r="E33" s="55" t="n">
+      <x:c r="E33" s="68" t="n">
         <x:f>IF(A33=1,INT(('1. Eingaben'!B8+'6. Quellen &amp; Methodik'!B33-1)/'6. Quellen &amp; Methodik'!B33)*('6. Quellen &amp; Methodik'!B31+'6. Quellen &amp; Methodik'!B32*'6. Quellen &amp; Methodik'!B35),IF(OR(A33=13,A33=25),INT(('1. Eingaben'!B8+'6. Quellen &amp; Methodik'!B33-1)/'6. Quellen &amp; Methodik'!B33)*('6. Quellen &amp; Methodik'!B31+'6. Quellen &amp; Methodik'!B32*'6. Quellen &amp; Methodik'!B35)*'6. Quellen &amp; Methodik'!B34,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F33" s="55" t="n">
+      <x:c r="F33" s="68" t="n">
         <x:f>IF(A33=1,'6. Quellen &amp; Methodik'!B16+MIN(C33,50)*'6. Quellen &amp; Methodik'!B17+MAX(MIN(C33-50,200),0)*'6. Quellen &amp; Methodik'!B18+MAX(MIN(C33-250,750),0)*'6. Quellen &amp; Methodik'!B19+MAX(C33-1000,0)*'6. Quellen &amp; Methodik'!B20,0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G33" s="55" t="n">
+      <x:c r="G33" s="68" t="n">
         <x:f>IF(OR(A33=1,A33=13,A33=25),'6. Quellen &amp; Methodik'!B36*(C33*'1. Eingaben'!B10*12+E33+F33),0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H33" s="55" t="n">
+      <x:c r="H33" s="68" t="n">
         <x:f>SUM(D33:G33)</x:f>
         <x:v>7800</x:v>
       </x:c>
-      <x:c r="I33" s="54" t="n">
+      <x:c r="I33" s="55" t="n">
         <x:f>'4. Szenarien'!B6*(1-(1-'4. Szenarien'!B13)*POWER(0.5,(A33-1)/'4. Szenarien'!B14))</x:f>
         <x:v>7.717157287525381</x:v>
       </x:c>
-      <x:c r="J33" s="54" t="n">
+      <x:c r="J33" s="55" t="n">
         <x:f>'4. Szenarien'!B7*(1-(1-'4. Szenarien'!B13)*POWER(0.5,(A33-1)/'4. Szenarien'!B14))</x:f>
         <x:v>8.681801948466052</x:v>
       </x:c>
-      <x:c r="K33" s="55" t="n">
+      <x:c r="K33" s="68" t="n">
         <x:f>C33*I33*'4. Szenarien'!D6*'1. Eingaben'!B9</x:f>
         <x:v>57878.67965644035</x:v>
       </x:c>
-      <x:c r="L33" s="55" t="n">
+      <x:c r="L33" s="68" t="n">
         <x:f>C33*J33*'4. Szenarien'!D7*'1. Eingaben'!B9</x:f>
         <x:v>65113.5146134954</x:v>
       </x:c>
-      <x:c r="M33" s="55" t="n">
+      <x:c r="M33" s="68" t="n">
         <x:f>M32+K33-H33</x:f>
         <x:v>159308.19484660536</x:v>
       </x:c>
-      <x:c r="N33" s="55" t="n">
+      <x:c r="N33" s="68" t="n">
         <x:f>N32+L33-H33</x:f>
         <x:v>209705.71920243098</x:v>
       </x:c>
-      <x:c r="O33" s="68" t="n">
+      <x:c r="O33" s="81" t="n">
         <x:f>IF(M33&gt;=0,A33,99)</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="P33" s="68" t="n">
+      <x:c r="P33" s="81" t="n">
         <x:f>IF(N33&gt;=0,A33,99)</x:f>
         <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="34">
-      <x:c r="A34" s="66" t="n">
+      <x:c r="A34" s="79" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="B34" s="66" t="n">
+      <x:c r="B34" s="79" t="n">
         <x:f>INT((A34-1)/12)+1</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C34" s="66" t="n">
+      <x:c r="C34" s="79" t="n">
         <x:f>'1. Eingaben'!B8</x:f>
         <x:v>300</x:v>
       </x:c>
-      <x:c r="D34" s="55" t="n">
+      <x:c r="D34" s="68" t="n">
         <x:f>C34*'1. Eingaben'!B10</x:f>
         <x:v>7800</x:v>
       </x:c>
-      <x:c r="E34" s="55" t="n">
+      <x:c r="E34" s="68" t="n">
         <x:f>IF(A34=1,INT(('1. Eingaben'!B8+'6. Quellen &amp; Methodik'!B33-1)/'6. Quellen &amp; Methodik'!B33)*('6. Quellen &amp; Methodik'!B31+'6. Quellen &amp; Methodik'!B32*'6. Quellen &amp; Methodik'!B35),IF(OR(A34=13,A34=25),INT(('1. Eingaben'!B8+'6. Quellen &amp; Methodik'!B33-1)/'6. Quellen &amp; Methodik'!B33)*('6. Quellen &amp; Methodik'!B31+'6. Quellen &amp; Methodik'!B32*'6. Quellen &amp; Methodik'!B35)*'6. Quellen &amp; Methodik'!B34,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F34" s="55" t="n">
+      <x:c r="F34" s="68" t="n">
         <x:f>IF(A34=1,'6. Quellen &amp; Methodik'!B16+MIN(C34,50)*'6. Quellen &amp; Methodik'!B17+MAX(MIN(C34-50,200),0)*'6. Quellen &amp; Methodik'!B18+MAX(MIN(C34-250,750),0)*'6. Quellen &amp; Methodik'!B19+MAX(C34-1000,0)*'6. Quellen &amp; Methodik'!B20,0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G34" s="55" t="n">
+      <x:c r="G34" s="68" t="n">
         <x:f>IF(OR(A34=1,A34=13,A34=25),'6. Quellen &amp; Methodik'!B36*(C34*'1. Eingaben'!B10*12+E34+F34),0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H34" s="55" t="n">
+      <x:c r="H34" s="68" t="n">
         <x:f>SUM(D34:G34)</x:f>
         <x:v>7800</x:v>
       </x:c>
-      <x:c r="I34" s="54" t="n">
+      <x:c r="I34" s="55" t="n">
         <x:f>'4. Szenarien'!B6*(1-(1-'4. Szenarien'!B13)*POWER(0.5,(A34-1)/'4. Szenarien'!B14))</x:f>
         <x:v>7.8</x:v>
       </x:c>
-      <x:c r="J34" s="54" t="n">
+      <x:c r="J34" s="55" t="n">
         <x:f>'4. Szenarien'!B7*(1-(1-'4. Szenarien'!B13)*POWER(0.5,(A34-1)/'4. Szenarien'!B14))</x:f>
         <x:v>8.775</x:v>
       </x:c>
-      <x:c r="K34" s="55" t="n">
+      <x:c r="K34" s="68" t="n">
         <x:f>C34*I34*'4. Szenarien'!D6*'1. Eingaben'!B9</x:f>
         <x:v>58500</x:v>
       </x:c>
-      <x:c r="L34" s="55" t="n">
+      <x:c r="L34" s="68" t="n">
         <x:f>C34*J34*'4. Szenarien'!D7*'1. Eingaben'!B9</x:f>
         <x:v>65812.5</x:v>
       </x:c>
-      <x:c r="M34" s="55" t="n">
+      <x:c r="M34" s="68" t="n">
         <x:f>M33+K34-H34</x:f>
         <x:v>210008.19484660536</x:v>
       </x:c>
-      <x:c r="N34" s="55" t="n">
+      <x:c r="N34" s="68" t="n">
         <x:f>N33+L34-H34</x:f>
         <x:v>267718.219202431</x:v>
       </x:c>
-      <x:c r="O34" s="68" t="n">
+      <x:c r="O34" s="81" t="n">
         <x:f>IF(M34&gt;=0,A34,99)</x:f>
         <x:v>9</x:v>
       </x:c>
-      <x:c r="P34" s="68" t="n">
+      <x:c r="P34" s="81" t="n">
         <x:f>IF(N34&gt;=0,A34,99)</x:f>
         <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
-      <x:c r="A35" s="66" t="n">
+      <x:c r="A35" s="79" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="B35" s="66" t="n">
+      <x:c r="B35" s="79" t="n">
         <x:f>INT((A35-1)/12)+1</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C35" s="66" t="n">
+      <x:c r="C35" s="79" t="n">
         <x:f>'1. Eingaben'!B8</x:f>
         <x:v>300</x:v>
       </x:c>
-      <x:c r="D35" s="55" t="n">
+      <x:c r="D35" s="68" t="n">
         <x:f>C35*'1. Eingaben'!B10</x:f>
         <x:v>7800</x:v>
       </x:c>
-      <x:c r="E35" s="55" t="n">
+      <x:c r="E35" s="68" t="n">
         <x:f>IF(A35=1,INT(('1. Eingaben'!B8+'6. Quellen &amp; Methodik'!B33-1)/'6. Quellen &amp; Methodik'!B33)*('6. Quellen &amp; Methodik'!B31+'6. Quellen &amp; Methodik'!B32*'6. Quellen &amp; Methodik'!B35),IF(OR(A35=13,A35=25),INT(('1. Eingaben'!B8+'6. Quellen &amp; Methodik'!B33-1)/'6. Quellen &amp; Methodik'!B33)*('6. Quellen &amp; Methodik'!B31+'6. Quellen &amp; Methodik'!B32*'6. Quellen &amp; Methodik'!B35)*'6. Quellen &amp; Methodik'!B34,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F35" s="55" t="n">
+      <x:c r="F35" s="68" t="n">
         <x:f>IF(A35=1,'6. Quellen &amp; Methodik'!B16+MIN(C35,50)*'6. Quellen &amp; Methodik'!B17+MAX(MIN(C35-50,200),0)*'6. Quellen &amp; Methodik'!B18+MAX(MIN(C35-250,750),0)*'6. Quellen &amp; Methodik'!B19+MAX(C35-1000,0)*'6. Quellen &amp; Methodik'!B20,0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G35" s="55" t="n">
+      <x:c r="G35" s="68" t="n">
         <x:f>IF(OR(A35=1,A35=13,A35=25),'6. Quellen &amp; Methodik'!B36*(C35*'1. Eingaben'!B10*12+E35+F35),0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H35" s="55" t="n">
+      <x:c r="H35" s="68" t="n">
         <x:f>SUM(D35:G35)</x:f>
         <x:v>7800</x:v>
       </x:c>
-      <x:c r="I35" s="54" t="n">
+      <x:c r="I35" s="55" t="n">
         <x:f>'4. Szenarien'!B6*(1-(1-'4. Szenarien'!B13)*POWER(0.5,(A35-1)/'4. Szenarien'!B14))</x:f>
         <x:v>7.858578643762691</x:v>
       </x:c>
-      <x:c r="J35" s="54" t="n">
+      <x:c r="J35" s="55" t="n">
         <x:f>'4. Szenarien'!B7*(1-(1-'4. Szenarien'!B13)*POWER(0.5,(A35-1)/'4. Szenarien'!B14))</x:f>
         <x:v>8.840900974233026</x:v>
       </x:c>
-      <x:c r="K35" s="55" t="n">
+      <x:c r="K35" s="68" t="n">
         <x:f>C35*I35*'4. Szenarien'!D6*'1. Eingaben'!B9</x:f>
         <x:v>58939.33982822018</x:v>
       </x:c>
-      <x:c r="L35" s="55" t="n">
+      <x:c r="L35" s="68" t="n">
         <x:f>C35*J35*'4. Szenarien'!D7*'1. Eingaben'!B9</x:f>
         <x:v>66306.75730674769</x:v>
       </x:c>
-      <x:c r="M35" s="55" t="n">
+      <x:c r="M35" s="68" t="n">
         <x:f>M34+K35-H35</x:f>
         <x:v>261147.53467482555</x:v>
       </x:c>
-      <x:c r="N35" s="55" t="n">
+      <x:c r="N35" s="68" t="n">
         <x:f>N34+L35-H35</x:f>
         <x:v>326224.97650917864</x:v>
       </x:c>
-      <x:c r="O35" s="68" t="n">
+      <x:c r="O35" s="81" t="n">
         <x:f>IF(M35&gt;=0,A35,99)</x:f>
         <x:v>10</x:v>
       </x:c>
-      <x:c r="P35" s="68" t="n">
+      <x:c r="P35" s="81" t="n">
         <x:f>IF(N35&gt;=0,A35,99)</x:f>
         <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="36">
-      <x:c r="A36" s="66" t="n">
+      <x:c r="A36" s="79" t="n">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="B36" s="66" t="n">
+      <x:c r="B36" s="79" t="n">
         <x:f>INT((A36-1)/12)+1</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C36" s="66" t="n">
+      <x:c r="C36" s="79" t="n">
         <x:f>'1. Eingaben'!B8</x:f>
         <x:v>300</x:v>
       </x:c>
-      <x:c r="D36" s="55" t="n">
+      <x:c r="D36" s="68" t="n">
         <x:f>C36*'1. Eingaben'!B10</x:f>
         <x:v>7800</x:v>
       </x:c>
-      <x:c r="E36" s="55" t="n">
+      <x:c r="E36" s="68" t="n">
         <x:f>IF(A36=1,INT(('1. Eingaben'!B8+'6. Quellen &amp; Methodik'!B33-1)/'6. Quellen &amp; Methodik'!B33)*('6. Quellen &amp; Methodik'!B31+'6. Quellen &amp; Methodik'!B32*'6. Quellen &amp; Methodik'!B35),IF(OR(A36=13,A36=25),INT(('1. Eingaben'!B8+'6. Quellen &amp; Methodik'!B33-1)/'6. Quellen &amp; Methodik'!B33)*('6. Quellen &amp; Methodik'!B31+'6. Quellen &amp; Methodik'!B32*'6. Quellen &amp; Methodik'!B35)*'6. Quellen &amp; Methodik'!B34,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F36" s="55" t="n">
+      <x:c r="F36" s="68" t="n">
         <x:f>IF(A36=1,'6. Quellen &amp; Methodik'!B16+MIN(C36,50)*'6. Quellen &amp; Methodik'!B17+MAX(MIN(C36-50,200),0)*'6. Quellen &amp; Methodik'!B18+MAX(MIN(C36-250,750),0)*'6. Quellen &amp; Methodik'!B19+MAX(C36-1000,0)*'6. Quellen &amp; Methodik'!B20,0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G36" s="55" t="n">
+      <x:c r="G36" s="68" t="n">
         <x:f>IF(OR(A36=1,A36=13,A36=25),'6. Quellen &amp; Methodik'!B36*(C36*'1. Eingaben'!B10*12+E36+F36),0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H36" s="55" t="n">
+      <x:c r="H36" s="68" t="n">
         <x:f>SUM(D36:G36)</x:f>
         <x:v>7800</x:v>
       </x:c>
-      <x:c r="I36" s="54" t="n">
+      <x:c r="I36" s="55" t="n">
         <x:f>'4. Szenarien'!B6*(1-(1-'4. Szenarien'!B13)*POWER(0.5,(A36-1)/'4. Szenarien'!B14))</x:f>
         <x:v>7.9</x:v>
       </x:c>
-      <x:c r="J36" s="54" t="n">
+      <x:c r="J36" s="55" t="n">
         <x:f>'4. Szenarien'!B7*(1-(1-'4. Szenarien'!B13)*POWER(0.5,(A36-1)/'4. Szenarien'!B14))</x:f>
         <x:v>8.887500000000001</x:v>
       </x:c>
-      <x:c r="K36" s="55" t="n">
+      <x:c r="K36" s="68" t="n">
         <x:f>C36*I36*'4. Szenarien'!D6*'1. Eingaben'!B9</x:f>
         <x:v>59250</x:v>
       </x:c>
-      <x:c r="L36" s="55" t="n">
+      <x:c r="L36" s="68" t="n">
         <x:f>C36*J36*'4. Szenarien'!D7*'1. Eingaben'!B9</x:f>
         <x:v>66656.25000000001</x:v>
       </x:c>
-      <x:c r="M36" s="55" t="n">
+      <x:c r="M36" s="68" t="n">
         <x:f>M35+K36-H36</x:f>
         <x:v>312597.53467482555</x:v>
       </x:c>
-      <x:c r="N36" s="55" t="n">
+      <x:c r="N36" s="68" t="n">
         <x:f>N35+L36-H36</x:f>
         <x:v>385081.22650917864</x:v>
       </x:c>
-      <x:c r="O36" s="68" t="n">
+      <x:c r="O36" s="81" t="n">
         <x:f>IF(M36&gt;=0,A36,99)</x:f>
         <x:v>11</x:v>
       </x:c>
-      <x:c r="P36" s="68" t="n">
+      <x:c r="P36" s="81" t="n">
         <x:f>IF(N36&gt;=0,A36,99)</x:f>
         <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="37">
-      <x:c r="A37" s="66" t="n">
+      <x:c r="A37" s="79" t="n">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="B37" s="66" t="n">
+      <x:c r="B37" s="79" t="n">
         <x:f>INT((A37-1)/12)+1</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C37" s="66" t="n">
+      <x:c r="C37" s="79" t="n">
         <x:f>'1. Eingaben'!B8</x:f>
         <x:v>300</x:v>
       </x:c>
-      <x:c r="D37" s="55" t="n">
+      <x:c r="D37" s="68" t="n">
         <x:f>C37*'1. Eingaben'!B10</x:f>
         <x:v>7800</x:v>
       </x:c>
-      <x:c r="E37" s="55" t="n">
+      <x:c r="E37" s="68" t="n">
         <x:f>IF(A37=1,INT(('1. Eingaben'!B8+'6. Quellen &amp; Methodik'!B33-1)/'6. Quellen &amp; Methodik'!B33)*('6. Quellen &amp; Methodik'!B31+'6. Quellen &amp; Methodik'!B32*'6. Quellen &amp; Methodik'!B35),IF(OR(A37=13,A37=25),INT(('1. Eingaben'!B8+'6. Quellen &amp; Methodik'!B33-1)/'6. Quellen &amp; Methodik'!B33)*('6. Quellen &amp; Methodik'!B31+'6. Quellen &amp; Methodik'!B32*'6. Quellen &amp; Methodik'!B35)*'6. Quellen &amp; Methodik'!B34,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F37" s="55" t="n">
+      <x:c r="F37" s="68" t="n">
         <x:f>IF(A37=1,'6. Quellen &amp; Methodik'!B16+MIN(C37,50)*'6. Quellen &amp; Methodik'!B17+MAX(MIN(C37-50,200),0)*'6. Quellen &amp; Methodik'!B18+MAX(MIN(C37-250,750),0)*'6. Quellen &amp; Methodik'!B19+MAX(C37-1000,0)*'6. Quellen &amp; Methodik'!B20,0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G37" s="55" t="n">
+      <x:c r="G37" s="68" t="n">
         <x:f>IF(OR(A37=1,A37=13,A37=25),'6. Quellen &amp; Methodik'!B36*(C37*'1. Eingaben'!B10*12+E37+F37),0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H37" s="55" t="n">
+      <x:c r="H37" s="68" t="n">
         <x:f>SUM(D37:G37)</x:f>
         <x:v>7800</x:v>
       </x:c>
-      <x:c r="I37" s="54" t="n">
+      <x:c r="I37" s="55" t="n">
         <x:f>'4. Szenarien'!B6*(1-(1-'4. Szenarien'!B13)*POWER(0.5,(A37-1)/'4. Szenarien'!B14))</x:f>
         <x:v>7.929289321881345</x:v>
       </x:c>
-      <x:c r="J37" s="54" t="n">
+      <x:c r="J37" s="55" t="n">
         <x:f>'4. Szenarien'!B7*(1-(1-'4. Szenarien'!B13)*POWER(0.5,(A37-1)/'4. Szenarien'!B14))</x:f>
         <x:v>8.920450487116513</x:v>
       </x:c>
-      <x:c r="K37" s="55" t="n">
+      <x:c r="K37" s="68" t="n">
         <x:f>C37*I37*'4. Szenarien'!D6*'1. Eingaben'!B9</x:f>
         <x:v>59469.66991411009</x:v>
       </x:c>
-      <x:c r="L37" s="55" t="n">
+      <x:c r="L37" s="68" t="n">
         <x:f>C37*J37*'4. Szenarien'!D7*'1. Eingaben'!B9</x:f>
         <x:v>66903.37865337385</x:v>
       </x:c>
-      <x:c r="M37" s="55" t="n">
+      <x:c r="M37" s="68" t="n">
         <x:f>M36+K37-H37</x:f>
         <x:v>364267.20458893565</x:v>
       </x:c>
-      <x:c r="N37" s="55" t="n">
+      <x:c r="N37" s="68" t="n">
         <x:f>N36+L37-H37</x:f>
         <x:v>444184.6051625525</x:v>
       </x:c>
-      <x:c r="O37" s="68" t="n">
+      <x:c r="O37" s="81" t="n">
         <x:f>IF(M37&gt;=0,A37,99)</x:f>
         <x:v>12</x:v>
       </x:c>
-      <x:c r="P37" s="68" t="n">
+      <x:c r="P37" s="81" t="n">
         <x:f>IF(N37&gt;=0,A37,99)</x:f>
         <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="38">
-      <x:c r="A38" s="66" t="n">
+      <x:c r="A38" s="79" t="n">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="B38" s="66" t="n">
+      <x:c r="B38" s="79" t="n">
         <x:f>INT((A38-1)/12)+1</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C38" s="66" t="n">
+      <x:c r="C38" s="79" t="n">
         <x:f>'1. Eingaben'!B8</x:f>
         <x:v>300</x:v>
       </x:c>
-      <x:c r="D38" s="55" t="n">
+      <x:c r="D38" s="68" t="n">
         <x:f>C38*'1. Eingaben'!B10</x:f>
         <x:v>7800</x:v>
       </x:c>
-      <x:c r="E38" s="55" t="n">
+      <x:c r="E38" s="68" t="n">
         <x:f>IF(A38=1,INT(('1. Eingaben'!B8+'6. Quellen &amp; Methodik'!B33-1)/'6. Quellen &amp; Methodik'!B33)*('6. Quellen &amp; Methodik'!B31+'6. Quellen &amp; Methodik'!B32*'6. Quellen &amp; Methodik'!B35),IF(OR(A38=13,A38=25),INT(('1. Eingaben'!B8+'6. Quellen &amp; Methodik'!B33-1)/'6. Quellen &amp; Methodik'!B33)*('6. Quellen &amp; Methodik'!B31+'6. Quellen &amp; Methodik'!B32*'6. Quellen &amp; Methodik'!B35)*'6. Quellen &amp; Methodik'!B34,0))</x:f>
         <x:v>62500</x:v>
       </x:c>
-      <x:c r="F38" s="55" t="n">
+      <x:c r="F38" s="68" t="n">
         <x:f>IF(A38=1,'6. Quellen &amp; Methodik'!B16+MIN(C38,50)*'6. Quellen &amp; Methodik'!B17+MAX(MIN(C38-50,200),0)*'6. Quellen &amp; Methodik'!B18+MAX(MIN(C38-250,750),0)*'6. Quellen &amp; Methodik'!B19+MAX(C38-1000,0)*'6. Quellen &amp; Methodik'!B20,0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G38" s="55" t="n">
+      <x:c r="G38" s="68" t="n">
         <x:f>IF(OR(A38=1,A38=13,A38=25),'6. Quellen &amp; Methodik'!B36*(C38*'1. Eingaben'!B10*12+E38+F38),0)</x:f>
         <x:v>18732</x:v>
       </x:c>
-      <x:c r="H38" s="55" t="n">
+      <x:c r="H38" s="68" t="n">
         <x:f>SUM(D38:G38)</x:f>
         <x:v>89032</x:v>
       </x:c>
-      <x:c r="I38" s="54" t="n">
+      <x:c r="I38" s="55" t="n">
         <x:f>'4. Szenarien'!B6*(1-(1-'4. Szenarien'!B13)*POWER(0.5,(A38-1)/'4. Szenarien'!B14))</x:f>
         <x:v>7.95</x:v>
       </x:c>
-      <x:c r="J38" s="54" t="n">
+      <x:c r="J38" s="55" t="n">
         <x:f>'4. Szenarien'!B7*(1-(1-'4. Szenarien'!B13)*POWER(0.5,(A38-1)/'4. Szenarien'!B14))</x:f>
         <x:v>8.94375</x:v>
       </x:c>
-      <x:c r="K38" s="55" t="n">
+      <x:c r="K38" s="68" t="n">
         <x:f>C38*I38*'4. Szenarien'!D6*'1. Eingaben'!B9</x:f>
         <x:v>59625</x:v>
       </x:c>
-      <x:c r="L38" s="55" t="n">
+      <x:c r="L38" s="68" t="n">
         <x:f>C38*J38*'4. Szenarien'!D7*'1. Eingaben'!B9</x:f>
         <x:v>67078.125</x:v>
       </x:c>
-      <x:c r="M38" s="55" t="n">
+      <x:c r="M38" s="68" t="n">
         <x:f>M37+K38-H38</x:f>
         <x:v>334860.20458893565</x:v>
       </x:c>
-      <x:c r="N38" s="55" t="n">
+      <x:c r="N38" s="68" t="n">
         <x:f>N37+L38-H38</x:f>
         <x:v>422230.7301625525</x:v>
       </x:c>
-      <x:c r="O38" s="68" t="n">
+      <x:c r="O38" s="81" t="n">
         <x:f>IF(M38&gt;=0,A38,99)</x:f>
         <x:v>13</x:v>
       </x:c>
-      <x:c r="P38" s="68" t="n">
+      <x:c r="P38" s="81" t="n">
         <x:f>IF(N38&gt;=0,A38,99)</x:f>
         <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="39">
-      <x:c r="A39" s="66" t="n">
+      <x:c r="A39" s="79" t="n">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="B39" s="66" t="n">
+      <x:c r="B39" s="79" t="n">
         <x:f>INT((A39-1)/12)+1</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C39" s="66" t="n">
+      <x:c r="C39" s="79" t="n">
         <x:f>'1. Eingaben'!B8</x:f>
         <x:v>300</x:v>
       </x:c>
-      <x:c r="D39" s="55" t="n">
+      <x:c r="D39" s="68" t="n">
         <x:f>C39*'1. Eingaben'!B10</x:f>
         <x:v>7800</x:v>
       </x:c>
-      <x:c r="E39" s="55" t="n">
+      <x:c r="E39" s="68" t="n">
         <x:f>IF(A39=1,INT(('1. Eingaben'!B8+'6. Quellen &amp; Methodik'!B33-1)/'6. Quellen &amp; Methodik'!B33)*('6. Quellen &amp; Methodik'!B31+'6. Quellen &amp; Methodik'!B32*'6. Quellen &amp; Methodik'!B35),IF(OR(A39=13,A39=25),INT(('1. Eingaben'!B8+'6. Quellen &amp; Methodik'!B33-1)/'6. Quellen &amp; Methodik'!B33)*('6. Quellen &amp; Methodik'!B31+'6. Quellen &amp; Methodik'!B32*'6. Quellen &amp; Methodik'!B35)*'6. Quellen &amp; Methodik'!B34,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F39" s="55" t="n">
+      <x:c r="F39" s="68" t="n">
         <x:f>IF(A39=1,'6. Quellen &amp; Methodik'!B16+MIN(C39,50)*'6. Quellen &amp; Methodik'!B17+MAX(MIN(C39-50,200),0)*'6. Quellen &amp; Methodik'!B18+MAX(MIN(C39-250,750),0)*'6. Quellen &amp; Methodik'!B19+MAX(C39-1000,0)*'6. Quellen &amp; Methodik'!B20,0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G39" s="55" t="n">
+      <x:c r="G39" s="68" t="n">
         <x:f>IF(OR(A39=1,A39=13,A39=25),'6. Quellen &amp; Methodik'!B36*(C39*'1. Eingaben'!B10*12+E39+F39),0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H39" s="55" t="n">
+      <x:c r="H39" s="68" t="n">
         <x:f>SUM(D39:G39)</x:f>
         <x:v>7800</x:v>
       </x:c>
-      <x:c r="I39" s="54" t="n">
+      <x:c r="I39" s="55" t="n">
         <x:f>'4. Szenarien'!B6*(1-(1-'4. Szenarien'!B13)*POWER(0.5,(A39-1)/'4. Szenarien'!B14))</x:f>
         <x:v>7.964644660940673</x:v>
       </x:c>
-      <x:c r="J39" s="54" t="n">
+      <x:c r="J39" s="55" t="n">
         <x:f>'4. Szenarien'!B7*(1-(1-'4. Szenarien'!B13)*POWER(0.5,(A39-1)/'4. Szenarien'!B14))</x:f>
         <x:v>8.960225243558257</x:v>
       </x:c>
-      <x:c r="K39" s="55" t="n">
+      <x:c r="K39" s="68" t="n">
         <x:f>C39*I39*'4. Szenarien'!D6*'1. Eingaben'!B9</x:f>
         <x:v>59734.83495705505</x:v>
       </x:c>
-      <x:c r="L39" s="55" t="n">
+      <x:c r="L39" s="68" t="n">
         <x:f>C39*J39*'4. Szenarien'!D7*'1. Eingaben'!B9</x:f>
         <x:v>67201.68932668693</x:v>
       </x:c>
-      <x:c r="M39" s="55" t="n">
+      <x:c r="M39" s="68" t="n">
         <x:f>M38+K39-H39</x:f>
         <x:v>386795.0395459907</x:v>
       </x:c>
-      <x:c r="N39" s="55" t="n">
+      <x:c r="N39" s="68" t="n">
         <x:f>N38+L39-H39</x:f>
         <x:v>481632.41948923946</x:v>
       </x:c>
-      <x:c r="O39" s="68" t="n">
+      <x:c r="O39" s="81" t="n">
         <x:f>IF(M39&gt;=0,A39,99)</x:f>
         <x:v>14</x:v>
       </x:c>
-      <x:c r="P39" s="68" t="n">
+      <x:c r="P39" s="81" t="n">
         <x:f>IF(N39&gt;=0,A39,99)</x:f>
         <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="40">
-      <x:c r="A40" s="66" t="n">
+      <x:c r="A40" s="79" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="B40" s="66" t="n">
+      <x:c r="B40" s="79" t="n">
         <x:f>INT((A40-1)/12)+1</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C40" s="66" t="n">
+      <x:c r="C40" s="79" t="n">
         <x:f>'1. Eingaben'!B8</x:f>
         <x:v>300</x:v>
       </x:c>
-      <x:c r="D40" s="55" t="n">
+      <x:c r="D40" s="68" t="n">
         <x:f>C40*'1. Eingaben'!B10</x:f>
         <x:v>7800</x:v>
       </x:c>
-      <x:c r="E40" s="55" t="n">
+      <x:c r="E40" s="68" t="n">
         <x:f>IF(A40=1,INT(('1. Eingaben'!B8+'6. Quellen &amp; Methodik'!B33-1)/'6. Quellen &amp; Methodik'!B33)*('6. Quellen &amp; Methodik'!B31+'6. Quellen &amp; Methodik'!B32*'6. Quellen &amp; Methodik'!B35),IF(OR(A40=13,A40=25),INT(('1. Eingaben'!B8+'6. Quellen &amp; Methodik'!B33-1)/'6. Quellen &amp; Methodik'!B33)*('6. Quellen &amp; Methodik'!B31+'6. Quellen &amp; Methodik'!B32*'6. Quellen &amp; Methodik'!B35)*'6. Quellen &amp; Methodik'!B34,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F40" s="55" t="n">
+      <x:c r="F40" s="68" t="n">
         <x:f>IF(A40=1,'6. Quellen &amp; Methodik'!B16+MIN(C40,50)*'6. Quellen &amp; Methodik'!B17+MAX(MIN(C40-50,200),0)*'6. Quellen &amp; Methodik'!B18+MAX(MIN(C40-250,750),0)*'6. Quellen &amp; Methodik'!B19+MAX(C40-1000,0)*'6. Quellen &amp; Methodik'!B20,0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G40" s="55" t="n">
+      <x:c r="G40" s="68" t="n">
         <x:f>IF(OR(A40=1,A40=13,A40=25),'6. Quellen &amp; Methodik'!B36*(C40*'1. Eingaben'!B10*12+E40+F40),0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H40" s="55" t="n">
+      <x:c r="H40" s="68" t="n">
         <x:f>SUM(D40:G40)</x:f>
         <x:v>7800</x:v>
       </x:c>
-      <x:c r="I40" s="54" t="n">
+      <x:c r="I40" s="55" t="n">
         <x:f>'4. Szenarien'!B6*(1-(1-'4. Szenarien'!B13)*POWER(0.5,(A40-1)/'4. Szenarien'!B14))</x:f>
         <x:v>7.975</x:v>
       </x:c>
-      <x:c r="J40" s="54" t="n">
+      <x:c r="J40" s="55" t="n">
         <x:f>'4. Szenarien'!B7*(1-(1-'4. Szenarien'!B13)*POWER(0.5,(A40-1)/'4. Szenarien'!B14))</x:f>
         <x:v>8.971874999999999</x:v>
       </x:c>
-      <x:c r="K40" s="55" t="n">
+      <x:c r="K40" s="68" t="n">
         <x:f>C40*I40*'4. Szenarien'!D6*'1. Eingaben'!B9</x:f>
         <x:v>59812.5</x:v>
       </x:c>
-      <x:c r="L40" s="55" t="n">
+      <x:c r="L40" s="68" t="n">
         <x:f>C40*J40*'4. Szenarien'!D7*'1. Eingaben'!B9</x:f>
         <x:v>67289.06249999999</x:v>
       </x:c>
-      <x:c r="M40" s="55" t="n">
+      <x:c r="M40" s="68" t="n">
         <x:f>M39+K40-H40</x:f>
         <x:v>438807.5395459907</x:v>
       </x:c>
-      <x:c r="N40" s="55" t="n">
+      <x:c r="N40" s="68" t="n">
         <x:f>N39+L40-H40</x:f>
         <x:v>541121.4819892395</x:v>
       </x:c>
-      <x:c r="O40" s="68" t="n">
+      <x:c r="O40" s="81" t="n">
         <x:f>IF(M40&gt;=0,A40,99)</x:f>
         <x:v>15</x:v>
       </x:c>
-      <x:c r="P40" s="68" t="n">
+      <x:c r="P40" s="81" t="n">
         <x:f>IF(N40&gt;=0,A40,99)</x:f>
         <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="41">
-      <x:c r="A41" s="66" t="n">
+      <x:c r="A41" s="79" t="n">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="B41" s="66" t="n">
+      <x:c r="B41" s="79" t="n">
         <x:f>INT((A41-1)/12)+1</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C41" s="66" t="n">
+      <x:c r="C41" s="79" t="n">
         <x:f>'1. Eingaben'!B8</x:f>
         <x:v>300</x:v>
       </x:c>
-      <x:c r="D41" s="55" t="n">
+      <x:c r="D41" s="68" t="n">
         <x:f>C41*'1. Eingaben'!B10</x:f>
         <x:v>7800</x:v>
       </x:c>
-      <x:c r="E41" s="55" t="n">
+      <x:c r="E41" s="68" t="n">
         <x:f>IF(A41=1,INT(('1. Eingaben'!B8+'6. Quellen &amp; Methodik'!B33-1)/'6. Quellen &amp; Methodik'!B33)*('6. Quellen &amp; Methodik'!B31+'6. Quellen &amp; Methodik'!B32*'6. Quellen &amp; Methodik'!B35),IF(OR(A41=13,A41=25),INT(('1. Eingaben'!B8+'6. Quellen &amp; Methodik'!B33-1)/'6. Quellen &amp; Methodik'!B33)*('6. Quellen &amp; Methodik'!B31+'6. Quellen &amp; Methodik'!B32*'6. Quellen &amp; Methodik'!B35)*'6. Quellen &amp; Methodik'!B34,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F41" s="55" t="n">
+      <x:c r="F41" s="68" t="n">
         <x:f>IF(A41=1,'6. Quellen &amp; Methodik'!B16+MIN(C41,50)*'6. Quellen &amp; Methodik'!B17+MAX(MIN(C41-50,200),0)*'6. Quellen &amp; Methodik'!B18+MAX(MIN(C41-250,750),0)*'6. Quellen &amp; Methodik'!B19+MAX(C41-1000,0)*'6. Quellen &amp; Methodik'!B20,0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G41" s="55" t="n">
+      <x:c r="G41" s="68" t="n">
         <x:f>IF(OR(A41=1,A41=13,A41=25),'6. Quellen &amp; Methodik'!B36*(C41*'1. Eingaben'!B10*12+E41+F41),0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H41" s="55" t="n">
+      <x:c r="H41" s="68" t="n">
         <x:f>SUM(D41:G41)</x:f>
         <x:v>7800</x:v>
       </x:c>
-      <x:c r="I41" s="54" t="n">
+      <x:c r="I41" s="55" t="n">
         <x:f>'4. Szenarien'!B6*(1-(1-'4. Szenarien'!B13)*POWER(0.5,(A41-1)/'4. Szenarien'!B14))</x:f>
         <x:v>7.982322330470336</x:v>
       </x:c>
-      <x:c r="J41" s="54" t="n">
+      <x:c r="J41" s="55" t="n">
         <x:f>'4. Szenarien'!B7*(1-(1-'4. Szenarien'!B13)*POWER(0.5,(A41-1)/'4. Szenarien'!B14))</x:f>
         <x:v>8.980112621779128</x:v>
       </x:c>
-      <x:c r="K41" s="55" t="n">
+      <x:c r="K41" s="68" t="n">
         <x:f>C41*I41*'4. Szenarien'!D6*'1. Eingaben'!B9</x:f>
         <x:v>59867.417478527525</x:v>
       </x:c>
-      <x:c r="L41" s="55" t="n">
+      <x:c r="L41" s="68" t="n">
         <x:f>C41*J41*'4. Szenarien'!D7*'1. Eingaben'!B9</x:f>
         <x:v>67350.84466334345</x:v>
       </x:c>
-      <x:c r="M41" s="55" t="n">
+      <x:c r="M41" s="68" t="n">
         <x:f>M40+K41-H41</x:f>
         <x:v>490874.9570245182</x:v>
       </x:c>
-      <x:c r="N41" s="55" t="n">
+      <x:c r="N41" s="68" t="n">
         <x:f>N40+L41-H41</x:f>
         <x:v>600672.326652583</x:v>
       </x:c>
-      <x:c r="O41" s="68" t="n">
+      <x:c r="O41" s="81" t="n">
         <x:f>IF(M41&gt;=0,A41,99)</x:f>
         <x:v>16</x:v>
       </x:c>
-      <x:c r="P41" s="68" t="n">
+      <x:c r="P41" s="81" t="n">
         <x:f>IF(N41&gt;=0,A41,99)</x:f>
         <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="42">
-      <x:c r="A42" s="66" t="n">
+      <x:c r="A42" s="79" t="n">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="B42" s="66" t="n">
+      <x:c r="B42" s="79" t="n">
         <x:f>INT((A42-1)/12)+1</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C42" s="66" t="n">
+      <x:c r="C42" s="79" t="n">
         <x:f>'1. Eingaben'!B8</x:f>
         <x:v>300</x:v>
       </x:c>
-      <x:c r="D42" s="55" t="n">
+      <x:c r="D42" s="68" t="n">
         <x:f>C42*'1. Eingaben'!B10</x:f>
         <x:v>7800</x:v>
       </x:c>
-      <x:c r="E42" s="55" t="n">
+      <x:c r="E42" s="68" t="n">
         <x:f>IF(A42=1,INT(('1. Eingaben'!B8+'6. Quellen &amp; Methodik'!B33-1)/'6. Quellen &amp; Methodik'!B33)*('6. Quellen &amp; Methodik'!B31+'6. Quellen &amp; Methodik'!B32*'6. Quellen &amp; Methodik'!B35),IF(OR(A42=13,A42=25),INT(('1. Eingaben'!B8+'6. Quellen &amp; Methodik'!B33-1)/'6. Quellen &amp; Methodik'!B33)*('6. Quellen &amp; Methodik'!B31+'6. Quellen &amp; Methodik'!B32*'6. Quellen &amp; Methodik'!B35)*'6. Quellen &amp; Methodik'!B34,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F42" s="55" t="n">
+      <x:c r="F42" s="68" t="n">
         <x:f>IF(A42=1,'6. Quellen &amp; Methodik'!B16+MIN(C42,50)*'6. Quellen &amp; Methodik'!B17+MAX(MIN(C42-50,200),0)*'6. Quellen &amp; Methodik'!B18+MAX(MIN(C42-250,750),0)*'6. Quellen &amp; Methodik'!B19+MAX(C42-1000,0)*'6. Quellen &amp; Methodik'!B20,0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G42" s="55" t="n">
+      <x:c r="G42" s="68" t="n">
         <x:f>IF(OR(A42=1,A42=13,A42=25),'6. Quellen &amp; Methodik'!B36*(C42*'1. Eingaben'!B10*12+E42+F42),0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H42" s="55" t="n">
+      <x:c r="H42" s="68" t="n">
         <x:f>SUM(D42:G42)</x:f>
         <x:v>7800</x:v>
       </x:c>
-      <x:c r="I42" s="54" t="n">
+      <x:c r="I42" s="55" t="n">
         <x:f>'4. Szenarien'!B6*(1-(1-'4. Szenarien'!B13)*POWER(0.5,(A42-1)/'4. Szenarien'!B14))</x:f>
         <x:v>7.9875</x:v>
       </x:c>
-      <x:c r="J42" s="54" t="n">
+      <x:c r="J42" s="55" t="n">
         <x:f>'4. Szenarien'!B7*(1-(1-'4. Szenarien'!B13)*POWER(0.5,(A42-1)/'4. Szenarien'!B14))</x:f>
         <x:v>8.9859375</x:v>
       </x:c>
-      <x:c r="K42" s="55" t="n">
+      <x:c r="K42" s="68" t="n">
         <x:f>C42*I42*'4. Szenarien'!D6*'1. Eingaben'!B9</x:f>
         <x:v>59906.25</x:v>
       </x:c>
-      <x:c r="L42" s="55" t="n">
+      <x:c r="L42" s="68" t="n">
         <x:f>C42*J42*'4. Szenarien'!D7*'1. Eingaben'!B9</x:f>
         <x:v>67394.53125</x:v>
       </x:c>
-      <x:c r="M42" s="55" t="n">
+      <x:c r="M42" s="68" t="n">
         <x:f>M41+K42-H42</x:f>
         <x:v>542981.2070245182</x:v>
       </x:c>
-      <x:c r="N42" s="55" t="n">
+      <x:c r="N42" s="68" t="n">
         <x:f>N41+L42-H42</x:f>
         <x:v>660266.857902583</x:v>
       </x:c>
-      <x:c r="O42" s="68" t="n">
+      <x:c r="O42" s="81" t="n">
         <x:f>IF(M42&gt;=0,A42,99)</x:f>
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P42" s="68" t="n">
+      <x:c r="P42" s="81" t="n">
         <x:f>IF(N42&gt;=0,A42,99)</x:f>
         <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="43">
-      <x:c r="A43" s="66" t="n">
+      <x:c r="A43" s="79" t="n">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="B43" s="66" t="n">
+      <x:c r="B43" s="79" t="n">
         <x:f>INT((A43-1)/12)+1</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C43" s="66" t="n">
+      <x:c r="C43" s="79" t="n">
         <x:f>'1. Eingaben'!B8</x:f>
         <x:v>300</x:v>
       </x:c>
-      <x:c r="D43" s="55" t="n">
+      <x:c r="D43" s="68" t="n">
         <x:f>C43*'1. Eingaben'!B10</x:f>
         <x:v>7800</x:v>
       </x:c>
-      <x:c r="E43" s="55" t="n">
+      <x:c r="E43" s="68" t="n">
         <x:f>IF(A43=1,INT(('1. Eingaben'!B8+'6. Quellen &amp; Methodik'!B33-1)/'6. Quellen &amp; Methodik'!B33)*('6. Quellen &amp; Methodik'!B31+'6. Quellen &amp; Methodik'!B32*'6. Quellen &amp; Methodik'!B35),IF(OR(A43=13,A43=25),INT(('1. Eingaben'!B8+'6. Quellen &amp; Methodik'!B33-1)/'6. Quellen &amp; Methodik'!B33)*('6. Quellen &amp; Methodik'!B31+'6. Quellen &amp; Methodik'!B32*'6. Quellen &amp; Methodik'!B35)*'6. Quellen &amp; Methodik'!B34,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F43" s="55" t="n">
+      <x:c r="F43" s="68" t="n">
         <x:f>IF(A43=1,'6. Quellen &amp; Methodik'!B16+MIN(C43,50)*'6. Quellen &amp; Methodik'!B17+MAX(MIN(C43-50,200),0)*'6. Quellen &amp; Methodik'!B18+MAX(MIN(C43-250,750),0)*'6. Quellen &amp; Methodik'!B19+MAX(C43-1000,0)*'6. Quellen &amp; Methodik'!B20,0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G43" s="55" t="n">
+      <x:c r="G43" s="68" t="n">
         <x:f>IF(OR(A43=1,A43=13,A43=25),'6. Quellen &amp; Methodik'!B36*(C43*'1. Eingaben'!B10*12+E43+F43),0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H43" s="55" t="n">
+      <x:c r="H43" s="68" t="n">
         <x:f>SUM(D43:G43)</x:f>
         <x:v>7800</x:v>
       </x:c>
-      <x:c r="I43" s="54" t="n">
+      <x:c r="I43" s="55" t="n">
         <x:f>'4. Szenarien'!B6*(1-(1-'4. Szenarien'!B13)*POWER(0.5,(A43-1)/'4. Szenarien'!B14))</x:f>
         <x:v>7.991161165235168</x:v>
       </x:c>
-      <x:c r="J43" s="54" t="n">
+      <x:c r="J43" s="55" t="n">
         <x:f>'4. Szenarien'!B7*(1-(1-'4. Szenarien'!B13)*POWER(0.5,(A43-1)/'4. Szenarien'!B14))</x:f>
         <x:v>8.990056310889564</x:v>
       </x:c>
-      <x:c r="K43" s="55" t="n">
+      <x:c r="K43" s="68" t="n">
         <x:f>C43*I43*'4. Szenarien'!D6*'1. Eingaben'!B9</x:f>
         <x:v>59933.70873926376</x:v>
       </x:c>
-      <x:c r="L43" s="55" t="n">
+      <x:c r="L43" s="68" t="n">
         <x:f>C43*J43*'4. Szenarien'!D7*'1. Eingaben'!B9</x:f>
         <x:v>67425.42233167174</x:v>
       </x:c>
-      <x:c r="M43" s="55" t="n">
+      <x:c r="M43" s="68" t="n">
         <x:f>M42+K43-H43</x:f>
         <x:v>595114.9157637819</x:v>
       </x:c>
-      <x:c r="N43" s="55" t="n">
+      <x:c r="N43" s="68" t="n">
         <x:f>N42+L43-H43</x:f>
         <x:v>719892.2802342547</x:v>
       </x:c>
-      <x:c r="O43" s="68" t="n">
+      <x:c r="O43" s="81" t="n">
         <x:f>IF(M43&gt;=0,A43,99)</x:f>
         <x:v>18</x:v>
       </x:c>
-      <x:c r="P43" s="68" t="n">
+      <x:c r="P43" s="81" t="n">
         <x:f>IF(N43&gt;=0,A43,99)</x:f>
         <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="44">
-      <x:c r="A44" s="66" t="n">
+      <x:c r="A44" s="79" t="n">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="B44" s="66" t="n">
+      <x:c r="B44" s="79" t="n">
         <x:f>INT((A44-1)/12)+1</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C44" s="66" t="n">
+      <x:c r="C44" s="79" t="n">
         <x:f>'1. Eingaben'!B8</x:f>
         <x:v>300</x:v>
       </x:c>
-      <x:c r="D44" s="55" t="n">
+      <x:c r="D44" s="68" t="n">
         <x:f>C44*'1. Eingaben'!B10</x:f>
         <x:v>7800</x:v>
       </x:c>
-      <x:c r="E44" s="55" t="n">
+      <x:c r="E44" s="68" t="n">
         <x:f>IF(A44=1,INT(('1. Eingaben'!B8+'6. Quellen &amp; Methodik'!B33-1)/'6. Quellen &amp; Methodik'!B33)*('6. Quellen &amp; Methodik'!B31+'6. Quellen &amp; Methodik'!B32*'6. Quellen &amp; Methodik'!B35),IF(OR(A44=13,A44=25),INT(('1. Eingaben'!B8+'6. Quellen &amp; Methodik'!B33-1)/'6. Quellen &amp; Methodik'!B33)*('6. Quellen &amp; Methodik'!B31+'6. Quellen &amp; Methodik'!B32*'6. Quellen &amp; Methodik'!B35)*'6. Quellen &amp; Methodik'!B34,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F44" s="55" t="n">
+      <x:c r="F44" s="68" t="n">
         <x:f>IF(A44=1,'6. Quellen &amp; Methodik'!B16+MIN(C44,50)*'6. Quellen &amp; Methodik'!B17+MAX(MIN(C44-50,200),0)*'6. Quellen &amp; Methodik'!B18+MAX(MIN(C44-250,750),0)*'6. Quellen &amp; Methodik'!B19+MAX(C44-1000,0)*'6. Quellen &amp; Methodik'!B20,0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G44" s="55" t="n">
+      <x:c r="G44" s="68" t="n">
         <x:f>IF(OR(A44=1,A44=13,A44=25),'6. Quellen &amp; Methodik'!B36*(C44*'1. Eingaben'!B10*12+E44+F44),0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H44" s="55" t="n">
+      <x:c r="H44" s="68" t="n">
         <x:f>SUM(D44:G44)</x:f>
         <x:v>7800</x:v>
       </x:c>
-      <x:c r="I44" s="54" t="n">
+      <x:c r="I44" s="55" t="n">
         <x:f>'4. Szenarien'!B6*(1-(1-'4. Szenarien'!B13)*POWER(0.5,(A44-1)/'4. Szenarien'!B14))</x:f>
         <x:v>7.99375</x:v>
       </x:c>
-      <x:c r="J44" s="54" t="n">
+      <x:c r="J44" s="55" t="n">
         <x:f>'4. Szenarien'!B7*(1-(1-'4. Szenarien'!B13)*POWER(0.5,(A44-1)/'4. Szenarien'!B14))</x:f>
         <x:v>8.992968750000001</x:v>
       </x:c>
-      <x:c r="K44" s="55" t="n">
+      <x:c r="K44" s="68" t="n">
         <x:f>C44*I44*'4. Szenarien'!D6*'1. Eingaben'!B9</x:f>
         <x:v>59953.125</x:v>
       </x:c>
-      <x:c r="L44" s="55" t="n">
+      <x:c r="L44" s="68" t="n">
         <x:f>C44*J44*'4. Szenarien'!D7*'1. Eingaben'!B9</x:f>
         <x:v>67447.26562500001</x:v>
       </x:c>
-      <x:c r="M44" s="55" t="n">
+      <x:c r="M44" s="68" t="n">
         <x:f>M43+K44-H44</x:f>
         <x:v>647268.0407637819</x:v>
       </x:c>
-      <x:c r="N44" s="55" t="n">
+      <x:c r="N44" s="68" t="n">
         <x:f>N43+L44-H44</x:f>
         <x:v>779539.5458592547</x:v>
       </x:c>
-      <x:c r="O44" s="68" t="n">
+      <x:c r="O44" s="81" t="n">
         <x:f>IF(M44&gt;=0,A44,99)</x:f>
         <x:v>19</x:v>
       </x:c>
-      <x:c r="P44" s="68" t="n">
+      <x:c r="P44" s="81" t="n">
         <x:f>IF(N44&gt;=0,A44,99)</x:f>
         <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="45">
-      <x:c r="A45" s="66" t="n">
+      <x:c r="A45" s="79" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="B45" s="66" t="n">
+      <x:c r="B45" s="79" t="n">
         <x:f>INT((A45-1)/12)+1</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C45" s="66" t="n">
+      <x:c r="C45" s="79" t="n">
         <x:f>'1. Eingaben'!B8</x:f>
         <x:v>300</x:v>
       </x:c>
-      <x:c r="D45" s="55" t="n">
+      <x:c r="D45" s="68" t="n">
         <x:f>C45*'1. Eingaben'!B10</x:f>
         <x:v>7800</x:v>
       </x:c>
-      <x:c r="E45" s="55" t="n">
+      <x:c r="E45" s="68" t="n">
         <x:f>IF(A45=1,INT(('1. Eingaben'!B8+'6. Quellen &amp; Methodik'!B33-1)/'6. Quellen &amp; Methodik'!B33)*('6. Quellen &amp; Methodik'!B31+'6. Quellen &amp; Methodik'!B32*'6. Quellen &amp; Methodik'!B35),IF(OR(A45=13,A45=25),INT(('1. Eingaben'!B8+'6. Quellen &amp; Methodik'!B33-1)/'6. Quellen &amp; Methodik'!B33)*('6. Quellen &amp; Methodik'!B31+'6. Quellen &amp; Methodik'!B32*'6. Quellen &amp; Methodik'!B35)*'6. Quellen &amp; Methodik'!B34,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F45" s="55" t="n">
+      <x:c r="F45" s="68" t="n">
         <x:f>IF(A45=1,'6. Quellen &amp; Methodik'!B16+MIN(C45,50)*'6. Quellen &amp; Methodik'!B17+MAX(MIN(C45-50,200),0)*'6. Quellen &amp; Methodik'!B18+MAX(MIN(C45-250,750),0)*'6. Quellen &amp; Methodik'!B19+MAX(C45-1000,0)*'6. Quellen &amp; Methodik'!B20,0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G45" s="55" t="n">
+      <x:c r="G45" s="68" t="n">
         <x:f>IF(OR(A45=1,A45=13,A45=25),'6. Quellen &amp; Methodik'!B36*(C45*'1. Eingaben'!B10*12+E45+F45),0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H45" s="55" t="n">
+      <x:c r="H45" s="68" t="n">
         <x:f>SUM(D45:G45)</x:f>
         <x:v>7800</x:v>
       </x:c>
-      <x:c r="I45" s="54" t="n">
+      <x:c r="I45" s="55" t="n">
         <x:f>'4. Szenarien'!B6*(1-(1-'4. Szenarien'!B13)*POWER(0.5,(A45-1)/'4. Szenarien'!B14))</x:f>
         <x:v>7.995580582617584</x:v>
       </x:c>
-      <x:c r="J45" s="54" t="n">
+      <x:c r="J45" s="55" t="n">
         <x:f>'4. Szenarien'!B7*(1-(1-'4. Szenarien'!B13)*POWER(0.5,(A45-1)/'4. Szenarien'!B14))</x:f>
         <x:v>8.995028155444782</x:v>
       </x:c>
-      <x:c r="K45" s="55" t="n">
+      <x:c r="K45" s="68" t="n">
         <x:f>C45*I45*'4. Szenarien'!D6*'1. Eingaben'!B9</x:f>
         <x:v>59966.85436963188</x:v>
       </x:c>
-      <x:c r="L45" s="55" t="n">
+      <x:c r="L45" s="68" t="n">
         <x:f>C45*J45*'4. Szenarien'!D7*'1. Eingaben'!B9</x:f>
         <x:v>67462.71116583586</x:v>
       </x:c>
-      <x:c r="M45" s="55" t="n">
+      <x:c r="M45" s="68" t="n">
         <x:f>M44+K45-H45</x:f>
         <x:v>699434.8951334137</x:v>
       </x:c>
-      <x:c r="N45" s="55" t="n">
+      <x:c r="N45" s="68" t="n">
         <x:f>N44+L45-H45</x:f>
         <x:v>839202.2570250905</x:v>
       </x:c>
-      <x:c r="O45" s="68" t="n">
+      <x:c r="O45" s="81" t="n">
         <x:f>IF(M45&gt;=0,A45,99)</x:f>
         <x:v>20</x:v>
       </x:c>
-      <x:c r="P45" s="68" t="n">
+      <x:c r="P45" s="81" t="n">
         <x:f>IF(N45&gt;=0,A45,99)</x:f>
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="46">
-      <x:c r="A46" s="66" t="n">
+      <x:c r="A46" s="79" t="n">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="B46" s="66" t="n">
+      <x:c r="B46" s="79" t="n">
         <x:f>INT((A46-1)/12)+1</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C46" s="66" t="n">
+      <x:c r="C46" s="79" t="n">
         <x:f>'1. Eingaben'!B8</x:f>
         <x:v>300</x:v>
       </x:c>
-      <x:c r="D46" s="55" t="n">
+      <x:c r="D46" s="68" t="n">
         <x:f>C46*'1. Eingaben'!B10</x:f>
         <x:v>7800</x:v>
       </x:c>
-      <x:c r="E46" s="55" t="n">
+      <x:c r="E46" s="68" t="n">
         <x:f>IF(A46=1,INT(('1. Eingaben'!B8+'6. Quellen &amp; Methodik'!B33-1)/'6. Quellen &amp; Methodik'!B33)*('6. Quellen &amp; Methodik'!B31+'6. Quellen &amp; Methodik'!B32*'6. Quellen &amp; Methodik'!B35),IF(OR(A46=13,A46=25),INT(('1. Eingaben'!B8+'6. Quellen &amp; Methodik'!B33-1)/'6. Quellen &amp; Methodik'!B33)*('6. Quellen &amp; Methodik'!B31+'6. Quellen &amp; Methodik'!B32*'6. Quellen &amp; Methodik'!B35)*'6. Quellen &amp; Methodik'!B34,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F46" s="55" t="n">
+      <x:c r="F46" s="68" t="n">
         <x:f>IF(A46=1,'6. Quellen &amp; Methodik'!B16+MIN(C46,50)*'6. Quellen &amp; Methodik'!B17+MAX(MIN(C46-50,200),0)*'6. Quellen &amp; Methodik'!B18+MAX(MIN(C46-250,750),0)*'6. Quellen &amp; Methodik'!B19+MAX(C46-1000,0)*'6. Quellen &amp; Methodik'!B20,0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G46" s="55" t="n">
+      <x:c r="G46" s="68" t="n">
         <x:f>IF(OR(A46=1,A46=13,A46=25),'6. Quellen &amp; Methodik'!B36*(C46*'1. Eingaben'!B10*12+E46+F46),0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H46" s="55" t="n">
+      <x:c r="H46" s="68" t="n">
         <x:f>SUM(D46:G46)</x:f>
         <x:v>7800</x:v>
       </x:c>
-      <x:c r="I46" s="54" t="n">
+      <x:c r="I46" s="55" t="n">
         <x:f>'4. Szenarien'!B6*(1-(1-'4. Szenarien'!B13)*POWER(0.5,(A46-1)/'4. Szenarien'!B14))</x:f>
         <x:v>7.996875</x:v>
       </x:c>
-      <x:c r="J46" s="54" t="n">
+      <x:c r="J46" s="55" t="n">
         <x:f>'4. Szenarien'!B7*(1-(1-'4. Szenarien'!B13)*POWER(0.5,(A46-1)/'4. Szenarien'!B14))</x:f>
         <x:v>8.996484375</x:v>
       </x:c>
-      <x:c r="K46" s="55" t="n">
+      <x:c r="K46" s="68" t="n">
         <x:f>C46*I46*'4. Szenarien'!D6*'1. Eingaben'!B9</x:f>
         <x:v>59976.5625</x:v>
       </x:c>
-      <x:c r="L46" s="55" t="n">
+      <x:c r="L46" s="68" t="n">
         <x:f>C46*J46*'4. Szenarien'!D7*'1. Eingaben'!B9</x:f>
         <x:v>67473.6328125</x:v>
       </x:c>
-      <x:c r="M46" s="55" t="n">
+      <x:c r="M46" s="68" t="n">
         <x:f>M45+K46-H46</x:f>
         <x:v>751611.4576334137</x:v>
       </x:c>
-      <x:c r="N46" s="55" t="n">
+      <x:c r="N46" s="68" t="n">
         <x:f>N45+L46-H46</x:f>
         <x:v>898875.8898375905</x:v>
       </x:c>
-      <x:c r="O46" s="68" t="n">
+      <x:c r="O46" s="81" t="n">
         <x:f>IF(M46&gt;=0,A46,99)</x:f>
         <x:v>21</x:v>
       </x:c>
-      <x:c r="P46" s="68" t="n">
+      <x:c r="P46" s="81" t="n">
         <x:f>IF(N46&gt;=0,A46,99)</x:f>
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="47">
-      <x:c r="A47" s="66" t="n">
+      <x:c r="A47" s="79" t="n">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="B47" s="66" t="n">
+      <x:c r="B47" s="79" t="n">
         <x:f>INT((A47-1)/12)+1</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C47" s="66" t="n">
+      <x:c r="C47" s="79" t="n">
         <x:f>'1. Eingaben'!B8</x:f>
         <x:v>300</x:v>
       </x:c>
-      <x:c r="D47" s="55" t="n">
+      <x:c r="D47" s="68" t="n">
         <x:f>C47*'1. Eingaben'!B10</x:f>
         <x:v>7800</x:v>
       </x:c>
-      <x:c r="E47" s="55" t="n">
+      <x:c r="E47" s="68" t="n">
         <x:f>IF(A47=1,INT(('1. Eingaben'!B8+'6. Quellen &amp; Methodik'!B33-1)/'6. Quellen &amp; Methodik'!B33)*('6. Quellen &amp; Methodik'!B31+'6. Quellen &amp; Methodik'!B32*'6. Quellen &amp; Methodik'!B35),IF(OR(A47=13,A47=25),INT(('1. Eingaben'!B8+'6. Quellen &amp; Methodik'!B33-1)/'6. Quellen &amp; Methodik'!B33)*('6. Quellen &amp; Methodik'!B31+'6. Quellen &amp; Methodik'!B32*'6. Quellen &amp; Methodik'!B35)*'6. Quellen &amp; Methodik'!B34,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F47" s="55" t="n">
+      <x:c r="F47" s="68" t="n">
         <x:f>IF(A47=1,'6. Quellen &amp; Methodik'!B16+MIN(C47,50)*'6. Quellen &amp; Methodik'!B17+MAX(MIN(C47-50,200),0)*'6. Quellen &amp; Methodik'!B18+MAX(MIN(C47-250,750),0)*'6. Quellen &amp; Methodik'!B19+MAX(C47-1000,0)*'6. Quellen &amp; Methodik'!B20,0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G47" s="55" t="n">
+      <x:c r="G47" s="68" t="n">
         <x:f>IF(OR(A47=1,A47=13,A47=25),'6. Quellen &amp; Methodik'!B36*(C47*'1. Eingaben'!B10*12+E47+F47),0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H47" s="55" t="n">
+      <x:c r="H47" s="68" t="n">
         <x:f>SUM(D47:G47)</x:f>
         <x:v>7800</x:v>
       </x:c>
-      <x:c r="I47" s="54" t="n">
+      <x:c r="I47" s="55" t="n">
         <x:f>'4. Szenarien'!B6*(1-(1-'4. Szenarien'!B13)*POWER(0.5,(A47-1)/'4. Szenarien'!B14))</x:f>
         <x:v>7.997790291308792</x:v>
       </x:c>
-      <x:c r="J47" s="54" t="n">
+      <x:c r="J47" s="55" t="n">
         <x:f>'4. Szenarien'!B7*(1-(1-'4. Szenarien'!B13)*POWER(0.5,(A47-1)/'4. Szenarien'!B14))</x:f>
         <x:v>8.997514077722391</x:v>
       </x:c>
-      <x:c r="K47" s="55" t="n">
+      <x:c r="K47" s="68" t="n">
         <x:f>C47*I47*'4. Szenarien'!D6*'1. Eingaben'!B9</x:f>
         <x:v>59983.42718481595</x:v>
       </x:c>
-      <x:c r="L47" s="55" t="n">
+      <x:c r="L47" s="68" t="n">
         <x:f>C47*J47*'4. Szenarien'!D7*'1. Eingaben'!B9</x:f>
         <x:v>67481.35558291794</x:v>
       </x:c>
-      <x:c r="M47" s="55" t="n">
+      <x:c r="M47" s="68" t="n">
         <x:f>M46+K47-H47</x:f>
         <x:v>803794.8848182297</x:v>
       </x:c>
-      <x:c r="N47" s="55" t="n">
+      <x:c r="N47" s="68" t="n">
         <x:f>N46+L47-H47</x:f>
         <x:v>958557.2454205084</x:v>
       </x:c>
-      <x:c r="O47" s="68" t="n">
+      <x:c r="O47" s="81" t="n">
         <x:f>IF(M47&gt;=0,A47,99)</x:f>
         <x:v>22</x:v>
       </x:c>
-      <x:c r="P47" s="68" t="n">
+      <x:c r="P47" s="81" t="n">
         <x:f>IF(N47&gt;=0,A47,99)</x:f>
         <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="48">
-      <x:c r="A48" s="66" t="n">
+      <x:c r="A48" s="79" t="n">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="B48" s="66" t="n">
+      <x:c r="B48" s="79" t="n">
         <x:f>INT((A48-1)/12)+1</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C48" s="66" t="n">
+      <x:c r="C48" s="79" t="n">
         <x:f>'1. Eingaben'!B8</x:f>
         <x:v>300</x:v>
       </x:c>
-      <x:c r="D48" s="55" t="n">
+      <x:c r="D48" s="68" t="n">
         <x:f>C48*'1. Eingaben'!B10</x:f>
         <x:v>7800</x:v>
       </x:c>
-      <x:c r="E48" s="55" t="n">
+      <x:c r="E48" s="68" t="n">
         <x:f>IF(A48=1,INT(('1. Eingaben'!B8+'6. Quellen &amp; Methodik'!B33-1)/'6. Quellen &amp; Methodik'!B33)*('6. Quellen &amp; Methodik'!B31+'6. Quellen &amp; Methodik'!B32*'6. Quellen &amp; Methodik'!B35),IF(OR(A48=13,A48=25),INT(('1. Eingaben'!B8+'6. Quellen &amp; Methodik'!B33-1)/'6. Quellen &amp; Methodik'!B33)*('6. Quellen &amp; Methodik'!B31+'6. Quellen &amp; Methodik'!B32*'6. Quellen &amp; Methodik'!B35)*'6. Quellen &amp; Methodik'!B34,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F48" s="55" t="n">
+      <x:c r="F48" s="68" t="n">
         <x:f>IF(A48=1,'6. Quellen &amp; Methodik'!B16+MIN(C48,50)*'6. Quellen &amp; Methodik'!B17+MAX(MIN(C48-50,200),0)*'6. Quellen &amp; Methodik'!B18+MAX(MIN(C48-250,750),0)*'6. Quellen &amp; Methodik'!B19+MAX(C48-1000,0)*'6. Quellen &amp; Methodik'!B20,0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G48" s="55" t="n">
+      <x:c r="G48" s="68" t="n">
         <x:f>IF(OR(A48=1,A48=13,A48=25),'6. Quellen &amp; Methodik'!B36*(C48*'1. Eingaben'!B10*12+E48+F48),0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H48" s="55" t="n">
+      <x:c r="H48" s="68" t="n">
         <x:f>SUM(D48:G48)</x:f>
         <x:v>7800</x:v>
       </x:c>
-      <x:c r="I48" s="54" t="n">
+      <x:c r="I48" s="55" t="n">
         <x:f>'4. Szenarien'!B6*(1-(1-'4. Szenarien'!B13)*POWER(0.5,(A48-1)/'4. Szenarien'!B14))</x:f>
         <x:v>7.9984375</x:v>
       </x:c>
-      <x:c r="J48" s="54" t="n">
+      <x:c r="J48" s="55" t="n">
         <x:f>'4. Szenarien'!B7*(1-(1-'4. Szenarien'!B13)*POWER(0.5,(A48-1)/'4. Szenarien'!B14))</x:f>
         <x:v>8.998242187499999</x:v>
       </x:c>
-      <x:c r="K48" s="55" t="n">
+      <x:c r="K48" s="68" t="n">
         <x:f>C48*I48*'4. Szenarien'!D6*'1. Eingaben'!B9</x:f>
         <x:v>59988.28125</x:v>
       </x:c>
-      <x:c r="L48" s="55" t="n">
+      <x:c r="L48" s="68" t="n">
         <x:f>C48*J48*'4. Szenarien'!D7*'1. Eingaben'!B9</x:f>
         <x:v>67486.81640624999</x:v>
       </x:c>
-      <x:c r="M48" s="55" t="n">
+      <x:c r="M48" s="68" t="n">
         <x:f>M47+K48-H48</x:f>
         <x:v>855983.1660682297</x:v>
       </x:c>
-      <x:c r="N48" s="55" t="n">
+      <x:c r="N48" s="68" t="n">
         <x:f>N47+L48-H48</x:f>
         <x:v>1018244.0618267584</x:v>
       </x:c>
-      <x:c r="O48" s="68" t="n">
+      <x:c r="O48" s="81" t="n">
         <x:f>IF(M48&gt;=0,A48,99)</x:f>
         <x:v>23</x:v>
       </x:c>
-      <x:c r="P48" s="68" t="n">
+      <x:c r="P48" s="81" t="n">
         <x:f>IF(N48&gt;=0,A48,99)</x:f>
         <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="49">
-      <x:c r="A49" s="66" t="n">
+      <x:c r="A49" s="79" t="n">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="B49" s="66" t="n">
+      <x:c r="B49" s="79" t="n">
         <x:f>INT((A49-1)/12)+1</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C49" s="66" t="n">
+      <x:c r="C49" s="79" t="n">
         <x:f>'1. Eingaben'!B8</x:f>
         <x:v>300</x:v>
       </x:c>
-      <x:c r="D49" s="55" t="n">
+      <x:c r="D49" s="68" t="n">
         <x:f>C49*'1. Eingaben'!B10</x:f>
         <x:v>7800</x:v>
       </x:c>
-      <x:c r="E49" s="55" t="n">
+      <x:c r="E49" s="68" t="n">
         <x:f>IF(A49=1,INT(('1. Eingaben'!B8+'6. Quellen &amp; Methodik'!B33-1)/'6. Quellen &amp; Methodik'!B33)*('6. Quellen &amp; Methodik'!B31+'6. Quellen &amp; Methodik'!B32*'6. Quellen &amp; Methodik'!B35),IF(OR(A49=13,A49=25),INT(('1. Eingaben'!B8+'6. Quellen &amp; Methodik'!B33-1)/'6. Quellen &amp; Methodik'!B33)*('6. Quellen &amp; Methodik'!B31+'6. Quellen &amp; Methodik'!B32*'6. Quellen &amp; Methodik'!B35)*'6. Quellen &amp; Methodik'!B34,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F49" s="55" t="n">
+      <x:c r="F49" s="68" t="n">
         <x:f>IF(A49=1,'6. Quellen &amp; Methodik'!B16+MIN(C49,50)*'6. Quellen &amp; Methodik'!B17+MAX(MIN(C49-50,200),0)*'6. Quellen &amp; Methodik'!B18+MAX(MIN(C49-250,750),0)*'6. Quellen &amp; Methodik'!B19+MAX(C49-1000,0)*'6. Quellen &amp; Methodik'!B20,0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G49" s="55" t="n">
+      <x:c r="G49" s="68" t="n">
         <x:f>IF(OR(A49=1,A49=13,A49=25),'6. Quellen &amp; Methodik'!B36*(C49*'1. Eingaben'!B10*12+E49+F49),0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H49" s="55" t="n">
+      <x:c r="H49" s="68" t="n">
         <x:f>SUM(D49:G49)</x:f>
         <x:v>7800</x:v>
       </x:c>
-      <x:c r="I49" s="54" t="n">
+      <x:c r="I49" s="55" t="n">
         <x:f>'4. Szenarien'!B6*(1-(1-'4. Szenarien'!B13)*POWER(0.5,(A49-1)/'4. Szenarien'!B14))</x:f>
         <x:v>7.998895145654396</x:v>
       </x:c>
-      <x:c r="J49" s="54" t="n">
+      <x:c r="J49" s="55" t="n">
         <x:f>'4. Szenarien'!B7*(1-(1-'4. Szenarien'!B13)*POWER(0.5,(A49-1)/'4. Szenarien'!B14))</x:f>
         <x:v>8.998757038861196</x:v>
       </x:c>
-      <x:c r="K49" s="55" t="n">
+      <x:c r="K49" s="68" t="n">
         <x:f>C49*I49*'4. Szenarien'!D6*'1. Eingaben'!B9</x:f>
         <x:v>59991.71359240797</x:v>
       </x:c>
-      <x:c r="L49" s="55" t="n">
+      <x:c r="L49" s="68" t="n">
         <x:f>C49*J49*'4. Szenarien'!D7*'1. Eingaben'!B9</x:f>
         <x:v>67490.67779145898</x:v>
       </x:c>
-      <x:c r="M49" s="55" t="n">
+      <x:c r="M49" s="68" t="n">
         <x:f>M48+K49-H49</x:f>
         <x:v>908174.8796606377</x:v>
       </x:c>
-      <x:c r="N49" s="55" t="n">
+      <x:c r="N49" s="68" t="n">
         <x:f>N48+L49-H49</x:f>
         <x:v>1077934.7396182173</x:v>
       </x:c>
-      <x:c r="O49" s="68" t="n">
+      <x:c r="O49" s="81" t="n">
         <x:f>IF(M49&gt;=0,A49,99)</x:f>
         <x:v>24</x:v>
       </x:c>
-      <x:c r="P49" s="68" t="n">
+      <x:c r="P49" s="81" t="n">
         <x:f>IF(N49&gt;=0,A49,99)</x:f>
         <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="50">
-      <x:c r="A50" s="66" t="n">
+      <x:c r="A50" s="79" t="n">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="B50" s="66" t="n">
+      <x:c r="B50" s="79" t="n">
         <x:f>INT((A50-1)/12)+1</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C50" s="66" t="n">
+      <x:c r="C50" s="79" t="n">
         <x:f>'1. Eingaben'!B8</x:f>
         <x:v>300</x:v>
       </x:c>
-      <x:c r="D50" s="55" t="n">
+      <x:c r="D50" s="68" t="n">
         <x:f>C50*'1. Eingaben'!B10</x:f>
         <x:v>7800</x:v>
       </x:c>
-      <x:c r="E50" s="55" t="n">
+      <x:c r="E50" s="68" t="n">
         <x:f>IF(A50=1,INT(('1. Eingaben'!B8+'6. Quellen &amp; Methodik'!B33-1)/'6. Quellen &amp; Methodik'!B33)*('6. Quellen &amp; Methodik'!B31+'6. Quellen &amp; Methodik'!B32*'6. Quellen &amp; Methodik'!B35),IF(OR(A50=13,A50=25),INT(('1. Eingaben'!B8+'6. Quellen &amp; Methodik'!B33-1)/'6. Quellen &amp; Methodik'!B33)*('6. Quellen &amp; Methodik'!B31+'6. Quellen &amp; Methodik'!B32*'6. Quellen &amp; Methodik'!B35)*'6. Quellen &amp; Methodik'!B34,0))</x:f>
         <x:v>62500</x:v>
       </x:c>
-      <x:c r="F50" s="55" t="n">
+      <x:c r="F50" s="68" t="n">
         <x:f>IF(A50=1,'6. Quellen &amp; Methodik'!B16+MIN(C50,50)*'6. Quellen &amp; Methodik'!B17+MAX(MIN(C50-50,200),0)*'6. Quellen &amp; Methodik'!B18+MAX(MIN(C50-250,750),0)*'6. Quellen &amp; Methodik'!B19+MAX(C50-1000,0)*'6. Quellen &amp; Methodik'!B20,0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G50" s="55" t="n">
+      <x:c r="G50" s="68" t="n">
         <x:f>IF(OR(A50=1,A50=13,A50=25),'6. Quellen &amp; Methodik'!B36*(C50*'1. Eingaben'!B10*12+E50+F50),0)</x:f>
         <x:v>18732</x:v>
       </x:c>
-      <x:c r="H50" s="55" t="n">
+      <x:c r="H50" s="68" t="n">
         <x:f>SUM(D50:G50)</x:f>
         <x:v>89032</x:v>
       </x:c>
-      <x:c r="I50" s="54" t="n">
+      <x:c r="I50" s="55" t="n">
         <x:f>'4. Szenarien'!B6*(1-(1-'4. Szenarien'!B13)*POWER(0.5,(A50-1)/'4. Szenarien'!B14))</x:f>
         <x:v>7.99921875</x:v>
       </x:c>
-      <x:c r="J50" s="54" t="n">
+      <x:c r="J50" s="55" t="n">
         <x:f>'4. Szenarien'!B7*(1-(1-'4. Szenarien'!B13)*POWER(0.5,(A50-1)/'4. Szenarien'!B14))</x:f>
         <x:v>8.99912109375</x:v>
       </x:c>
-      <x:c r="K50" s="55" t="n">
+      <x:c r="K50" s="68" t="n">
         <x:f>C50*I50*'4. Szenarien'!D6*'1. Eingaben'!B9</x:f>
         <x:v>59994.140625</x:v>
       </x:c>
-      <x:c r="L50" s="55" t="n">
+      <x:c r="L50" s="68" t="n">
         <x:f>C50*J50*'4. Szenarien'!D7*'1. Eingaben'!B9</x:f>
         <x:v>67493.408203125</x:v>
       </x:c>
-      <x:c r="M50" s="55" t="n">
+      <x:c r="M50" s="68" t="n">
         <x:f>M49+K50-H50</x:f>
         <x:v>879137.0202856377</x:v>
       </x:c>
-      <x:c r="N50" s="55" t="n">
+      <x:c r="N50" s="68" t="n">
         <x:f>N49+L50-H50</x:f>
         <x:v>1056396.1478213423</x:v>
       </x:c>
-      <x:c r="O50" s="68" t="n">
+      <x:c r="O50" s="81" t="n">
         <x:f>IF(M50&gt;=0,A50,99)</x:f>
         <x:v>25</x:v>
       </x:c>
-      <x:c r="P50" s="68" t="n">
+      <x:c r="P50" s="81" t="n">
         <x:f>IF(N50&gt;=0,A50,99)</x:f>
         <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="51">
-      <x:c r="A51" s="66" t="n">
+      <x:c r="A51" s="79" t="n">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="B51" s="66" t="n">
+      <x:c r="B51" s="79" t="n">
         <x:f>INT((A51-1)/12)+1</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C51" s="66" t="n">
+      <x:c r="C51" s="79" t="n">
         <x:f>'1. Eingaben'!B8</x:f>
         <x:v>300</x:v>
       </x:c>
-      <x:c r="D51" s="55" t="n">
+      <x:c r="D51" s="68" t="n">
         <x:f>C51*'1. Eingaben'!B10</x:f>
         <x:v>7800</x:v>
       </x:c>
-      <x:c r="E51" s="55" t="n">
+      <x:c r="E51" s="68" t="n">
         <x:f>IF(A51=1,INT(('1. Eingaben'!B8+'6. Quellen &amp; Methodik'!B33-1)/'6. Quellen &amp; Methodik'!B33)*('6. Quellen &amp; Methodik'!B31+'6. Quellen &amp; Methodik'!B32*'6. Quellen &amp; Methodik'!B35),IF(OR(A51=13,A51=25),INT(('1. Eingaben'!B8+'6. Quellen &amp; Methodik'!B33-1)/'6. Quellen &amp; Methodik'!B33)*('6. Quellen &amp; Methodik'!B31+'6. Quellen &amp; Methodik'!B32*'6. Quellen &amp; Methodik'!B35)*'6. Quellen &amp; Methodik'!B34,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F51" s="55" t="n">
+      <x:c r="F51" s="68" t="n">
         <x:f>IF(A51=1,'6. Quellen &amp; Methodik'!B16+MIN(C51,50)*'6. Quellen &amp; Methodik'!B17+MAX(MIN(C51-50,200),0)*'6. Quellen &amp; Methodik'!B18+MAX(MIN(C51-250,750),0)*'6. Quellen &amp; Methodik'!B19+MAX(C51-1000,0)*'6. Quellen &amp; Methodik'!B20,0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G51" s="55" t="n">
+      <x:c r="G51" s="68" t="n">
         <x:f>IF(OR(A51=1,A51=13,A51=25),'6. Quellen &amp; Methodik'!B36*(C51*'1. Eingaben'!B10*12+E51+F51),0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H51" s="55" t="n">
+      <x:c r="H51" s="68" t="n">
         <x:f>SUM(D51:G51)</x:f>
         <x:v>7800</x:v>
       </x:c>
-      <x:c r="I51" s="54" t="n">
+      <x:c r="I51" s="55" t="n">
         <x:f>'4. Szenarien'!B6*(1-(1-'4. Szenarien'!B13)*POWER(0.5,(A51-1)/'4. Szenarien'!B14))</x:f>
         <x:v>7.999447572827198</x:v>
       </x:c>
-      <x:c r="J51" s="54" t="n">
+      <x:c r="J51" s="55" t="n">
         <x:f>'4. Szenarien'!B7*(1-(1-'4. Szenarien'!B13)*POWER(0.5,(A51-1)/'4. Szenarien'!B14))</x:f>
         <x:v>8.999378519430598</x:v>
       </x:c>
-      <x:c r="K51" s="55" t="n">
+      <x:c r="K51" s="68" t="n">
         <x:f>C51*I51*'4. Szenarien'!D6*'1. Eingaben'!B9</x:f>
         <x:v>59995.85679620399</x:v>
       </x:c>
-      <x:c r="L51" s="55" t="n">
+      <x:c r="L51" s="68" t="n">
         <x:f>C51*J51*'4. Szenarien'!D7*'1. Eingaben'!B9</x:f>
         <x:v>67495.3388957295</x:v>
       </x:c>
-      <x:c r="M51" s="55" t="n">
+      <x:c r="M51" s="68" t="n">
         <x:f>M50+K51-H51</x:f>
         <x:v>931332.8770818417</x:v>
       </x:c>
-      <x:c r="N51" s="55" t="n">
+      <x:c r="N51" s="68" t="n">
         <x:f>N50+L51-H51</x:f>
         <x:v>1116091.4867170718</x:v>
       </x:c>
-      <x:c r="O51" s="68" t="n">
+      <x:c r="O51" s="81" t="n">
         <x:f>IF(M51&gt;=0,A51,99)</x:f>
         <x:v>26</x:v>
       </x:c>
-      <x:c r="P51" s="68" t="n">
+      <x:c r="P51" s="81" t="n">
         <x:f>IF(N51&gt;=0,A51,99)</x:f>
         <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="52">
-      <x:c r="A52" s="66" t="n">
+      <x:c r="A52" s="79" t="n">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="B52" s="66" t="n">
+      <x:c r="B52" s="79" t="n">
         <x:f>INT((A52-1)/12)+1</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C52" s="66" t="n">
+      <x:c r="C52" s="79" t="n">
         <x:f>'1. Eingaben'!B8</x:f>
         <x:v>300</x:v>
       </x:c>
-      <x:c r="D52" s="55" t="n">
+      <x:c r="D52" s="68" t="n">
         <x:f>C52*'1. Eingaben'!B10</x:f>
         <x:v>7800</x:v>
       </x:c>
-      <x:c r="E52" s="55" t="n">
+      <x:c r="E52" s="68" t="n">
         <x:f>IF(A52=1,INT(('1. Eingaben'!B8+'6. Quellen &amp; Methodik'!B33-1)/'6. Quellen &amp; Methodik'!B33)*('6. Quellen &amp; Methodik'!B31+'6. Quellen &amp; Methodik'!B32*'6. Quellen &amp; Methodik'!B35),IF(OR(A52=13,A52=25),INT(('1. Eingaben'!B8+'6. Quellen &amp; Methodik'!B33-1)/'6. Quellen &amp; Methodik'!B33)*('6. Quellen &amp; Methodik'!B31+'6. Quellen &amp; Methodik'!B32*'6. Quellen &amp; Methodik'!B35)*'6. Quellen &amp; Methodik'!B34,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F52" s="55" t="n">
+      <x:c r="F52" s="68" t="n">
         <x:f>IF(A52=1,'6. Quellen &amp; Methodik'!B16+MIN(C52,50)*'6. Quellen &amp; Methodik'!B17+MAX(MIN(C52-50,200),0)*'6. Quellen &amp; Methodik'!B18+MAX(MIN(C52-250,750),0)*'6. Quellen &amp; Methodik'!B19+MAX(C52-1000,0)*'6. Quellen &amp; Methodik'!B20,0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G52" s="55" t="n">
+      <x:c r="G52" s="68" t="n">
         <x:f>IF(OR(A52=1,A52=13,A52=25),'6. Quellen &amp; Methodik'!B36*(C52*'1. Eingaben'!B10*12+E52+F52),0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H52" s="55" t="n">
+      <x:c r="H52" s="68" t="n">
         <x:f>SUM(D52:G52)</x:f>
         <x:v>7800</x:v>
       </x:c>
-      <x:c r="I52" s="54" t="n">
+      <x:c r="I52" s="55" t="n">
         <x:f>'4. Szenarien'!B6*(1-(1-'4. Szenarien'!B13)*POWER(0.5,(A52-1)/'4. Szenarien'!B14))</x:f>
         <x:v>7.999609375</x:v>
       </x:c>
-      <x:c r="J52" s="54" t="n">
+      <x:c r="J52" s="55" t="n">
         <x:f>'4. Szenarien'!B7*(1-(1-'4. Szenarien'!B13)*POWER(0.5,(A52-1)/'4. Szenarien'!B14))</x:f>
         <x:v>8.999560546875001</x:v>
       </x:c>
-      <x:c r="K52" s="55" t="n">
+      <x:c r="K52" s="68" t="n">
         <x:f>C52*I52*'4. Szenarien'!D6*'1. Eingaben'!B9</x:f>
         <x:v>59997.0703125</x:v>
       </x:c>
-      <x:c r="L52" s="55" t="n">
+      <x:c r="L52" s="68" t="n">
         <x:f>C52*J52*'4. Szenarien'!D7*'1. Eingaben'!B9</x:f>
         <x:v>67496.70410156251</x:v>
       </x:c>
-      <x:c r="M52" s="55" t="n">
+      <x:c r="M52" s="68" t="n">
         <x:f>M51+K52-H52</x:f>
         <x:v>983529.9473943417</x:v>
       </x:c>
-      <x:c r="N52" s="55" t="n">
+      <x:c r="N52" s="68" t="n">
         <x:f>N51+L52-H52</x:f>
         <x:v>1175788.1908186343</x:v>
       </x:c>
-      <x:c r="O52" s="68" t="n">
+      <x:c r="O52" s="81" t="n">
         <x:f>IF(M52&gt;=0,A52,99)</x:f>
         <x:v>27</x:v>
       </x:c>
-      <x:c r="P52" s="68" t="n">
+      <x:c r="P52" s="81" t="n">
         <x:f>IF(N52&gt;=0,A52,99)</x:f>
         <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="53">
-      <x:c r="A53" s="66" t="n">
+      <x:c r="A53" s="79" t="n">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="B53" s="66" t="n">
+      <x:c r="B53" s="79" t="n">
         <x:f>INT((A53-1)/12)+1</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C53" s="66" t="n">
+      <x:c r="C53" s="79" t="n">
         <x:f>'1. Eingaben'!B8</x:f>
         <x:v>300</x:v>
       </x:c>
-      <x:c r="D53" s="55" t="n">
+      <x:c r="D53" s="68" t="n">
         <x:f>C53*'1. Eingaben'!B10</x:f>
         <x:v>7800</x:v>
       </x:c>
-      <x:c r="E53" s="55" t="n">
+      <x:c r="E53" s="68" t="n">
         <x:f>IF(A53=1,INT(('1. Eingaben'!B8+'6. Quellen &amp; Methodik'!B33-1)/'6. Quellen &amp; Methodik'!B33)*('6. Quellen &amp; Methodik'!B31+'6. Quellen &amp; Methodik'!B32*'6. Quellen &amp; Methodik'!B35),IF(OR(A53=13,A53=25),INT(('1. Eingaben'!B8+'6. Quellen &amp; Methodik'!B33-1)/'6. Quellen &amp; Methodik'!B33)*('6. Quellen &amp; Methodik'!B31+'6. Quellen &amp; Methodik'!B32*'6. Quellen &amp; Methodik'!B35)*'6. Quellen &amp; Methodik'!B34,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F53" s="55" t="n">
+      <x:c r="F53" s="68" t="n">
         <x:f>IF(A53=1,'6. Quellen &amp; Methodik'!B16+MIN(C53,50)*'6. Quellen &amp; Methodik'!B17+MAX(MIN(C53-50,200),0)*'6. Quellen &amp; Methodik'!B18+MAX(MIN(C53-250,750),0)*'6. Quellen &amp; Methodik'!B19+MAX(C53-1000,0)*'6. Quellen &amp; Methodik'!B20,0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G53" s="55" t="n">
+      <x:c r="G53" s="68" t="n">
         <x:f>IF(OR(A53=1,A53=13,A53=25),'6. Quellen &amp; Methodik'!B36*(C53*'1. Eingaben'!B10*12+E53+F53),0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H53" s="55" t="n">
+      <x:c r="H53" s="68" t="n">
         <x:f>SUM(D53:G53)</x:f>
         <x:v>7800</x:v>
       </x:c>
-      <x:c r="I53" s="54" t="n">
+      <x:c r="I53" s="55" t="n">
         <x:f>'4. Szenarien'!B6*(1-(1-'4. Szenarien'!B13)*POWER(0.5,(A53-1)/'4. Szenarien'!B14))</x:f>
         <x:v>7.999723786413599</x:v>
       </x:c>
-      <x:c r="J53" s="54" t="n">
+      <x:c r="J53" s="55" t="n">
         <x:f>'4. Szenarien'!B7*(1-(1-'4. Szenarien'!B13)*POWER(0.5,(A53-1)/'4. Szenarien'!B14))</x:f>
         <x:v>8.999689259715298</x:v>
       </x:c>
-      <x:c r="K53" s="55" t="n">
+      <x:c r="K53" s="68" t="n">
         <x:f>C53*I53*'4. Szenarien'!D6*'1. Eingaben'!B9</x:f>
         <x:v>59997.92839810199</x:v>
       </x:c>
-      <x:c r="L53" s="55" t="n">
+      <x:c r="L53" s="68" t="n">
         <x:f>C53*J53*'4. Szenarien'!D7*'1. Eingaben'!B9</x:f>
         <x:v>67497.66944786474</x:v>
       </x:c>
-      <x:c r="M53" s="55" t="n">
+      <x:c r="M53" s="68" t="n">
         <x:f>M52+K53-H53</x:f>
         <x:v>1035727.8757924436</x:v>
       </x:c>
-      <x:c r="N53" s="55" t="n">
+      <x:c r="N53" s="68" t="n">
         <x:f>N52+L53-H53</x:f>
         <x:v>1235485.860266499</x:v>
       </x:c>
-      <x:c r="O53" s="68" t="n">
+      <x:c r="O53" s="81" t="n">
         <x:f>IF(M53&gt;=0,A53,99)</x:f>
         <x:v>28</x:v>
       </x:c>
-      <x:c r="P53" s="68" t="n">
+      <x:c r="P53" s="81" t="n">
         <x:f>IF(N53&gt;=0,A53,99)</x:f>
         <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="54">
-      <x:c r="A54" s="66" t="n">
+      <x:c r="A54" s="79" t="n">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="B54" s="66" t="n">
+      <x:c r="B54" s="79" t="n">
         <x:f>INT((A54-1)/12)+1</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C54" s="66" t="n">
+      <x:c r="C54" s="79" t="n">
         <x:f>'1. Eingaben'!B8</x:f>
         <x:v>300</x:v>
       </x:c>
-      <x:c r="D54" s="55" t="n">
+      <x:c r="D54" s="68" t="n">
         <x:f>C54*'1. Eingaben'!B10</x:f>
         <x:v>7800</x:v>
       </x:c>
-      <x:c r="E54" s="55" t="n">
+      <x:c r="E54" s="68" t="n">
         <x:f>IF(A54=1,INT(('1. Eingaben'!B8+'6. Quellen &amp; Methodik'!B33-1)/'6. Quellen &amp; Methodik'!B33)*('6. Quellen &amp; Methodik'!B31+'6. Quellen &amp; Methodik'!B32*'6. Quellen &amp; Methodik'!B35),IF(OR(A54=13,A54=25),INT(('1. Eingaben'!B8+'6. Quellen &amp; Methodik'!B33-1)/'6. Quellen &amp; Methodik'!B33)*('6. Quellen &amp; Methodik'!B31+'6. Quellen &amp; Methodik'!B32*'6. Quellen &amp; Methodik'!B35)*'6. Quellen &amp; Methodik'!B34,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F54" s="55" t="n">
+      <x:c r="F54" s="68" t="n">
         <x:f>IF(A54=1,'6. Quellen &amp; Methodik'!B16+MIN(C54,50)*'6. Quellen &amp; Methodik'!B17+MAX(MIN(C54-50,200),0)*'6. Quellen &amp; Methodik'!B18+MAX(MIN(C54-250,750),0)*'6. Quellen &amp; Methodik'!B19+MAX(C54-1000,0)*'6. Quellen &amp; Methodik'!B20,0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G54" s="55" t="n">
+      <x:c r="G54" s="68" t="n">
         <x:f>IF(OR(A54=1,A54=13,A54=25),'6. Quellen &amp; Methodik'!B36*(C54*'1. Eingaben'!B10*12+E54+F54),0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H54" s="55" t="n">
+      <x:c r="H54" s="68" t="n">
         <x:f>SUM(D54:G54)</x:f>
         <x:v>7800</x:v>
       </x:c>
-      <x:c r="I54" s="54" t="n">
+      <x:c r="I54" s="55" t="n">
         <x:f>'4. Szenarien'!B6*(1-(1-'4. Szenarien'!B13)*POWER(0.5,(A54-1)/'4. Szenarien'!B14))</x:f>
         <x:v>7.9998046875</x:v>
       </x:c>
-      <x:c r="J54" s="54" t="n">
+      <x:c r="J54" s="55" t="n">
         <x:f>'4. Szenarien'!B7*(1-(1-'4. Szenarien'!B13)*POWER(0.5,(A54-1)/'4. Szenarien'!B14))</x:f>
         <x:v>8.9997802734375</x:v>
       </x:c>
-      <x:c r="K54" s="55" t="n">
+      <x:c r="K54" s="68" t="n">
         <x:f>C54*I54*'4. Szenarien'!D6*'1. Eingaben'!B9</x:f>
         <x:v>59998.53515625</x:v>
       </x:c>
-      <x:c r="L54" s="55" t="n">
+      <x:c r="L54" s="68" t="n">
         <x:f>C54*J54*'4. Szenarien'!D7*'1. Eingaben'!B9</x:f>
         <x:v>67498.35205078125</x:v>
       </x:c>
-      <x:c r="M54" s="55" t="n">
+      <x:c r="M54" s="68" t="n">
         <x:f>M53+K54-H54</x:f>
         <x:v>1087926.4109486938</x:v>
       </x:c>
-      <x:c r="N54" s="55" t="n">
+      <x:c r="N54" s="68" t="n">
         <x:f>N53+L54-H54</x:f>
         <x:v>1295184.2123172802</x:v>
       </x:c>
-      <x:c r="O54" s="68" t="n">
+      <x:c r="O54" s="81" t="n">
         <x:f>IF(M54&gt;=0,A54,99)</x:f>
         <x:v>29</x:v>
       </x:c>
-      <x:c r="P54" s="68" t="n">
+      <x:c r="P54" s="81" t="n">
         <x:f>IF(N54&gt;=0,A54,99)</x:f>
         <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="55">
-      <x:c r="A55" s="66" t="n">
+      <x:c r="A55" s="79" t="n">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="B55" s="66" t="n">
+      <x:c r="B55" s="79" t="n">
         <x:f>INT((A55-1)/12)+1</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C55" s="66" t="n">
+      <x:c r="C55" s="79" t="n">
         <x:f>'1. Eingaben'!B8</x:f>
         <x:v>300</x:v>
       </x:c>
-      <x:c r="D55" s="55" t="n">
+      <x:c r="D55" s="68" t="n">
         <x:f>C55*'1. Eingaben'!B10</x:f>
         <x:v>7800</x:v>
       </x:c>
-      <x:c r="E55" s="55" t="n">
+      <x:c r="E55" s="68" t="n">
         <x:f>IF(A55=1,INT(('1. Eingaben'!B8+'6. Quellen &amp; Methodik'!B33-1)/'6. Quellen &amp; Methodik'!B33)*('6. Quellen &amp; Methodik'!B31+'6. Quellen &amp; Methodik'!B32*'6. Quellen &amp; Methodik'!B35),IF(OR(A55=13,A55=25),INT(('1. Eingaben'!B8+'6. Quellen &amp; Methodik'!B33-1)/'6. Quellen &amp; Methodik'!B33)*('6. Quellen &amp; Methodik'!B31+'6. Quellen &amp; Methodik'!B32*'6. Quellen &amp; Methodik'!B35)*'6. Quellen &amp; Methodik'!B34,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F55" s="55" t="n">
+      <x:c r="F55" s="68" t="n">
         <x:f>IF(A55=1,'6. Quellen &amp; Methodik'!B16+MIN(C55,50)*'6. Quellen &amp; Methodik'!B17+MAX(MIN(C55-50,200),0)*'6. Quellen &amp; Methodik'!B18+MAX(MIN(C55-250,750),0)*'6. Quellen &amp; Methodik'!B19+MAX(C55-1000,0)*'6. Quellen &amp; Methodik'!B20,0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G55" s="55" t="n">
+      <x:c r="G55" s="68" t="n">
         <x:f>IF(OR(A55=1,A55=13,A55=25),'6. Quellen &amp; Methodik'!B36*(C55*'1. Eingaben'!B10*12+E55+F55),0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H55" s="55" t="n">
+      <x:c r="H55" s="68" t="n">
         <x:f>SUM(D55:G55)</x:f>
         <x:v>7800</x:v>
       </x:c>
-      <x:c r="I55" s="54" t="n">
+      <x:c r="I55" s="55" t="n">
         <x:f>'4. Szenarien'!B6*(1-(1-'4. Szenarien'!B13)*POWER(0.5,(A55-1)/'4. Szenarien'!B14))</x:f>
         <x:v>7.999861893206799</x:v>
       </x:c>
-      <x:c r="J55" s="54" t="n">
+      <x:c r="J55" s="55" t="n">
         <x:f>'4. Szenarien'!B7*(1-(1-'4. Szenarien'!B13)*POWER(0.5,(A55-1)/'4. Szenarien'!B14))</x:f>
         <x:v>8.99984462985765</x:v>
       </x:c>
-      <x:c r="K55" s="55" t="n">
+      <x:c r="K55" s="68" t="n">
         <x:f>C55*I55*'4. Szenarien'!D6*'1. Eingaben'!B9</x:f>
         <x:v>59998.964199051</x:v>
       </x:c>
-      <x:c r="L55" s="55" t="n">
+      <x:c r="L55" s="68" t="n">
         <x:f>C55*J55*'4. Szenarien'!D7*'1. Eingaben'!B9</x:f>
         <x:v>67498.83472393238</x:v>
       </x:c>
-      <x:c r="M55" s="55" t="n">
+      <x:c r="M55" s="68" t="n">
         <x:f>M54+K55-H55</x:f>
         <x:v>1140125.3751477448</x:v>
       </x:c>
-      <x:c r="N55" s="55" t="n">
+      <x:c r="N55" s="68" t="n">
         <x:f>N54+L55-H55</x:f>
         <x:v>1354883.0470412127</x:v>
       </x:c>
-      <x:c r="O55" s="68" t="n">
+      <x:c r="O55" s="81" t="n">
         <x:f>IF(M55&gt;=0,A55,99)</x:f>
         <x:v>30</x:v>
       </x:c>
-      <x:c r="P55" s="68" t="n">
+      <x:c r="P55" s="81" t="n">
         <x:f>IF(N55&gt;=0,A55,99)</x:f>
         <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="56">
-      <x:c r="A56" s="66" t="n">
+      <x:c r="A56" s="79" t="n">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="B56" s="66" t="n">
+      <x:c r="B56" s="79" t="n">
         <x:f>INT((A56-1)/12)+1</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C56" s="66" t="n">
+      <x:c r="C56" s="79" t="n">
         <x:f>'1. Eingaben'!B8</x:f>
         <x:v>300</x:v>
       </x:c>
-      <x:c r="D56" s="55" t="n">
+      <x:c r="D56" s="68" t="n">
         <x:f>C56*'1. Eingaben'!B10</x:f>
         <x:v>7800</x:v>
       </x:c>
-      <x:c r="E56" s="55" t="n">
+      <x:c r="E56" s="68" t="n">
         <x:f>IF(A56=1,INT(('1. Eingaben'!B8+'6. Quellen &amp; Methodik'!B33-1)/'6. Quellen &amp; Methodik'!B33)*('6. Quellen &amp; Methodik'!B31+'6. Quellen &amp; Methodik'!B32*'6. Quellen &amp; Methodik'!B35),IF(OR(A56=13,A56=25),INT(('1. Eingaben'!B8+'6. Quellen &amp; Methodik'!B33-1)/'6. Quellen &amp; Methodik'!B33)*('6. Quellen &amp; Methodik'!B31+'6. Quellen &amp; Methodik'!B32*'6. Quellen &amp; Methodik'!B35)*'6. Quellen &amp; Methodik'!B34,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F56" s="55" t="n">
+      <x:c r="F56" s="68" t="n">
         <x:f>IF(A56=1,'6. Quellen &amp; Methodik'!B16+MIN(C56,50)*'6. Quellen &amp; Methodik'!B17+MAX(MIN(C56-50,200),0)*'6. Quellen &amp; Methodik'!B18+MAX(MIN(C56-250,750),0)*'6. Quellen &amp; Methodik'!B19+MAX(C56-1000,0)*'6. Quellen &amp; Methodik'!B20,0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G56" s="55" t="n">
+      <x:c r="G56" s="68" t="n">
         <x:f>IF(OR(A56=1,A56=13,A56=25),'6. Quellen &amp; Methodik'!B36*(C56*'1. Eingaben'!B10*12+E56+F56),0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H56" s="55" t="n">
+      <x:c r="H56" s="68" t="n">
         <x:f>SUM(D56:G56)</x:f>
         <x:v>7800</x:v>
       </x:c>
-      <x:c r="I56" s="54" t="n">
+      <x:c r="I56" s="55" t="n">
         <x:f>'4. Szenarien'!B6*(1-(1-'4. Szenarien'!B13)*POWER(0.5,(A56-1)/'4. Szenarien'!B14))</x:f>
         <x:v>7.99990234375</x:v>
       </x:c>
-      <x:c r="J56" s="54" t="n">
+      <x:c r="J56" s="55" t="n">
         <x:f>'4. Szenarien'!B7*(1-(1-'4. Szenarien'!B13)*POWER(0.5,(A56-1)/'4. Szenarien'!B14))</x:f>
         <x:v>8.999890136718749</x:v>
       </x:c>
-      <x:c r="K56" s="55" t="n">
+      <x:c r="K56" s="68" t="n">
         <x:f>C56*I56*'4. Szenarien'!D6*'1. Eingaben'!B9</x:f>
         <x:v>59999.267578125</x:v>
       </x:c>
-      <x:c r="L56" s="55" t="n">
+      <x:c r="L56" s="68" t="n">
         <x:f>C56*J56*'4. Szenarien'!D7*'1. Eingaben'!B9</x:f>
         <x:v>67499.17602539061</x:v>
       </x:c>
-      <x:c r="M56" s="55" t="n">
+      <x:c r="M56" s="68" t="n">
         <x:f>M55+K56-H56</x:f>
         <x:v>1192324.6427258698</x:v>
       </x:c>
-      <x:c r="N56" s="55" t="n">
+      <x:c r="N56" s="68" t="n">
         <x:f>N55+L56-H56</x:f>
         <x:v>1414582.2230666033</x:v>
       </x:c>
-      <x:c r="O56" s="68" t="n">
+      <x:c r="O56" s="81" t="n">
         <x:f>IF(M56&gt;=0,A56,99)</x:f>
         <x:v>31</x:v>
       </x:c>
-      <x:c r="P56" s="68" t="n">
+      <x:c r="P56" s="81" t="n">
         <x:f>IF(N56&gt;=0,A56,99)</x:f>
         <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="57">
-      <x:c r="A57" s="66" t="n">
+      <x:c r="A57" s="79" t="n">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="B57" s="66" t="n">
+      <x:c r="B57" s="79" t="n">
         <x:f>INT((A57-1)/12)+1</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C57" s="66" t="n">
+      <x:c r="C57" s="79" t="n">
         <x:f>'1. Eingaben'!B8</x:f>
         <x:v>300</x:v>
       </x:c>
-      <x:c r="D57" s="55" t="n">
+      <x:c r="D57" s="68" t="n">
         <x:f>C57*'1. Eingaben'!B10</x:f>
         <x:v>7800</x:v>
       </x:c>
-      <x:c r="E57" s="55" t="n">
+      <x:c r="E57" s="68" t="n">
         <x:f>IF(A57=1,INT(('1. Eingaben'!B8+'6. Quellen &amp; Methodik'!B33-1)/'6. Quellen &amp; Methodik'!B33)*('6. Quellen &amp; Methodik'!B31+'6. Quellen &amp; Methodik'!B32*'6. Quellen &amp; Methodik'!B35),IF(OR(A57=13,A57=25),INT(('1. Eingaben'!B8+'6. Quellen &amp; Methodik'!B33-1)/'6. Quellen &amp; Methodik'!B33)*('6. Quellen &amp; Methodik'!B31+'6. Quellen &amp; Methodik'!B32*'6. Quellen &amp; Methodik'!B35)*'6. Quellen &amp; Methodik'!B34,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F57" s="55" t="n">
+      <x:c r="F57" s="68" t="n">
         <x:f>IF(A57=1,'6. Quellen &amp; Methodik'!B16+MIN(C57,50)*'6. Quellen &amp; Methodik'!B17+MAX(MIN(C57-50,200),0)*'6. Quellen &amp; Methodik'!B18+MAX(MIN(C57-250,750),0)*'6. Quellen &amp; Methodik'!B19+MAX(C57-1000,0)*'6. Quellen &amp; Methodik'!B20,0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G57" s="55" t="n">
+      <x:c r="G57" s="68" t="n">
         <x:f>IF(OR(A57=1,A57=13,A57=25),'6. Quellen &amp; Methodik'!B36*(C57*'1. Eingaben'!B10*12+E57+F57),0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H57" s="55" t="n">
+      <x:c r="H57" s="68" t="n">
         <x:f>SUM(D57:G57)</x:f>
         <x:v>7800</x:v>
       </x:c>
-      <x:c r="I57" s="54" t="n">
+      <x:c r="I57" s="55" t="n">
         <x:f>'4. Szenarien'!B6*(1-(1-'4. Szenarien'!B13)*POWER(0.5,(A57-1)/'4. Szenarien'!B14))</x:f>
         <x:v>7.9999309466034</x:v>
       </x:c>
-      <x:c r="J57" s="54" t="n">
+      <x:c r="J57" s="55" t="n">
         <x:f>'4. Szenarien'!B7*(1-(1-'4. Szenarien'!B13)*POWER(0.5,(A57-1)/'4. Szenarien'!B14))</x:f>
         <x:v>8.999922314928826</x:v>
       </x:c>
-      <x:c r="K57" s="55" t="n">
+      <x:c r="K57" s="68" t="n">
         <x:f>C57*I57*'4. Szenarien'!D6*'1. Eingaben'!B9</x:f>
         <x:v>59999.48209952551</x:v>
       </x:c>
-      <x:c r="L57" s="55" t="n">
+      <x:c r="L57" s="68" t="n">
         <x:f>C57*J57*'4. Szenarien'!D7*'1. Eingaben'!B9</x:f>
         <x:v>67499.4173619662</x:v>
       </x:c>
-      <x:c r="M57" s="55" t="n">
+      <x:c r="M57" s="68" t="n">
         <x:f>M56+K57-H57</x:f>
         <x:v>1244524.1248253952</x:v>
       </x:c>
-      <x:c r="N57" s="55" t="n">
+      <x:c r="N57" s="68" t="n">
         <x:f>N56+L57-H57</x:f>
         <x:v>1474281.6404285694</x:v>
       </x:c>
-      <x:c r="O57" s="68" t="n">
+      <x:c r="O57" s="81" t="n">
         <x:f>IF(M57&gt;=0,A57,99)</x:f>
         <x:v>32</x:v>
       </x:c>
-      <x:c r="P57" s="68" t="n">
+      <x:c r="P57" s="81" t="n">
         <x:f>IF(N57&gt;=0,A57,99)</x:f>
         <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="58">
-      <x:c r="A58" s="66" t="n">
+      <x:c r="A58" s="79" t="n">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="B58" s="66" t="n">
+      <x:c r="B58" s="79" t="n">
         <x:f>INT((A58-1)/12)+1</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C58" s="66" t="n">
+      <x:c r="C58" s="79" t="n">
         <x:f>'1. Eingaben'!B8</x:f>
         <x:v>300</x:v>
       </x:c>
-      <x:c r="D58" s="55" t="n">
+      <x:c r="D58" s="68" t="n">
         <x:f>C58*'1. Eingaben'!B10</x:f>
         <x:v>7800</x:v>
       </x:c>
-      <x:c r="E58" s="55" t="n">
+      <x:c r="E58" s="68" t="n">
         <x:f>IF(A58=1,INT(('1. Eingaben'!B8+'6. Quellen &amp; Methodik'!B33-1)/'6. Quellen &amp; Methodik'!B33)*('6. Quellen &amp; Methodik'!B31+'6. Quellen &amp; Methodik'!B32*'6. Quellen &amp; Methodik'!B35),IF(OR(A58=13,A58=25),INT(('1. Eingaben'!B8+'6. Quellen &amp; Methodik'!B33-1)/'6. Quellen &amp; Methodik'!B33)*('6. Quellen &amp; Methodik'!B31+'6. Quellen &amp; Methodik'!B32*'6. Quellen &amp; Methodik'!B35)*'6. Quellen &amp; Methodik'!B34,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F58" s="55" t="n">
+      <x:c r="F58" s="68" t="n">
         <x:f>IF(A58=1,'6. Quellen &amp; Methodik'!B16+MIN(C58,50)*'6. Quellen &amp; Methodik'!B17+MAX(MIN(C58-50,200),0)*'6. Quellen &amp; Methodik'!B18+MAX(MIN(C58-250,750),0)*'6. Quellen &amp; Methodik'!B19+MAX(C58-1000,0)*'6. Quellen &amp; Methodik'!B20,0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G58" s="55" t="n">
+      <x:c r="G58" s="68" t="n">
         <x:f>IF(OR(A58=1,A58=13,A58=25),'6. Quellen &amp; Methodik'!B36*(C58*'1. Eingaben'!B10*12+E58+F58),0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H58" s="55" t="n">
+      <x:c r="H58" s="68" t="n">
         <x:f>SUM(D58:G58)</x:f>
         <x:v>7800</x:v>
       </x:c>
-      <x:c r="I58" s="54" t="n">
+      <x:c r="I58" s="55" t="n">
         <x:f>'4. Szenarien'!B6*(1-(1-'4. Szenarien'!B13)*POWER(0.5,(A58-1)/'4. Szenarien'!B14))</x:f>
         <x:v>7.999951171875</x:v>
       </x:c>
-      <x:c r="J58" s="54" t="n">
+      <x:c r="J58" s="55" t="n">
         <x:f>'4. Szenarien'!B7*(1-(1-'4. Szenarien'!B13)*POWER(0.5,(A58-1)/'4. Szenarien'!B14))</x:f>
         <x:v>8.999945068359375</x:v>
       </x:c>
-      <x:c r="K58" s="55" t="n">
+      <x:c r="K58" s="68" t="n">
         <x:f>C58*I58*'4. Szenarien'!D6*'1. Eingaben'!B9</x:f>
         <x:v>59999.6337890625</x:v>
       </x:c>
-      <x:c r="L58" s="55" t="n">
+      <x:c r="L58" s="68" t="n">
         <x:f>C58*J58*'4. Szenarien'!D7*'1. Eingaben'!B9</x:f>
         <x:v>67499.58801269531</x:v>
       </x:c>
-      <x:c r="M58" s="55" t="n">
+      <x:c r="M58" s="68" t="n">
         <x:f>M57+K58-H58</x:f>
         <x:v>1296723.7586144577</x:v>
       </x:c>
-      <x:c r="N58" s="55" t="n">
+      <x:c r="N58" s="68" t="n">
         <x:f>N57+L58-H58</x:f>
         <x:v>1533981.2284412647</x:v>
       </x:c>
-      <x:c r="O58" s="68" t="n">
+      <x:c r="O58" s="81" t="n">
         <x:f>IF(M58&gt;=0,A58,99)</x:f>
         <x:v>33</x:v>
       </x:c>
-      <x:c r="P58" s="68" t="n">
+      <x:c r="P58" s="81" t="n">
         <x:f>IF(N58&gt;=0,A58,99)</x:f>
         <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="59">
-      <x:c r="A59" s="66" t="n">
+      <x:c r="A59" s="79" t="n">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="B59" s="66" t="n">
+      <x:c r="B59" s="79" t="n">
         <x:f>INT((A59-1)/12)+1</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C59" s="66" t="n">
+      <x:c r="C59" s="79" t="n">
         <x:f>'1. Eingaben'!B8</x:f>
         <x:v>300</x:v>
       </x:c>
-      <x:c r="D59" s="55" t="n">
+      <x:c r="D59" s="68" t="n">
         <x:f>C59*'1. Eingaben'!B10</x:f>
         <x:v>7800</x:v>
       </x:c>
-      <x:c r="E59" s="55" t="n">
+      <x:c r="E59" s="68" t="n">
         <x:f>IF(A59=1,INT(('1. Eingaben'!B8+'6. Quellen &amp; Methodik'!B33-1)/'6. Quellen &amp; Methodik'!B33)*('6. Quellen &amp; Methodik'!B31+'6. Quellen &amp; Methodik'!B32*'6. Quellen &amp; Methodik'!B35),IF(OR(A59=13,A59=25),INT(('1. Eingaben'!B8+'6. Quellen &amp; Methodik'!B33-1)/'6. Quellen &amp; Methodik'!B33)*('6. Quellen &amp; Methodik'!B31+'6. Quellen &amp; Methodik'!B32*'6. Quellen &amp; Methodik'!B35)*'6. Quellen &amp; Methodik'!B34,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F59" s="55" t="n">
+      <x:c r="F59" s="68" t="n">
         <x:f>IF(A59=1,'6. Quellen &amp; Methodik'!B16+MIN(C59,50)*'6. Quellen &amp; Methodik'!B17+MAX(MIN(C59-50,200),0)*'6. Quellen &amp; Methodik'!B18+MAX(MIN(C59-250,750),0)*'6. Quellen &amp; Methodik'!B19+MAX(C59-1000,0)*'6. Quellen &amp; Methodik'!B20,0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G59" s="55" t="n">
+      <x:c r="G59" s="68" t="n">
         <x:f>IF(OR(A59=1,A59=13,A59=25),'6. Quellen &amp; Methodik'!B36*(C59*'1. Eingaben'!B10*12+E59+F59),0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H59" s="55" t="n">
+      <x:c r="H59" s="68" t="n">
         <x:f>SUM(D59:G59)</x:f>
         <x:v>7800</x:v>
       </x:c>
-      <x:c r="I59" s="54" t="n">
+      <x:c r="I59" s="55" t="n">
         <x:f>'4. Szenarien'!B6*(1-(1-'4. Szenarien'!B13)*POWER(0.5,(A59-1)/'4. Szenarien'!B14))</x:f>
         <x:v>7.9999654733017</x:v>
       </x:c>
-      <x:c r="J59" s="54" t="n">
+      <x:c r="J59" s="55" t="n">
         <x:f>'4. Szenarien'!B7*(1-(1-'4. Szenarien'!B13)*POWER(0.5,(A59-1)/'4. Szenarien'!B14))</x:f>
         <x:v>8.999961157464412</x:v>
       </x:c>
-      <x:c r="K59" s="55" t="n">
+      <x:c r="K59" s="68" t="n">
         <x:f>C59*I59*'4. Szenarien'!D6*'1. Eingaben'!B9</x:f>
         <x:v>59999.74104976275</x:v>
       </x:c>
-      <x:c r="L59" s="55" t="n">
+      <x:c r="L59" s="68" t="n">
         <x:f>C59*J59*'4. Szenarien'!D7*'1. Eingaben'!B9</x:f>
         <x:v>67499.7086809831</x:v>
       </x:c>
-      <x:c r="M59" s="55" t="n">
+      <x:c r="M59" s="68" t="n">
         <x:f>M58+K59-H59</x:f>
         <x:v>1348923.4996642205</x:v>
       </x:c>
-      <x:c r="N59" s="55" t="n">
+      <x:c r="N59" s="68" t="n">
         <x:f>N58+L59-H59</x:f>
         <x:v>1593680.9371222479</x:v>
       </x:c>
-      <x:c r="O59" s="68" t="n">
+      <x:c r="O59" s="81" t="n">
         <x:f>IF(M59&gt;=0,A59,99)</x:f>
         <x:v>34</x:v>
       </x:c>
-      <x:c r="P59" s="68" t="n">
+      <x:c r="P59" s="81" t="n">
         <x:f>IF(N59&gt;=0,A59,99)</x:f>
         <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="60">
-      <x:c r="A60" s="66" t="n">
+      <x:c r="A60" s="79" t="n">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="B60" s="66" t="n">
+      <x:c r="B60" s="79" t="n">
         <x:f>INT((A60-1)/12)+1</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C60" s="66" t="n">
+      <x:c r="C60" s="79" t="n">
         <x:f>'1. Eingaben'!B8</x:f>
         <x:v>300</x:v>
       </x:c>
-      <x:c r="D60" s="55" t="n">
+      <x:c r="D60" s="68" t="n">
         <x:f>C60*'1. Eingaben'!B10</x:f>
         <x:v>7800</x:v>
       </x:c>
-      <x:c r="E60" s="55" t="n">
+      <x:c r="E60" s="68" t="n">
         <x:f>IF(A60=1,INT(('1. Eingaben'!B8+'6. Quellen &amp; Methodik'!B33-1)/'6. Quellen &amp; Methodik'!B33)*('6. Quellen &amp; Methodik'!B31+'6. Quellen &amp; Methodik'!B32*'6. Quellen &amp; Methodik'!B35),IF(OR(A60=13,A60=25),INT(('1. Eingaben'!B8+'6. Quellen &amp; Methodik'!B33-1)/'6. Quellen &amp; Methodik'!B33)*('6. Quellen &amp; Methodik'!B31+'6. Quellen &amp; Methodik'!B32*'6. Quellen &amp; Methodik'!B35)*'6. Quellen &amp; Methodik'!B34,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F60" s="55" t="n">
+      <x:c r="F60" s="68" t="n">
         <x:f>IF(A60=1,'6. Quellen &amp; Methodik'!B16+MIN(C60,50)*'6. Quellen &amp; Methodik'!B17+MAX(MIN(C60-50,200),0)*'6. Quellen &amp; Methodik'!B18+MAX(MIN(C60-250,750),0)*'6. Quellen &amp; Methodik'!B19+MAX(C60-1000,0)*'6. Quellen &amp; Methodik'!B20,0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G60" s="55" t="n">
+      <x:c r="G60" s="68" t="n">
         <x:f>IF(OR(A60=1,A60=13,A60=25),'6. Quellen &amp; Methodik'!B36*(C60*'1. Eingaben'!B10*12+E60+F60),0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H60" s="55" t="n">
+      <x:c r="H60" s="68" t="n">
         <x:f>SUM(D60:G60)</x:f>
         <x:v>7800</x:v>
       </x:c>
-      <x:c r="I60" s="54" t="n">
+      <x:c r="I60" s="55" t="n">
         <x:f>'4. Szenarien'!B6*(1-(1-'4. Szenarien'!B13)*POWER(0.5,(A60-1)/'4. Szenarien'!B14))</x:f>
         <x:v>7.9999755859375</x:v>
       </x:c>
-      <x:c r="J60" s="54" t="n">
+      <x:c r="J60" s="55" t="n">
         <x:f>'4. Szenarien'!B7*(1-(1-'4. Szenarien'!B13)*POWER(0.5,(A60-1)/'4. Szenarien'!B14))</x:f>
         <x:v>8.999972534179689</x:v>
       </x:c>
-      <x:c r="K60" s="55" t="n">
+      <x:c r="K60" s="68" t="n">
         <x:f>C60*I60*'4. Szenarien'!D6*'1. Eingaben'!B9</x:f>
         <x:v>59999.81689453125</x:v>
       </x:c>
-      <x:c r="L60" s="55" t="n">
+      <x:c r="L60" s="68" t="n">
         <x:f>C60*J60*'4. Szenarien'!D7*'1. Eingaben'!B9</x:f>
         <x:v>67499.79400634767</x:v>
       </x:c>
-      <x:c r="M60" s="55" t="n">
+      <x:c r="M60" s="68" t="n">
         <x:f>M59+K60-H60</x:f>
         <x:v>1401123.3165587517</x:v>
       </x:c>
-      <x:c r="N60" s="55" t="n">
+      <x:c r="N60" s="68" t="n">
         <x:f>N59+L60-H60</x:f>
         <x:v>1653380.7311285955</x:v>
       </x:c>
-      <x:c r="O60" s="68" t="n">
+      <x:c r="O60" s="81" t="n">
         <x:f>IF(M60&gt;=0,A60,99)</x:f>
         <x:v>35</x:v>
       </x:c>
-      <x:c r="P60" s="68" t="n">
+      <x:c r="P60" s="81" t="n">
         <x:f>IF(N60&gt;=0,A60,99)</x:f>
         <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="61">
-      <x:c r="A61" s="66" t="n">
+      <x:c r="A61" s="79" t="n">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="B61" s="66" t="n">
+      <x:c r="B61" s="79" t="n">
         <x:f>INT((A61-1)/12)+1</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C61" s="66" t="n">
+      <x:c r="C61" s="79" t="n">
         <x:f>'1. Eingaben'!B8</x:f>
         <x:v>300</x:v>
       </x:c>
-      <x:c r="D61" s="55" t="n">
+      <x:c r="D61" s="68" t="n">
         <x:f>C61*'1. Eingaben'!B10</x:f>
         <x:v>7800</x:v>
       </x:c>
-      <x:c r="E61" s="55" t="n">
+      <x:c r="E61" s="68" t="n">
         <x:f>IF(A61=1,INT(('1. Eingaben'!B8+'6. Quellen &amp; Methodik'!B33-1)/'6. Quellen &amp; Methodik'!B33)*('6. Quellen &amp; Methodik'!B31+'6. Quellen &amp; Methodik'!B32*'6. Quellen &amp; Methodik'!B35),IF(OR(A61=13,A61=25),INT(('1. Eingaben'!B8+'6. Quellen &amp; Methodik'!B33-1)/'6. Quellen &amp; Methodik'!B33)*('6. Quellen &amp; Methodik'!B31+'6. Quellen &amp; Methodik'!B32*'6. Quellen &amp; Methodik'!B35)*'6. Quellen &amp; Methodik'!B34,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F61" s="55" t="n">
+      <x:c r="F61" s="68" t="n">
         <x:f>IF(A61=1,'6. Quellen &amp; Methodik'!B16+MIN(C61,50)*'6. Quellen &amp; Methodik'!B17+MAX(MIN(C61-50,200),0)*'6. Quellen &amp; Methodik'!B18+MAX(MIN(C61-250,750),0)*'6. Quellen &amp; Methodik'!B19+MAX(C61-1000,0)*'6. Quellen &amp; Methodik'!B20,0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G61" s="55" t="n">
+      <x:c r="G61" s="68" t="n">
         <x:f>IF(OR(A61=1,A61=13,A61=25),'6. Quellen &amp; Methodik'!B36*(C61*'1. Eingaben'!B10*12+E61+F61),0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H61" s="55" t="n">
+      <x:c r="H61" s="68" t="n">
         <x:f>SUM(D61:G61)</x:f>
         <x:v>7800</x:v>
       </x:c>
-      <x:c r="I61" s="54" t="n">
+      <x:c r="I61" s="55" t="n">
         <x:f>'4. Szenarien'!B6*(1-(1-'4. Szenarien'!B13)*POWER(0.5,(A61-1)/'4. Szenarien'!B14))</x:f>
         <x:v>7.99998273665085</x:v>
       </x:c>
-      <x:c r="J61" s="54" t="n">
+      <x:c r="J61" s="55" t="n">
         <x:f>'4. Szenarien'!B7*(1-(1-'4. Szenarien'!B13)*POWER(0.5,(A61-1)/'4. Szenarien'!B14))</x:f>
         <x:v>8.999980578732206</x:v>
       </x:c>
-      <x:c r="K61" s="55" t="n">
+      <x:c r="K61" s="68" t="n">
         <x:f>C61*I61*'4. Szenarien'!D6*'1. Eingaben'!B9</x:f>
         <x:v>59999.87052488137</x:v>
       </x:c>
-      <x:c r="L61" s="55" t="n">
+      <x:c r="L61" s="68" t="n">
         <x:f>C61*J61*'4. Szenarien'!D7*'1. Eingaben'!B9</x:f>
         <x:v>67499.85434049155</x:v>
       </x:c>
-      <x:c r="M61" s="55" t="n">
+      <x:c r="M61" s="68" t="n">
         <x:f>M60+K61-H61</x:f>
         <x:v>1453323.1870836332</x:v>
       </x:c>
-      <x:c r="N61" s="55" t="n">
+      <x:c r="N61" s="68" t="n">
         <x:f>N60+L61-H61</x:f>
         <x:v>1713080.5854690871</x:v>
       </x:c>
-      <x:c r="O61" s="68" t="n">
+      <x:c r="O61" s="81" t="n">
         <x:f>IF(M61&gt;=0,A61,99)</x:f>
         <x:v>36</x:v>
       </x:c>
-      <x:c r="P61" s="68" t="n">
+      <x:c r="P61" s="81" t="n">
         <x:f>IF(N61&gt;=0,A61,99)</x:f>
         <x:v>36</x:v>
       </x:c>
@@ -6751,99 +7053,99 @@
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="20" t="str">
-        <x:v>1. Monatliche Zeitersparnis</x:v>
-      </x:c>
-      <x:c r="B5" s="49" t="str">
-        <x:v>Ziel-Zeitersparnis × [1 − (1 − Startanteil) × 0,5^((Monat−1) ÷ Halbwertszeit)]</x:v>
-      </x:c>
-      <x:c r="C5" s="49"/>
-      <x:c r="D5" s="49"/>
-      <x:c r="E5" s="49"/>
-      <x:c r="F5" s="49"/>
+        <x:v>1. Assistenz-Baseline im Kompetenzaufbau</x:v>
+      </x:c>
+      <x:c r="B5" s="50" t="str">
+        <x:v>Ziel-Zeitersparnis × [1 − (1 − Startanteil) × 0,5^((Monat−1) ÷ Halbwertszeit)]. Die Zielgröße ist eine vorsichtige Planungsbasis, keine langfristige Obergrenze.</x:v>
+      </x:c>
+      <x:c r="C5" s="50"/>
+      <x:c r="D5" s="50"/>
+      <x:c r="E5" s="50"/>
+      <x:c r="F5" s="50"/>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="20" t="str">
         <x:v>2. Gesparte Stunden</x:v>
       </x:c>
-      <x:c r="B6" s="49" t="str">
+      <x:c r="B6" s="50" t="str">
         <x:v>Alle Nutzer × durchschnittliche Zeitersparnis je Person</x:v>
       </x:c>
-      <x:c r="C6" s="49"/>
-      <x:c r="D6" s="49"/>
-      <x:c r="E6" s="49"/>
-      <x:c r="F6" s="49"/>
+      <x:c r="C6" s="50"/>
+      <x:c r="D6" s="50"/>
+      <x:c r="E6" s="50"/>
+      <x:c r="F6" s="50"/>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="20" t="str">
         <x:v>3. Realisierter Nutzen</x:v>
       </x:c>
-      <x:c r="B7" s="49" t="str">
+      <x:c r="B7" s="50" t="str">
         <x:v>Gesparte Stunden × Vollkosten-Stundensatz × 50% wirtschaftliche Realisierung</x:v>
       </x:c>
-      <x:c r="C7" s="49"/>
-      <x:c r="D7" s="49"/>
-      <x:c r="E7" s="49"/>
-      <x:c r="F7" s="49"/>
+      <x:c r="C7" s="50"/>
+      <x:c r="D7" s="50"/>
+      <x:c r="E7" s="50"/>
+      <x:c r="F7" s="50"/>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="20" t="str">
         <x:v>4. Training</x:v>
       </x:c>
-      <x:c r="B8" s="49" t="str">
+      <x:c r="B8" s="50" t="str">
         <x:v>Jahr 1: 100% | Jahr 2: 50% | Jahr 3: 50%</x:v>
       </x:c>
-      <x:c r="C8" s="49"/>
-      <x:c r="D8" s="49"/>
-      <x:c r="E8" s="49"/>
-      <x:c r="F8" s="49"/>
+      <x:c r="C8" s="50"/>
+      <x:c r="D8" s="50"/>
+      <x:c r="E8" s="50"/>
+      <x:c r="F8" s="50"/>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="20" t="str">
         <x:v>5. IT-Setup</x:v>
       </x:c>
-      <x:c r="B9" s="49" t="str">
+      <x:c r="B9" s="50" t="str">
         <x:v>2.500 € Grundaufwand + degressive Nutzerstaffel; nur Jahr 1</x:v>
       </x:c>
-      <x:c r="C9" s="49"/>
-      <x:c r="D9" s="49"/>
-      <x:c r="E9" s="49"/>
-      <x:c r="F9" s="49"/>
+      <x:c r="C9" s="50"/>
+      <x:c r="D9" s="50"/>
+      <x:c r="E9" s="50"/>
+      <x:c r="F9" s="50"/>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="20" t="str">
         <x:v>6. Change &amp; Adoption</x:v>
       </x:c>
-      <x:c r="B10" s="49" t="str">
+      <x:c r="B10" s="50" t="str">
         <x:v>12% der jährlichen Lizenz-, Trainings- und IT-Basiskosten</x:v>
       </x:c>
-      <x:c r="C10" s="49"/>
-      <x:c r="D10" s="49"/>
-      <x:c r="E10" s="49"/>
-      <x:c r="F10" s="49"/>
+      <x:c r="C10" s="50"/>
+      <x:c r="D10" s="50"/>
+      <x:c r="E10" s="50"/>
+      <x:c r="F10" s="50"/>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="20" t="str">
         <x:v>7. ROI</x:v>
       </x:c>
-      <x:c r="B11" s="49" t="str">
+      <x:c r="B11" s="50" t="str">
         <x:v>(Realisierter Nutzen − Gesamtkosten) ÷ Gesamtkosten. &gt; 0% = Netto-Nutzen; 0% = Break-even; &lt; 0% = Kosten noch nicht gedeckt. 100% bedeutet: gesamter Nutzen ist doppelt so hoch wie die Kosten.</x:v>
       </x:c>
-      <x:c r="C11" s="49"/>
-      <x:c r="D11" s="49"/>
-      <x:c r="E11" s="49"/>
-      <x:c r="F11" s="49"/>
+      <x:c r="C11" s="50"/>
+      <x:c r="D11" s="50"/>
+      <x:c r="E11" s="50"/>
+      <x:c r="F11" s="50"/>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="20" t="str">
         <x:v>8. Kostenzeitpunkt</x:v>
       </x:c>
-      <x:c r="B12" s="49" t="str">
+      <x:c r="B12" s="50" t="str">
         <x:v>Jahreslizenzen monatlich; Training, IT und Change im ersten Monat des jeweiligen Jahres</x:v>
       </x:c>
-      <x:c r="C12" s="49"/>
-      <x:c r="D12" s="49"/>
-      <x:c r="E12" s="49"/>
-      <x:c r="F12" s="49"/>
+      <x:c r="C12" s="50"/>
+      <x:c r="D12" s="50"/>
+      <x:c r="E12" s="50"/>
+      <x:c r="F12" s="50"/>
     </x:row>
     <x:row r="14" ht="22" customHeight="1">
       <x:c r="A14" s="12" t="str">
@@ -6886,102 +7188,102 @@
       </x:c>
     </x:row>
     <x:row r="16">
-      <x:c r="A16" s="49" t="str">
+      <x:c r="A16" s="50" t="str">
         <x:v>Grundaufwand</x:v>
       </x:c>
-      <x:c r="B16" s="131" t="n">
+      <x:c r="B16" s="121" t="n">
         <x:v>2500</x:v>
       </x:c>
-      <x:c r="C16" s="49" t="str">
+      <x:c r="C16" s="50" t="str">
         <x:v>jede Einführung</x:v>
       </x:c>
-      <x:c r="D16" s="49" t="str">
+      <x:c r="D16" s="50" t="str">
         <x:v>Tenant-Prüfung, Grundkonzept, Koordination</x:v>
       </x:c>
-      <x:c r="E16" s="49" t="str">
+      <x:c r="E16" s="50" t="str">
         <x:v>Modellannahme</x:v>
       </x:c>
-      <x:c r="F16" s="49" t="str">
+      <x:c r="F16" s="50" t="str">
         <x:v>Geschützte Modellannahme</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
-      <x:c r="A17" s="49" t="str">
+      <x:c r="A17" s="50" t="str">
         <x:v>Stufe 1</x:v>
       </x:c>
-      <x:c r="B17" s="131" t="n">
+      <x:c r="B17" s="121" t="n">
         <x:v>150</x:v>
       </x:c>
-      <x:c r="C17" s="49" t="str">
+      <x:c r="C17" s="50" t="str">
         <x:v>Nutzer 1–50</x:v>
       </x:c>
-      <x:c r="D17" s="49" t="str">
+      <x:c r="D17" s="50" t="str">
         <x:v>Hoher Aufwand je Nutzer bei kleinen Rollouts</x:v>
       </x:c>
-      <x:c r="E17" s="49" t="str">
+      <x:c r="E17" s="50" t="str">
         <x:v>Modellannahme</x:v>
       </x:c>
-      <x:c r="F17" s="49" t="str">
+      <x:c r="F17" s="50" t="str">
         <x:v>Grenzkosten je Nutzer</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
-      <x:c r="A18" s="49" t="str">
+      <x:c r="A18" s="50" t="str">
         <x:v>Stufe 2</x:v>
       </x:c>
-      <x:c r="B18" s="131" t="n">
+      <x:c r="B18" s="121" t="n">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="C18" s="49" t="str">
+      <x:c r="C18" s="50" t="str">
         <x:v>Nutzer 51–250</x:v>
       </x:c>
-      <x:c r="D18" s="49" t="str">
+      <x:c r="D18" s="50" t="str">
         <x:v>Erste Skaleneffekte</x:v>
       </x:c>
-      <x:c r="E18" s="49" t="str">
+      <x:c r="E18" s="50" t="str">
         <x:v>Modellannahme</x:v>
       </x:c>
-      <x:c r="F18" s="49" t="str">
+      <x:c r="F18" s="50" t="str">
         <x:v>Grenzkosten je Nutzer</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
-      <x:c r="A19" s="49" t="str">
+      <x:c r="A19" s="50" t="str">
         <x:v>Stufe 3</x:v>
       </x:c>
-      <x:c r="B19" s="131" t="n">
+      <x:c r="B19" s="121" t="n">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="C19" s="49" t="str">
+      <x:c r="C19" s="50" t="str">
         <x:v>Nutzer 251–1.000</x:v>
       </x:c>
-      <x:c r="D19" s="49" t="str">
+      <x:c r="D19" s="50" t="str">
         <x:v>Standardisierung und Wiederverwendung</x:v>
       </x:c>
-      <x:c r="E19" s="49" t="str">
+      <x:c r="E19" s="50" t="str">
         <x:v>Modellannahme</x:v>
       </x:c>
-      <x:c r="F19" s="49" t="str">
+      <x:c r="F19" s="50" t="str">
         <x:v>Grenzkosten je Nutzer</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
-      <x:c r="A20" s="49" t="str">
+      <x:c r="A20" s="50" t="str">
         <x:v>Stufe 4</x:v>
       </x:c>
-      <x:c r="B20" s="131" t="n">
+      <x:c r="B20" s="121" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="C20" s="49" t="str">
+      <x:c r="C20" s="50" t="str">
         <x:v>ab Nutzer 1.001</x:v>
       </x:c>
-      <x:c r="D20" s="49" t="str">
+      <x:c r="D20" s="50" t="str">
         <x:v>Weitere Skaleneffekte, aber zusätzliche Governance</x:v>
       </x:c>
-      <x:c r="E20" s="49" t="str">
+      <x:c r="E20" s="50" t="str">
         <x:v>Modellannahme</x:v>
       </x:c>
-      <x:c r="F20" s="49" t="str">
+      <x:c r="F20" s="50" t="str">
         <x:v>Grenzkosten je Nutzer</x:v>
       </x:c>
     </x:row>
@@ -7026,82 +7328,82 @@
       </x:c>
     </x:row>
     <x:row r="24">
-      <x:c r="A24" s="49" t="str">
+      <x:c r="A24" s="50" t="str">
         <x:v>Zeitersparnis</x:v>
       </x:c>
-      <x:c r="B24" s="49" t="str">
+      <x:c r="B24" s="50" t="str">
         <x:v>Typische allgemeine Nutzer: 8 Std./Monat; Modellwert: 9 Std.; hoch entwickelte Nutzer: bis 20 Std.</x:v>
       </x:c>
-      <x:c r="C24" s="49" t="str">
+      <x:c r="C24" s="50" t="str">
         <x:v>https://tei.forrester.com/go/microsoft/M365Copilot/?lang=en-us</x:v>
       </x:c>
-      <x:c r="D24" s="49" t="str">
+      <x:c r="D24" s="50" t="str">
         <x:v>März 2025</x:v>
       </x:c>
-      <x:c r="E24" s="49" t="str">
+      <x:c r="E24" s="50" t="str">
         <x:v>Microsoft-beauftragte Forrester-TEI-Studie</x:v>
       </x:c>
-      <x:c r="F24" s="49" t="str">
+      <x:c r="F24" s="50" t="str">
         <x:v>Realistisches Szenario nutzt 8 Std.; kein garantierter Kundenwert</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
-      <x:c r="A25" s="49" t="str">
+      <x:c r="A25" s="50" t="str">
         <x:v>Realisierungsfaktor</x:v>
       </x:c>
-      <x:c r="B25" s="49" t="str">
+      <x:c r="B25" s="50" t="str">
         <x:v>Forrester verwendet 50% Productivity Recapture</x:v>
       </x:c>
-      <x:c r="C25" s="49" t="str">
+      <x:c r="C25" s="50" t="str">
         <x:v>https://tei.forrester.com/go/microsoft/M365Copilot/?lang=en-us</x:v>
       </x:c>
-      <x:c r="D25" s="49" t="str">
+      <x:c r="D25" s="50" t="str">
         <x:v>März 2025</x:v>
       </x:c>
-      <x:c r="E25" s="49" t="str">
+      <x:c r="E25" s="50" t="str">
         <x:v>Studienannahme</x:v>
       </x:c>
-      <x:c r="F25" s="49" t="str">
+      <x:c r="F25" s="50" t="str">
         <x:v>Im Rechner separat ausgewiesen</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
-      <x:c r="A26" s="49" t="str">
+      <x:c r="A26" s="50" t="str">
         <x:v>Kompetenzaufbau</x:v>
       </x:c>
-      <x:c r="B26" s="49" t="str">
+      <x:c r="B26" s="50" t="str">
         <x:v>Mindestens 12 Wochen bis Vertrautheit; etwa 3 Monate bis Kompetenz</x:v>
       </x:c>
-      <x:c r="C26" s="49" t="str">
+      <x:c r="C26" s="50" t="str">
         <x:v>https://tei.forrester.com/go/microsoft/M365Copilot/?lang=en-us</x:v>
       </x:c>
-      <x:c r="D26" s="49" t="str">
+      <x:c r="D26" s="50" t="str">
         <x:v>März 2025</x:v>
       </x:c>
-      <x:c r="E26" s="49" t="str">
+      <x:c r="E26" s="50" t="str">
         <x:v>Forrester-Interviews</x:v>
       </x:c>
-      <x:c r="F26" s="49" t="str">
+      <x:c r="F26" s="50" t="str">
         <x:v>Stützt schnellen Start plus weitere Entwicklung</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
-      <x:c r="A27" s="49" t="str">
+      <x:c r="A27" s="50" t="str">
         <x:v>Laufende Adoption</x:v>
       </x:c>
-      <x:c r="B27" s="49" t="str">
+      <x:c r="B27" s="50" t="str">
         <x:v>Adoption-Community-Nutzer hatten 30% mehr aktive Tage über 12 Wochen</x:v>
       </x:c>
-      <x:c r="C27" s="49" t="str">
+      <x:c r="C27" s="50" t="str">
         <x:v>https://adoption.microsoft.com/en-us/copilot/adoption-community/</x:v>
       </x:c>
-      <x:c r="D27" s="49" t="str">
+      <x:c r="D27" s="50" t="str">
         <x:v>Juli 2025</x:v>
       </x:c>
-      <x:c r="E27" s="49" t="str">
+      <x:c r="E27" s="50" t="str">
         <x:v>Interne Microsoft-Analyse</x:v>
       </x:c>
-      <x:c r="F27" s="49" t="str">
+      <x:c r="F27" s="50" t="str">
         <x:v>Stützt fortlaufendes Lernen und Community-Begleitung</x:v>
       </x:c>
     </x:row>
@@ -7149,7 +7451,7 @@
       <x:c r="A31" s="20" t="str">
         <x:v>Kick-off je Gruppe</x:v>
       </x:c>
-      <x:c r="B31" s="55" t="n">
+      <x:c r="B31" s="68" t="n">
         <x:v>1800</x:v>
       </x:c>
       <x:c r="C31" s="20" t="str">
@@ -7169,7 +7471,7 @@
       <x:c r="A32" s="20" t="str">
         <x:v>Anzahl Lernreise-Termine</x:v>
       </x:c>
-      <x:c r="B32" s="66" t="n">
+      <x:c r="B32" s="79" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C32" s="20" t="str">
@@ -7189,7 +7491,7 @@
       <x:c r="A33" s="20" t="str">
         <x:v>Gruppengröße</x:v>
       </x:c>
-      <x:c r="B33" s="66" t="n">
+      <x:c r="B33" s="79" t="n">
         <x:v>12</x:v>
       </x:c>
       <x:c r="C33" s="20" t="str">
@@ -7209,7 +7511,7 @@
       <x:c r="A34" s="20" t="str">
         <x:v>Weiterbildung Folgejahre</x:v>
       </x:c>
-      <x:c r="B34" s="56" t="n">
+      <x:c r="B34" s="69" t="n">
         <x:v>0.5</x:v>
       </x:c>
       <x:c r="C34" s="20" t="str">
@@ -7229,7 +7531,7 @@
       <x:c r="A35" s="20" t="str">
         <x:v>Preis je Lernreise-Termin</x:v>
       </x:c>
-      <x:c r="B35" s="55" t="n">
+      <x:c r="B35" s="68" t="n">
         <x:v>800</x:v>
       </x:c>
       <x:c r="C35" s="20" t="str">
@@ -7249,7 +7551,7 @@
       <x:c r="A36" s="20" t="str">
         <x:v>Change &amp; Adoption</x:v>
       </x:c>
-      <x:c r="B36" s="56" t="n">
+      <x:c r="B36" s="69" t="n">
         <x:v>0.12</x:v>
       </x:c>
       <x:c r="C36" s="20" t="str">
@@ -7300,7 +7602,7 @@
       <x:c r="A39" s="20" t="str">
         <x:v>Nutzerzahl &gt; 0</x:v>
       </x:c>
-      <x:c r="B39" s="42" t="str">
+      <x:c r="B39" s="43" t="str">
         <x:f>IF('1. Eingaben'!B8&gt;0,"OK","PRÜFEN")</x:f>
         <x:v>OK</x:v>
       </x:c>
@@ -7312,7 +7614,7 @@
       <x:c r="A40" s="20" t="str">
         <x:v>Gruppengröße &gt; 0</x:v>
       </x:c>
-      <x:c r="B40" s="42" t="str">
+      <x:c r="B40" s="43" t="str">
         <x:f>IF(B33&gt;0,"OK","PRÜFEN")</x:f>
         <x:v>OK</x:v>
       </x:c>
@@ -7324,7 +7626,7 @@
       <x:c r="A41" s="20" t="str">
         <x:v>Folgejahresfaktor 0–100%</x:v>
       </x:c>
-      <x:c r="B41" s="42" t="str">
+      <x:c r="B41" s="43" t="str">
         <x:f>IF(AND(B34&gt;=0,B34&lt;=1),"OK","PRÜFEN")</x:f>
         <x:v>OK</x:v>
       </x:c>
@@ -7336,7 +7638,7 @@
       <x:c r="A42" s="20" t="str">
         <x:v>IT-Setup steigt mit Nutzerzahl</x:v>
       </x:c>
-      <x:c r="B42" s="42" t="str">
+      <x:c r="B42" s="43" t="str">
         <x:f>IF('5. Berechnung'!F19&gt;0,"OK","PRÜFEN")</x:f>
         <x:v>OK</x:v>
       </x:c>
@@ -7348,7 +7650,7 @@
       <x:c r="A43" s="20" t="str">
         <x:v>Ziel-Zeitersparnis 0–20 Std./Monat</x:v>
       </x:c>
-      <x:c r="B43" s="42" t="str">
+      <x:c r="B43" s="43" t="str">
         <x:f>IF(AND(MIN('4. Szenarien'!B6:B7)&gt;=0,MAX('4. Szenarien'!B6:B7)&lt;=20),"OK","PRÜFEN")</x:f>
         <x:v>OK</x:v>
       </x:c>
@@ -7360,7 +7662,7 @@
       <x:c r="A44" s="20" t="str">
         <x:v>Realisierungsfaktor 0–100%</x:v>
       </x:c>
-      <x:c r="B44" s="42" t="str">
+      <x:c r="B44" s="43" t="str">
         <x:f>IF(AND(MIN('4. Szenarien'!D6:D7)&gt;=0,MAX('4. Szenarien'!D6:D7)&lt;=1),"OK","PRÜFEN")</x:f>
         <x:v>OK</x:v>
       </x:c>
@@ -7372,7 +7674,7 @@
       <x:c r="A45" s="20" t="str">
         <x:v>36 Monatszeilen vorhanden</x:v>
       </x:c>
-      <x:c r="B45" s="42" t="str">
+      <x:c r="B45" s="43" t="str">
         <x:f>IF(AND(MIN('5. Berechnung'!A26:A61)=1,MAX('5. Berechnung'!A26:A61)=36),"OK","PRÜFEN")</x:f>
         <x:v>OK</x:v>
       </x:c>
@@ -7384,7 +7686,7 @@
       <x:c r="A46" s="20" t="str">
         <x:v>Gesamtstatus</x:v>
       </x:c>
-      <x:c r="B46" s="132" t="str">
+      <x:c r="B46" s="122" t="str">
         <x:f>IF(COUNTIF(B39:B45,"PRÜFEN")=0,"PASS","PRÜFEN")</x:f>
         <x:v>PASS</x:v>
       </x:c>
@@ -7433,123 +7735,123 @@
       </x:c>
     </x:row>
     <x:row r="51">
-      <x:c r="A51" s="49" t="str">
+      <x:c r="A51" s="50" t="str">
         <x:v>DWP Microsoft 365 Copilot Evaluation</x:v>
       </x:c>
-      <x:c r="B51" s="49" t="str">
+      <x:c r="B51" s="50" t="str">
         <x:v>19 Min./Tag ≈ 6,9 Std./Monat</x:v>
       </x:c>
-      <x:c r="C51" s="49" t="str">
+      <x:c r="C51" s="50" t="str">
         <x:v>https://www.gov.uk/government/publications/an-evaluation-of-dwps-microsoft-copilot-365-trial/an-evaluation-of-dwps-microsoft-365-copilot-trial</x:v>
       </x:c>
-      <x:c r="D51" s="49" t="str">
+      <x:c r="D51" s="50" t="str">
         <x:v>Januar 2026</x:v>
       </x:c>
-      <x:c r="E51" s="49" t="str">
+      <x:c r="E51" s="50" t="str">
         <x:v>Unterhalb von 8 Std.; Vergleichsgruppe und Regression, aber selbstberichtete Zeitwerte</x:v>
       </x:c>
-      <x:c r="F51" s="49" t="str">
+      <x:c r="F51" s="50" t="str">
         <x:v>Nur Plausibilitätsprüfung</x:v>
       </x:c>
     </x:row>
     <x:row r="52">
-      <x:c r="A52" s="49" t="str">
+      <x:c r="A52" s="50" t="str">
         <x:v>UK Cross-Government Copilot Experiment</x:v>
       </x:c>
-      <x:c r="B52" s="49" t="str">
+      <x:c r="B52" s="50" t="str">
         <x:v>26 Min./Tag ≈ 9,4 Std./Monat</x:v>
       </x:c>
-      <x:c r="C52" s="49" t="str">
+      <x:c r="C52" s="50" t="str">
         <x:v>https://www.gov.uk/government/publications/microsoft-365-copilot-experiment-cross-government-findings-report/microsoft-365-copilot-experiment-cross-government-findings-report-html</x:v>
       </x:c>
-      <x:c r="D52" s="49" t="str">
+      <x:c r="D52" s="50" t="str">
         <x:v>Juni 2025</x:v>
       </x:c>
-      <x:c r="E52" s="49" t="str">
+      <x:c r="E52" s="50" t="str">
         <x:v>Nahe am studiennahen Szenario; selbstberichtete Zeitwerte</x:v>
       </x:c>
-      <x:c r="F52" s="49" t="str">
+      <x:c r="F52" s="50" t="str">
         <x:v>Nur Plausibilitätsprüfung</x:v>
       </x:c>
     </x:row>
     <x:row r="53">
-      <x:c r="A53" s="49" t="str">
+      <x:c r="A53" s="50" t="str">
         <x:v>OECD: Generative AI und Produktivität</x:v>
       </x:c>
-      <x:c r="B53" s="49" t="str">
+      <x:c r="B53" s="50" t="str">
         <x:v>Wirkung hängt stark von Aufgabe, Erfahrung und Mensch-KI-Zusammenarbeit ab</x:v>
       </x:c>
-      <x:c r="C53" s="49" t="str">
+      <x:c r="C53" s="50" t="str">
         <x:v>https://www.oecd.org/en/publications/the-effects-of-generative-ai-on-productivity-innovation-and-entrepreneurship_b21df222-en.html</x:v>
       </x:c>
-      <x:c r="D53" s="49" t="str">
+      <x:c r="D53" s="50" t="str">
         <x:v>Juni 2025</x:v>
       </x:c>
-      <x:c r="E53" s="49" t="str">
+      <x:c r="E53" s="50" t="str">
         <x:v>Begründet Szenarien und Erfolgsmessung statt eines universellen Werts</x:v>
       </x:c>
-      <x:c r="F53" s="49" t="str">
+      <x:c r="F53" s="50" t="str">
         <x:v>Nur Plausibilitätsprüfung</x:v>
       </x:c>
     </x:row>
     <x:row r="55">
-      <x:c r="A55" s="99" t="str">
-        <x:v>Abgrenzung: Die verwendeten Zeitwerte betreffen KI überwiegend als persönlichen Assistenten für einzelne Aufgaben. Zusätzlicher Nutzen aus agentischen, mehrstufigen Tätigkeiten ist nicht eingerechnet. Dadurch bleibt der Business Case bewusst auf heute besser belegbare Assistenz-Nutzung begrenzt.</x:v>
-      </x:c>
-      <x:c r="B55" s="100" t="str">
-        <x:v>Abgrenzung: Die verwendeten Zeitwerte betreffen KI überwiegend als persönlichen Assistenten für einzelne Aufgaben. Zusätzlicher Nutzen aus agentischen, mehrstufigen Tätigkeiten ist nicht eingerechnet. Dadurch bleibt der Business Case bewusst auf heute besser belegbare Assistenz-Nutzung begrenzt.</x:v>
-      </x:c>
-      <x:c r="C55" s="100" t="str">
-        <x:v>Abgrenzung: Die verwendeten Zeitwerte betreffen KI überwiegend als persönlichen Assistenten für einzelne Aufgaben. Zusätzlicher Nutzen aus agentischen, mehrstufigen Tätigkeiten ist nicht eingerechnet. Dadurch bleibt der Business Case bewusst auf heute besser belegbare Assistenz-Nutzung begrenzt.</x:v>
-      </x:c>
-      <x:c r="D55" s="100" t="str">
-        <x:v>Abgrenzung: Die verwendeten Zeitwerte betreffen KI überwiegend als persönlichen Assistenten für einzelne Aufgaben. Zusätzlicher Nutzen aus agentischen, mehrstufigen Tätigkeiten ist nicht eingerechnet. Dadurch bleibt der Business Case bewusst auf heute besser belegbare Assistenz-Nutzung begrenzt.</x:v>
-      </x:c>
-      <x:c r="E55" s="100" t="str">
-        <x:v>Abgrenzung: Die verwendeten Zeitwerte betreffen KI überwiegend als persönlichen Assistenten für einzelne Aufgaben. Zusätzlicher Nutzen aus agentischen, mehrstufigen Tätigkeiten ist nicht eingerechnet. Dadurch bleibt der Business Case bewusst auf heute besser belegbare Assistenz-Nutzung begrenzt.</x:v>
-      </x:c>
-      <x:c r="F55" s="101" t="str">
-        <x:v>Abgrenzung: Die verwendeten Zeitwerte betreffen KI überwiegend als persönlichen Assistenten für einzelne Aufgaben. Zusätzlicher Nutzen aus agentischen, mehrstufigen Tätigkeiten ist nicht eingerechnet. Dadurch bleibt der Business Case bewusst auf heute besser belegbare Assistenz-Nutzung begrenzt.</x:v>
+      <x:c r="A55" s="60" t="str">
+        <x:v>Abgrenzung: Die verwendeten Zeitwerte betreffen KI überwiegend als persönlichen Assistenten für einzelne Aufgaben. Die Assistenz-Baseline wird nach dem Kompetenzaufbau konstant gehalten, ist aber keine Sättigungsannahme für das gesamte KI-Potenzial. Zusätzlicher Nutzen durch leistungsfähigere Modelle, neue Funktionen und Tools, tiefere Prozessintegration sowie agentische, mehrstufige Tätigkeiten ist nicht eingerechnet. Dadurch bleibt der Business Case auf heute besser belegbare Nutzung begrenzt und enthält bewusst weiteres Aufwärtspotenzial.</x:v>
+      </x:c>
+      <x:c r="B55" s="61" t="str">
+        <x:v>Abgrenzung: Die verwendeten Zeitwerte betreffen KI überwiegend als persönlichen Assistenten für einzelne Aufgaben. Die Assistenz-Baseline wird nach dem Kompetenzaufbau konstant gehalten, ist aber keine Sättigungsannahme für das gesamte KI-Potenzial. Zusätzlicher Nutzen durch leistungsfähigere Modelle, neue Funktionen und Tools, tiefere Prozessintegration sowie agentische, mehrstufige Tätigkeiten ist nicht eingerechnet. Dadurch bleibt der Business Case auf heute besser belegbare Nutzung begrenzt und enthält bewusst weiteres Aufwärtspotenzial.</x:v>
+      </x:c>
+      <x:c r="C55" s="61" t="str">
+        <x:v>Abgrenzung: Die verwendeten Zeitwerte betreffen KI überwiegend als persönlichen Assistenten für einzelne Aufgaben. Die Assistenz-Baseline wird nach dem Kompetenzaufbau konstant gehalten, ist aber keine Sättigungsannahme für das gesamte KI-Potenzial. Zusätzlicher Nutzen durch leistungsfähigere Modelle, neue Funktionen und Tools, tiefere Prozessintegration sowie agentische, mehrstufige Tätigkeiten ist nicht eingerechnet. Dadurch bleibt der Business Case auf heute besser belegbare Nutzung begrenzt und enthält bewusst weiteres Aufwärtspotenzial.</x:v>
+      </x:c>
+      <x:c r="D55" s="61" t="str">
+        <x:v>Abgrenzung: Die verwendeten Zeitwerte betreffen KI überwiegend als persönlichen Assistenten für einzelne Aufgaben. Die Assistenz-Baseline wird nach dem Kompetenzaufbau konstant gehalten, ist aber keine Sättigungsannahme für das gesamte KI-Potenzial. Zusätzlicher Nutzen durch leistungsfähigere Modelle, neue Funktionen und Tools, tiefere Prozessintegration sowie agentische, mehrstufige Tätigkeiten ist nicht eingerechnet. Dadurch bleibt der Business Case auf heute besser belegbare Nutzung begrenzt und enthält bewusst weiteres Aufwärtspotenzial.</x:v>
+      </x:c>
+      <x:c r="E55" s="61" t="str">
+        <x:v>Abgrenzung: Die verwendeten Zeitwerte betreffen KI überwiegend als persönlichen Assistenten für einzelne Aufgaben. Die Assistenz-Baseline wird nach dem Kompetenzaufbau konstant gehalten, ist aber keine Sättigungsannahme für das gesamte KI-Potenzial. Zusätzlicher Nutzen durch leistungsfähigere Modelle, neue Funktionen und Tools, tiefere Prozessintegration sowie agentische, mehrstufige Tätigkeiten ist nicht eingerechnet. Dadurch bleibt der Business Case auf heute besser belegbare Nutzung begrenzt und enthält bewusst weiteres Aufwärtspotenzial.</x:v>
+      </x:c>
+      <x:c r="F55" s="62" t="str">
+        <x:v>Abgrenzung: Die verwendeten Zeitwerte betreffen KI überwiegend als persönlichen Assistenten für einzelne Aufgaben. Die Assistenz-Baseline wird nach dem Kompetenzaufbau konstant gehalten, ist aber keine Sättigungsannahme für das gesamte KI-Potenzial. Zusätzlicher Nutzen durch leistungsfähigere Modelle, neue Funktionen und Tools, tiefere Prozessintegration sowie agentische, mehrstufige Tätigkeiten ist nicht eingerechnet. Dadurch bleibt der Business Case auf heute besser belegbare Nutzung begrenzt und enthält bewusst weiteres Aufwärtspotenzial.</x:v>
       </x:c>
     </x:row>
     <x:row r="56">
-      <x:c r="A56" s="102" t="str">
-        <x:v>Abgrenzung: Die verwendeten Zeitwerte betreffen KI überwiegend als persönlichen Assistenten für einzelne Aufgaben. Zusätzlicher Nutzen aus agentischen, mehrstufigen Tätigkeiten ist nicht eingerechnet. Dadurch bleibt der Business Case bewusst auf heute besser belegbare Assistenz-Nutzung begrenzt.</x:v>
-      </x:c>
-      <x:c r="B56" s="98" t="str">
-        <x:v>Abgrenzung: Die verwendeten Zeitwerte betreffen KI überwiegend als persönlichen Assistenten für einzelne Aufgaben. Zusätzlicher Nutzen aus agentischen, mehrstufigen Tätigkeiten ist nicht eingerechnet. Dadurch bleibt der Business Case bewusst auf heute besser belegbare Assistenz-Nutzung begrenzt.</x:v>
-      </x:c>
-      <x:c r="C56" s="98" t="str">
-        <x:v>Abgrenzung: Die verwendeten Zeitwerte betreffen KI überwiegend als persönlichen Assistenten für einzelne Aufgaben. Zusätzlicher Nutzen aus agentischen, mehrstufigen Tätigkeiten ist nicht eingerechnet. Dadurch bleibt der Business Case bewusst auf heute besser belegbare Assistenz-Nutzung begrenzt.</x:v>
-      </x:c>
-      <x:c r="D56" s="98" t="str">
-        <x:v>Abgrenzung: Die verwendeten Zeitwerte betreffen KI überwiegend als persönlichen Assistenten für einzelne Aufgaben. Zusätzlicher Nutzen aus agentischen, mehrstufigen Tätigkeiten ist nicht eingerechnet. Dadurch bleibt der Business Case bewusst auf heute besser belegbare Assistenz-Nutzung begrenzt.</x:v>
-      </x:c>
-      <x:c r="E56" s="98" t="str">
-        <x:v>Abgrenzung: Die verwendeten Zeitwerte betreffen KI überwiegend als persönlichen Assistenten für einzelne Aufgaben. Zusätzlicher Nutzen aus agentischen, mehrstufigen Tätigkeiten ist nicht eingerechnet. Dadurch bleibt der Business Case bewusst auf heute besser belegbare Assistenz-Nutzung begrenzt.</x:v>
-      </x:c>
-      <x:c r="F56" s="103" t="str">
-        <x:v>Abgrenzung: Die verwendeten Zeitwerte betreffen KI überwiegend als persönlichen Assistenten für einzelne Aufgaben. Zusätzlicher Nutzen aus agentischen, mehrstufigen Tätigkeiten ist nicht eingerechnet. Dadurch bleibt der Business Case bewusst auf heute besser belegbare Assistenz-Nutzung begrenzt.</x:v>
+      <x:c r="A56" s="63" t="str">
+        <x:v>Abgrenzung: Die verwendeten Zeitwerte betreffen KI überwiegend als persönlichen Assistenten für einzelne Aufgaben. Die Assistenz-Baseline wird nach dem Kompetenzaufbau konstant gehalten, ist aber keine Sättigungsannahme für das gesamte KI-Potenzial. Zusätzlicher Nutzen durch leistungsfähigere Modelle, neue Funktionen und Tools, tiefere Prozessintegration sowie agentische, mehrstufige Tätigkeiten ist nicht eingerechnet. Dadurch bleibt der Business Case auf heute besser belegbare Nutzung begrenzt und enthält bewusst weiteres Aufwärtspotenzial.</x:v>
+      </x:c>
+      <x:c r="B56" s="59" t="str">
+        <x:v>Abgrenzung: Die verwendeten Zeitwerte betreffen KI überwiegend als persönlichen Assistenten für einzelne Aufgaben. Die Assistenz-Baseline wird nach dem Kompetenzaufbau konstant gehalten, ist aber keine Sättigungsannahme für das gesamte KI-Potenzial. Zusätzlicher Nutzen durch leistungsfähigere Modelle, neue Funktionen und Tools, tiefere Prozessintegration sowie agentische, mehrstufige Tätigkeiten ist nicht eingerechnet. Dadurch bleibt der Business Case auf heute besser belegbare Nutzung begrenzt und enthält bewusst weiteres Aufwärtspotenzial.</x:v>
+      </x:c>
+      <x:c r="C56" s="59" t="str">
+        <x:v>Abgrenzung: Die verwendeten Zeitwerte betreffen KI überwiegend als persönlichen Assistenten für einzelne Aufgaben. Die Assistenz-Baseline wird nach dem Kompetenzaufbau konstant gehalten, ist aber keine Sättigungsannahme für das gesamte KI-Potenzial. Zusätzlicher Nutzen durch leistungsfähigere Modelle, neue Funktionen und Tools, tiefere Prozessintegration sowie agentische, mehrstufige Tätigkeiten ist nicht eingerechnet. Dadurch bleibt der Business Case auf heute besser belegbare Nutzung begrenzt und enthält bewusst weiteres Aufwärtspotenzial.</x:v>
+      </x:c>
+      <x:c r="D56" s="59" t="str">
+        <x:v>Abgrenzung: Die verwendeten Zeitwerte betreffen KI überwiegend als persönlichen Assistenten für einzelne Aufgaben. Die Assistenz-Baseline wird nach dem Kompetenzaufbau konstant gehalten, ist aber keine Sättigungsannahme für das gesamte KI-Potenzial. Zusätzlicher Nutzen durch leistungsfähigere Modelle, neue Funktionen und Tools, tiefere Prozessintegration sowie agentische, mehrstufige Tätigkeiten ist nicht eingerechnet. Dadurch bleibt der Business Case auf heute besser belegbare Nutzung begrenzt und enthält bewusst weiteres Aufwärtspotenzial.</x:v>
+      </x:c>
+      <x:c r="E56" s="59" t="str">
+        <x:v>Abgrenzung: Die verwendeten Zeitwerte betreffen KI überwiegend als persönlichen Assistenten für einzelne Aufgaben. Die Assistenz-Baseline wird nach dem Kompetenzaufbau konstant gehalten, ist aber keine Sättigungsannahme für das gesamte KI-Potenzial. Zusätzlicher Nutzen durch leistungsfähigere Modelle, neue Funktionen und Tools, tiefere Prozessintegration sowie agentische, mehrstufige Tätigkeiten ist nicht eingerechnet. Dadurch bleibt der Business Case auf heute besser belegbare Nutzung begrenzt und enthält bewusst weiteres Aufwärtspotenzial.</x:v>
+      </x:c>
+      <x:c r="F56" s="64" t="str">
+        <x:v>Abgrenzung: Die verwendeten Zeitwerte betreffen KI überwiegend als persönlichen Assistenten für einzelne Aufgaben. Die Assistenz-Baseline wird nach dem Kompetenzaufbau konstant gehalten, ist aber keine Sättigungsannahme für das gesamte KI-Potenzial. Zusätzlicher Nutzen durch leistungsfähigere Modelle, neue Funktionen und Tools, tiefere Prozessintegration sowie agentische, mehrstufige Tätigkeiten ist nicht eingerechnet. Dadurch bleibt der Business Case auf heute besser belegbare Nutzung begrenzt und enthält bewusst weiteres Aufwärtspotenzial.</x:v>
       </x:c>
     </x:row>
     <x:row r="57">
-      <x:c r="A57" s="104" t="str">
-        <x:v>Abgrenzung: Die verwendeten Zeitwerte betreffen KI überwiegend als persönlichen Assistenten für einzelne Aufgaben. Zusätzlicher Nutzen aus agentischen, mehrstufigen Tätigkeiten ist nicht eingerechnet. Dadurch bleibt der Business Case bewusst auf heute besser belegbare Assistenz-Nutzung begrenzt.</x:v>
-      </x:c>
-      <x:c r="B57" s="105" t="str">
-        <x:v>Abgrenzung: Die verwendeten Zeitwerte betreffen KI überwiegend als persönlichen Assistenten für einzelne Aufgaben. Zusätzlicher Nutzen aus agentischen, mehrstufigen Tätigkeiten ist nicht eingerechnet. Dadurch bleibt der Business Case bewusst auf heute besser belegbare Assistenz-Nutzung begrenzt.</x:v>
-      </x:c>
-      <x:c r="C57" s="105" t="str">
-        <x:v>Abgrenzung: Die verwendeten Zeitwerte betreffen KI überwiegend als persönlichen Assistenten für einzelne Aufgaben. Zusätzlicher Nutzen aus agentischen, mehrstufigen Tätigkeiten ist nicht eingerechnet. Dadurch bleibt der Business Case bewusst auf heute besser belegbare Assistenz-Nutzung begrenzt.</x:v>
-      </x:c>
-      <x:c r="D57" s="105" t="str">
-        <x:v>Abgrenzung: Die verwendeten Zeitwerte betreffen KI überwiegend als persönlichen Assistenten für einzelne Aufgaben. Zusätzlicher Nutzen aus agentischen, mehrstufigen Tätigkeiten ist nicht eingerechnet. Dadurch bleibt der Business Case bewusst auf heute besser belegbare Assistenz-Nutzung begrenzt.</x:v>
-      </x:c>
-      <x:c r="E57" s="105" t="str">
-        <x:v>Abgrenzung: Die verwendeten Zeitwerte betreffen KI überwiegend als persönlichen Assistenten für einzelne Aufgaben. Zusätzlicher Nutzen aus agentischen, mehrstufigen Tätigkeiten ist nicht eingerechnet. Dadurch bleibt der Business Case bewusst auf heute besser belegbare Assistenz-Nutzung begrenzt.</x:v>
-      </x:c>
-      <x:c r="F57" s="106" t="str">
-        <x:v>Abgrenzung: Die verwendeten Zeitwerte betreffen KI überwiegend als persönlichen Assistenten für einzelne Aufgaben. Zusätzlicher Nutzen aus agentischen, mehrstufigen Tätigkeiten ist nicht eingerechnet. Dadurch bleibt der Business Case bewusst auf heute besser belegbare Assistenz-Nutzung begrenzt.</x:v>
+      <x:c r="A57" s="65" t="str">
+        <x:v>Abgrenzung: Die verwendeten Zeitwerte betreffen KI überwiegend als persönlichen Assistenten für einzelne Aufgaben. Die Assistenz-Baseline wird nach dem Kompetenzaufbau konstant gehalten, ist aber keine Sättigungsannahme für das gesamte KI-Potenzial. Zusätzlicher Nutzen durch leistungsfähigere Modelle, neue Funktionen und Tools, tiefere Prozessintegration sowie agentische, mehrstufige Tätigkeiten ist nicht eingerechnet. Dadurch bleibt der Business Case auf heute besser belegbare Nutzung begrenzt und enthält bewusst weiteres Aufwärtspotenzial.</x:v>
+      </x:c>
+      <x:c r="B57" s="66" t="str">
+        <x:v>Abgrenzung: Die verwendeten Zeitwerte betreffen KI überwiegend als persönlichen Assistenten für einzelne Aufgaben. Die Assistenz-Baseline wird nach dem Kompetenzaufbau konstant gehalten, ist aber keine Sättigungsannahme für das gesamte KI-Potenzial. Zusätzlicher Nutzen durch leistungsfähigere Modelle, neue Funktionen und Tools, tiefere Prozessintegration sowie agentische, mehrstufige Tätigkeiten ist nicht eingerechnet. Dadurch bleibt der Business Case auf heute besser belegbare Nutzung begrenzt und enthält bewusst weiteres Aufwärtspotenzial.</x:v>
+      </x:c>
+      <x:c r="C57" s="66" t="str">
+        <x:v>Abgrenzung: Die verwendeten Zeitwerte betreffen KI überwiegend als persönlichen Assistenten für einzelne Aufgaben. Die Assistenz-Baseline wird nach dem Kompetenzaufbau konstant gehalten, ist aber keine Sättigungsannahme für das gesamte KI-Potenzial. Zusätzlicher Nutzen durch leistungsfähigere Modelle, neue Funktionen und Tools, tiefere Prozessintegration sowie agentische, mehrstufige Tätigkeiten ist nicht eingerechnet. Dadurch bleibt der Business Case auf heute besser belegbare Nutzung begrenzt und enthält bewusst weiteres Aufwärtspotenzial.</x:v>
+      </x:c>
+      <x:c r="D57" s="66" t="str">
+        <x:v>Abgrenzung: Die verwendeten Zeitwerte betreffen KI überwiegend als persönlichen Assistenten für einzelne Aufgaben. Die Assistenz-Baseline wird nach dem Kompetenzaufbau konstant gehalten, ist aber keine Sättigungsannahme für das gesamte KI-Potenzial. Zusätzlicher Nutzen durch leistungsfähigere Modelle, neue Funktionen und Tools, tiefere Prozessintegration sowie agentische, mehrstufige Tätigkeiten ist nicht eingerechnet. Dadurch bleibt der Business Case auf heute besser belegbare Nutzung begrenzt und enthält bewusst weiteres Aufwärtspotenzial.</x:v>
+      </x:c>
+      <x:c r="E57" s="66" t="str">
+        <x:v>Abgrenzung: Die verwendeten Zeitwerte betreffen KI überwiegend als persönlichen Assistenten für einzelne Aufgaben. Die Assistenz-Baseline wird nach dem Kompetenzaufbau konstant gehalten, ist aber keine Sättigungsannahme für das gesamte KI-Potenzial. Zusätzlicher Nutzen durch leistungsfähigere Modelle, neue Funktionen und Tools, tiefere Prozessintegration sowie agentische, mehrstufige Tätigkeiten ist nicht eingerechnet. Dadurch bleibt der Business Case auf heute besser belegbare Nutzung begrenzt und enthält bewusst weiteres Aufwärtspotenzial.</x:v>
+      </x:c>
+      <x:c r="F57" s="67" t="str">
+        <x:v>Abgrenzung: Die verwendeten Zeitwerte betreffen KI überwiegend als persönlichen Assistenten für einzelne Aufgaben. Die Assistenz-Baseline wird nach dem Kompetenzaufbau konstant gehalten, ist aber keine Sättigungsannahme für das gesamte KI-Potenzial. Zusätzlicher Nutzen durch leistungsfähigere Modelle, neue Funktionen und Tools, tiefere Prozessintegration sowie agentische, mehrstufige Tätigkeiten ist nicht eingerechnet. Dadurch bleibt der Business Case auf heute besser belegbare Nutzung begrenzt und enthält bewusst weiteres Aufwärtspotenzial.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
